--- a/TRAME_260512_NOTES_BAC_BLANC_N°2_v2.xlsx
+++ b/TRAME_260512_NOTES_BAC_BLANC_N°2_v2.xlsx
@@ -1489,7 +1489,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CE4B"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
@@ -13238,7 +13238,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1" password="CE4B"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:CR2"/>
     <mergeCell ref="A1:CR1"/>

--- a/TRAME_260512_NOTES_BAC_BLANC_N°2_v2.xlsx
+++ b/TRAME_260512_NOTES_BAC_BLANC_N°2_v2.xlsx
@@ -2399,7 +2399,7 @@
       </c>
       <c r="G5" s="18" t="n"/>
       <c r="H5" s="19">
-        <f>IF(G5="","",IF(G5="NE","",IF(G5="0",0,IF(G5="1",0.5,IF(G5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(G5="","",IF(G5="NE","",(IFERROR(IF(ISNUMBER(G5),G5,VALUE(G5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="I5" s="20">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="J5" s="18" t="n"/>
       <c r="K5" s="19">
-        <f>IF(J5="","",IF(J5="NE","",IF(J5="0",0,IF(J5="1",0.5,IF(J5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(J5="","",IF(J5="NE","",(IFERROR(IF(ISNUMBER(J5),J5,VALUE(J5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="L5" s="20">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="M5" s="18" t="n"/>
       <c r="N5" s="19">
-        <f>IF(M5="","",IF(M5="NE","",IF(M5="0",0,IF(M5="1",0.5,IF(M5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(M5="","",IF(M5="NE","",(IFERROR(IF(ISNUMBER(M5),M5,VALUE(M5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="O5" s="20">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="P5" s="18" t="n"/>
       <c r="Q5" s="19">
-        <f>IF(P5="","",IF(P5="NE","",IF(P5="0",0,IF(P5="1",0.5,IF(P5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(P5="","",IF(P5="NE","",(IFERROR(IF(ISNUMBER(P5),P5,VALUE(P5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="R5" s="20">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="S5" s="18" t="n"/>
       <c r="T5" s="19">
-        <f>IF(S5="","",IF(S5="NE","",IF(S5="0",0,IF(S5="1",0.5,IF(S5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(S5="","",IF(S5="NE","",(IFERROR(IF(ISNUMBER(S5),S5,VALUE(S5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="U5" s="20">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="V5" s="18" t="n"/>
       <c r="W5" s="19">
-        <f>IF(V5="","",IF(V5="NE","",IF(V5="0",0,IF(V5="1",0.5,IF(V5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(V5="","",IF(V5="NE","",(IFERROR(IF(ISNUMBER(V5),V5,VALUE(V5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="X5" s="20">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="Y5" s="18" t="n"/>
       <c r="Z5" s="19">
-        <f>IF(Y5="","",IF(Y5="NE","",IF(Y5="0",0,IF(Y5="1",0.5,IF(Y5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(Y5="","",IF(Y5="NE","",(IFERROR(IF(ISNUMBER(Y5),Y5,VALUE(Y5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AA5" s="20">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB5" s="18" t="n"/>
       <c r="AC5" s="19">
-        <f>IF(AB5="","",IF(AB5="NE","",IF(AB5="0",0,IF(AB5="1",0.5,IF(AB5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AB5="","",IF(AB5="NE","",(IFERROR(IF(ISNUMBER(AB5),AB5,VALUE(AB5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AD5" s="20">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="AE5" s="18" t="n"/>
       <c r="AF5" s="19">
-        <f>IF(AE5="","",IF(AE5="NE","",IF(AE5="0",0,IF(AE5="1",0.5,IF(AE5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AE5="","",IF(AE5="NE","",(IFERROR(IF(ISNUMBER(AE5),AE5,VALUE(AE5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AG5" s="20">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="AH5" s="18" t="n"/>
       <c r="AI5" s="19">
-        <f>IF(AH5="","",IF(AH5="NE","",IF(AH5="0",0,IF(AH5="1",0.5,IF(AH5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AH5="","",IF(AH5="NE","",(IFERROR(IF(ISNUMBER(AH5),AH5,VALUE(AH5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AJ5" s="20">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AK5" s="18" t="n"/>
       <c r="AL5" s="19">
-        <f>IF(AK5="","",IF(AK5="NE","",IF(AK5="0",0,IF(AK5="1",0.5,IF(AK5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AK5="","",IF(AK5="NE","",(IFERROR(IF(ISNUMBER(AK5),AK5,VALUE(AK5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AM5" s="20">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AN5" s="18" t="n"/>
       <c r="AO5" s="19">
-        <f>IF(AN5="","",IF(AN5="NE","",IF(AN5="0",0,IF(AN5="1",0.5,IF(AN5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AN5="","",IF(AN5="NE","",(IFERROR(IF(ISNUMBER(AN5),AN5,VALUE(AN5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AP5" s="20">
@@ -2507,7 +2507,7 @@
       </c>
       <c r="AQ5" s="18" t="n"/>
       <c r="AR5" s="19">
-        <f>IF(AQ5="","",IF(AQ5="NE","",IF(AQ5="0",0,IF(AQ5="1",0.5,IF(AQ5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AQ5="","",IF(AQ5="NE","",(IFERROR(IF(ISNUMBER(AQ5),AQ5,VALUE(AQ5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AS5" s="20">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="AT5" s="18" t="n"/>
       <c r="AU5" s="19">
-        <f>IF(AT5="","",IF(AT5="NE","",IF(AT5="0",0,IF(AT5="1",0.5,IF(AT5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AT5="","",IF(AT5="NE","",(IFERROR(IF(ISNUMBER(AT5),AT5,VALUE(AT5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AV5" s="20">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="AW5" s="18" t="n"/>
       <c r="AX5" s="19">
-        <f>IF(AW5="","",IF(AW5="NE","",IF(AW5="0",0,IF(AW5="1",0.5,IF(AW5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AW5="","",IF(AW5="NE","",(IFERROR(IF(ISNUMBER(AW5),AW5,VALUE(AW5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="AY5" s="20">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AZ5" s="18" t="n"/>
       <c r="BA5" s="19">
-        <f>IF(AZ5="","",IF(AZ5="NE","",IF(AZ5="0",0,IF(AZ5="1",0.5,IF(AZ5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(AZ5="","",IF(AZ5="NE","",(IFERROR(IF(ISNUMBER(AZ5),AZ5,VALUE(AZ5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BB5" s="20">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="BC5" s="18" t="n"/>
       <c r="BD5" s="19">
-        <f>IF(BC5="","",IF(BC5="NE","",IF(BC5="0",0,IF(BC5="1",0.5,IF(BC5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BC5="","",IF(BC5="NE","",(IFERROR(IF(ISNUMBER(BC5),BC5,VALUE(BC5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BE5" s="20">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="BF5" s="18" t="n"/>
       <c r="BG5" s="19">
-        <f>IF(BF5="","",IF(BF5="NE","",IF(BF5="0",0,IF(BF5="1",0.5,IF(BF5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BF5="","",IF(BF5="NE","",(IFERROR(IF(ISNUMBER(BF5),BF5,VALUE(BF5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BH5" s="20">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="BI5" s="18" t="n"/>
       <c r="BJ5" s="19">
-        <f>IF(BI5="","",IF(BI5="NE","",IF(BI5="0",0,IF(BI5="1",0.5,IF(BI5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BI5="","",IF(BI5="NE","",(IFERROR(IF(ISNUMBER(BI5),BI5,VALUE(BI5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BK5" s="20">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="BL5" s="18" t="n"/>
       <c r="BM5" s="19">
-        <f>IF(BL5="","",IF(BL5="NE","",IF(BL5="0",0,IF(BL5="1",0.5,IF(BL5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BL5="","",IF(BL5="NE","",(IFERROR(IF(ISNUMBER(BL5),BL5,VALUE(BL5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BN5" s="20">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="BO5" s="18" t="n"/>
       <c r="BP5" s="19">
-        <f>IF(BO5="","",IF(BO5="NE","",IF(BO5="0",0,IF(BO5="1",0.5,IF(BO5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BO5="","",IF(BO5="NE","",(IFERROR(IF(ISNUMBER(BO5),BO5,VALUE(BO5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BQ5" s="20">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="BR5" s="18" t="n"/>
       <c r="BS5" s="19">
-        <f>IF(BR5="","",IF(BR5="NE","",IF(BR5="0",0,IF(BR5="1",0.5,IF(BR5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BR5="","",IF(BR5="NE","",(IFERROR(IF(ISNUMBER(BR5),BR5,VALUE(BR5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BT5" s="20">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="BU5" s="18" t="n"/>
       <c r="BV5" s="19">
-        <f>IF(BU5="","",IF(BU5="NE","",IF(BU5="0",0,IF(BU5="1",0.5,IF(BU5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BU5="","",IF(BU5="NE","",(IFERROR(IF(ISNUMBER(BU5),BU5,VALUE(BU5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BW5" s="20">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="BX5" s="18" t="n"/>
       <c r="BY5" s="19">
-        <f>IF(BX5="","",IF(BX5="NE","",IF(BX5="0",0,IF(BX5="1",0.5,IF(BX5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(BX5="","",IF(BX5="NE","",(IFERROR(IF(ISNUMBER(BX5),BX5,VALUE(BX5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="BZ5" s="20">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="CA5" s="18" t="n"/>
       <c r="CB5" s="19">
-        <f>IF(CA5="","",IF(CA5="NE","",IF(CA5="0",0,IF(CA5="1",0.5,IF(CA5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(CA5="","",IF(CA5="NE","",(IFERROR(IF(ISNUMBER(CA5),CA5,VALUE(CA5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="CC5" s="20">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="CD5" s="18" t="n"/>
       <c r="CE5" s="19">
-        <f>IF(CD5="","",IF(CD5="NE","",IF(CD5="0",0,IF(CD5="1",0.5,IF(CD5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(CD5="","",IF(CD5="NE","",(IFERROR(IF(ISNUMBER(CD5),CD5,VALUE(CD5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="CF5" s="20">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="CG5" s="18" t="n"/>
       <c r="CH5" s="19">
-        <f>IF(CG5="","",IF(CG5="NE","",IF(CG5="0",0,IF(CG5="1",0.5,IF(CG5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(CG5="","",IF(CG5="NE","",(IFERROR(IF(ISNUMBER(CG5),CG5,VALUE(CG5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="CI5" s="20">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="CJ5" s="18" t="n"/>
       <c r="CK5" s="19">
-        <f>IF(CJ5="","",IF(CJ5="NE","",IF(CJ5="0",0,IF(CJ5="1",0.5,IF(CJ5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(CJ5="","",IF(CJ5="NE","",(IFERROR(IF(ISNUMBER(CJ5),CJ5,VALUE(CJ5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="CL5" s="20">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="CM5" s="18" t="n"/>
       <c r="CN5" s="19">
-        <f>IF(CM5="","",IF(CM5="NE","",IF(CM5="0",0,IF(CM5="1",0.5,IF(CM5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(CM5="","",IF(CM5="NE","",(IFERROR(IF(ISNUMBER(CM5),CM5,VALUE(CM5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="CO5" s="20">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="CP5" s="18" t="n"/>
       <c r="CQ5" s="19">
-        <f>IF(CP5="","",IF(CP5="NE","",IF(CP5="0",0,IF(CP5="1",0.5,IF(CP5="2",1,0)))*$F5*$F$4*20))</f>
+        <f>IF(CP5="","",IF(CP5="NE","",(IFERROR(IF(ISNUMBER(CP5),CP5,VALUE(CP5)),0)/2)*$F5*$F$4*20))</f>
         <v/>
       </c>
       <c r="CR5" s="20">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="G6" s="18" t="n"/>
       <c r="H6" s="19">
-        <f>IF(G6="","",IF(G6="NE","",IF(G6="0",0,IF(G6="1",0.5,IF(G6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(G6="","",IF(G6="NE","",(IFERROR(IF(ISNUMBER(G6),G6,VALUE(G6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="I6" s="20">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="J6" s="18" t="n"/>
       <c r="K6" s="19">
-        <f>IF(J6="","",IF(J6="NE","",IF(J6="0",0,IF(J6="1",0.5,IF(J6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(J6="","",IF(J6="NE","",(IFERROR(IF(ISNUMBER(J6),J6,VALUE(J6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="L6" s="20">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="M6" s="18" t="n"/>
       <c r="N6" s="19">
-        <f>IF(M6="","",IF(M6="NE","",IF(M6="0",0,IF(M6="1",0.5,IF(M6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(M6="","",IF(M6="NE","",(IFERROR(IF(ISNUMBER(M6),M6,VALUE(M6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="O6" s="20">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="P6" s="18" t="n"/>
       <c r="Q6" s="19">
-        <f>IF(P6="","",IF(P6="NE","",IF(P6="0",0,IF(P6="1",0.5,IF(P6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(P6="","",IF(P6="NE","",(IFERROR(IF(ISNUMBER(P6),P6,VALUE(P6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="R6" s="20">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="S6" s="18" t="n"/>
       <c r="T6" s="19">
-        <f>IF(S6="","",IF(S6="NE","",IF(S6="0",0,IF(S6="1",0.5,IF(S6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(S6="","",IF(S6="NE","",(IFERROR(IF(ISNUMBER(S6),S6,VALUE(S6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="U6" s="20">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="V6" s="18" t="n"/>
       <c r="W6" s="19">
-        <f>IF(V6="","",IF(V6="NE","",IF(V6="0",0,IF(V6="1",0.5,IF(V6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(V6="","",IF(V6="NE","",(IFERROR(IF(ISNUMBER(V6),V6,VALUE(V6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="X6" s="20">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="Y6" s="18" t="n"/>
       <c r="Z6" s="19">
-        <f>IF(Y6="","",IF(Y6="NE","",IF(Y6="0",0,IF(Y6="1",0.5,IF(Y6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(Y6="","",IF(Y6="NE","",(IFERROR(IF(ISNUMBER(Y6),Y6,VALUE(Y6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AA6" s="20">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="AB6" s="18" t="n"/>
       <c r="AC6" s="19">
-        <f>IF(AB6="","",IF(AB6="NE","",IF(AB6="0",0,IF(AB6="1",0.5,IF(AB6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AB6="","",IF(AB6="NE","",(IFERROR(IF(ISNUMBER(AB6),AB6,VALUE(AB6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AD6" s="20">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="AE6" s="18" t="n"/>
       <c r="AF6" s="19">
-        <f>IF(AE6="","",IF(AE6="NE","",IF(AE6="0",0,IF(AE6="1",0.5,IF(AE6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AE6="","",IF(AE6="NE","",(IFERROR(IF(ISNUMBER(AE6),AE6,VALUE(AE6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AG6" s="20">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AH6" s="18" t="n"/>
       <c r="AI6" s="19">
-        <f>IF(AH6="","",IF(AH6="NE","",IF(AH6="0",0,IF(AH6="1",0.5,IF(AH6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AH6="","",IF(AH6="NE","",(IFERROR(IF(ISNUMBER(AH6),AH6,VALUE(AH6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AJ6" s="20">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="AK6" s="18" t="n"/>
       <c r="AL6" s="19">
-        <f>IF(AK6="","",IF(AK6="NE","",IF(AK6="0",0,IF(AK6="1",0.5,IF(AK6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AK6="","",IF(AK6="NE","",(IFERROR(IF(ISNUMBER(AK6),AK6,VALUE(AK6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AM6" s="20">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="AN6" s="18" t="n"/>
       <c r="AO6" s="19">
-        <f>IF(AN6="","",IF(AN6="NE","",IF(AN6="0",0,IF(AN6="1",0.5,IF(AN6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AN6="","",IF(AN6="NE","",(IFERROR(IF(ISNUMBER(AN6),AN6,VALUE(AN6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AP6" s="20">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="AQ6" s="18" t="n"/>
       <c r="AR6" s="19">
-        <f>IF(AQ6="","",IF(AQ6="NE","",IF(AQ6="0",0,IF(AQ6="1",0.5,IF(AQ6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AQ6="","",IF(AQ6="NE","",(IFERROR(IF(ISNUMBER(AQ6),AQ6,VALUE(AQ6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AS6" s="20">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AT6" s="18" t="n"/>
       <c r="AU6" s="19">
-        <f>IF(AT6="","",IF(AT6="NE","",IF(AT6="0",0,IF(AT6="1",0.5,IF(AT6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AT6="","",IF(AT6="NE","",(IFERROR(IF(ISNUMBER(AT6),AT6,VALUE(AT6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AV6" s="20">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW6" s="18" t="n"/>
       <c r="AX6" s="19">
-        <f>IF(AW6="","",IF(AW6="NE","",IF(AW6="0",0,IF(AW6="1",0.5,IF(AW6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AW6="","",IF(AW6="NE","",(IFERROR(IF(ISNUMBER(AW6),AW6,VALUE(AW6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="AY6" s="20">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="AZ6" s="18" t="n"/>
       <c r="BA6" s="19">
-        <f>IF(AZ6="","",IF(AZ6="NE","",IF(AZ6="0",0,IF(AZ6="1",0.5,IF(AZ6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(AZ6="","",IF(AZ6="NE","",(IFERROR(IF(ISNUMBER(AZ6),AZ6,VALUE(AZ6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BB6" s="20">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="BC6" s="18" t="n"/>
       <c r="BD6" s="19">
-        <f>IF(BC6="","",IF(BC6="NE","",IF(BC6="0",0,IF(BC6="1",0.5,IF(BC6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BC6="","",IF(BC6="NE","",(IFERROR(IF(ISNUMBER(BC6),BC6,VALUE(BC6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BE6" s="20">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="BF6" s="18" t="n"/>
       <c r="BG6" s="19">
-        <f>IF(BF6="","",IF(BF6="NE","",IF(BF6="0",0,IF(BF6="1",0.5,IF(BF6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BF6="","",IF(BF6="NE","",(IFERROR(IF(ISNUMBER(BF6),BF6,VALUE(BF6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BH6" s="20">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="BI6" s="18" t="n"/>
       <c r="BJ6" s="19">
-        <f>IF(BI6="","",IF(BI6="NE","",IF(BI6="0",0,IF(BI6="1",0.5,IF(BI6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BI6="","",IF(BI6="NE","",(IFERROR(IF(ISNUMBER(BI6),BI6,VALUE(BI6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BK6" s="20">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="BL6" s="18" t="n"/>
       <c r="BM6" s="19">
-        <f>IF(BL6="","",IF(BL6="NE","",IF(BL6="0",0,IF(BL6="1",0.5,IF(BL6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BL6="","",IF(BL6="NE","",(IFERROR(IF(ISNUMBER(BL6),BL6,VALUE(BL6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BN6" s="20">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="BO6" s="18" t="n"/>
       <c r="BP6" s="19">
-        <f>IF(BO6="","",IF(BO6="NE","",IF(BO6="0",0,IF(BO6="1",0.5,IF(BO6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BO6="","",IF(BO6="NE","",(IFERROR(IF(ISNUMBER(BO6),BO6,VALUE(BO6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BQ6" s="20">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="BR6" s="18" t="n"/>
       <c r="BS6" s="19">
-        <f>IF(BR6="","",IF(BR6="NE","",IF(BR6="0",0,IF(BR6="1",0.5,IF(BR6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BR6="","",IF(BR6="NE","",(IFERROR(IF(ISNUMBER(BR6),BR6,VALUE(BR6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BT6" s="20">
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BU6" s="18" t="n"/>
       <c r="BV6" s="19">
-        <f>IF(BU6="","",IF(BU6="NE","",IF(BU6="0",0,IF(BU6="1",0.5,IF(BU6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BU6="","",IF(BU6="NE","",(IFERROR(IF(ISNUMBER(BU6),BU6,VALUE(BU6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BW6" s="20">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="BX6" s="18" t="n"/>
       <c r="BY6" s="19">
-        <f>IF(BX6="","",IF(BX6="NE","",IF(BX6="0",0,IF(BX6="1",0.5,IF(BX6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(BX6="","",IF(BX6="NE","",(IFERROR(IF(ISNUMBER(BX6),BX6,VALUE(BX6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="BZ6" s="20">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="CA6" s="18" t="n"/>
       <c r="CB6" s="19">
-        <f>IF(CA6="","",IF(CA6="NE","",IF(CA6="0",0,IF(CA6="1",0.5,IF(CA6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(CA6="","",IF(CA6="NE","",(IFERROR(IF(ISNUMBER(CA6),CA6,VALUE(CA6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="CC6" s="20">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="CD6" s="18" t="n"/>
       <c r="CE6" s="19">
-        <f>IF(CD6="","",IF(CD6="NE","",IF(CD6="0",0,IF(CD6="1",0.5,IF(CD6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(CD6="","",IF(CD6="NE","",(IFERROR(IF(ISNUMBER(CD6),CD6,VALUE(CD6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="CF6" s="20">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="CG6" s="18" t="n"/>
       <c r="CH6" s="19">
-        <f>IF(CG6="","",IF(CG6="NE","",IF(CG6="0",0,IF(CG6="1",0.5,IF(CG6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(CG6="","",IF(CG6="NE","",(IFERROR(IF(ISNUMBER(CG6),CG6,VALUE(CG6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="CI6" s="20">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="CJ6" s="18" t="n"/>
       <c r="CK6" s="19">
-        <f>IF(CJ6="","",IF(CJ6="NE","",IF(CJ6="0",0,IF(CJ6="1",0.5,IF(CJ6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(CJ6="","",IF(CJ6="NE","",(IFERROR(IF(ISNUMBER(CJ6),CJ6,VALUE(CJ6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="CL6" s="20">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="CM6" s="18" t="n"/>
       <c r="CN6" s="19">
-        <f>IF(CM6="","",IF(CM6="NE","",IF(CM6="0",0,IF(CM6="1",0.5,IF(CM6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(CM6="","",IF(CM6="NE","",(IFERROR(IF(ISNUMBER(CM6),CM6,VALUE(CM6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="CO6" s="20">
@@ -2958,7 +2958,7 @@
       </c>
       <c r="CP6" s="18" t="n"/>
       <c r="CQ6" s="19">
-        <f>IF(CP6="","",IF(CP6="NE","",IF(CP6="0",0,IF(CP6="1",0.5,IF(CP6="2",1,0)))*$F6*$F$4*20))</f>
+        <f>IF(CP6="","",IF(CP6="NE","",(IFERROR(IF(ISNUMBER(CP6),CP6,VALUE(CP6)),0)/2)*$F6*$F$4*20))</f>
         <v/>
       </c>
       <c r="CR6" s="20">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="G7" s="18" t="n"/>
       <c r="H7" s="19">
-        <f>IF(G7="","",IF(G7="NE","",IF(G7="0",0,IF(G7="1",0.5,IF(G7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(G7="","",IF(G7="NE","",(IFERROR(IF(ISNUMBER(G7),G7,VALUE(G7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="I7" s="20">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J7" s="18" t="n"/>
       <c r="K7" s="19">
-        <f>IF(J7="","",IF(J7="NE","",IF(J7="0",0,IF(J7="1",0.5,IF(J7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(J7="","",IF(J7="NE","",(IFERROR(IF(ISNUMBER(J7),J7,VALUE(J7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="L7" s="20">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="M7" s="18" t="n"/>
       <c r="N7" s="19">
-        <f>IF(M7="","",IF(M7="NE","",IF(M7="0",0,IF(M7="1",0.5,IF(M7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(M7="","",IF(M7="NE","",(IFERROR(IF(ISNUMBER(M7),M7,VALUE(M7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="O7" s="20">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="P7" s="18" t="n"/>
       <c r="Q7" s="19">
-        <f>IF(P7="","",IF(P7="NE","",IF(P7="0",0,IF(P7="1",0.5,IF(P7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(P7="","",IF(P7="NE","",(IFERROR(IF(ISNUMBER(P7),P7,VALUE(P7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="R7" s="20">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S7" s="18" t="n"/>
       <c r="T7" s="19">
-        <f>IF(S7="","",IF(S7="NE","",IF(S7="0",0,IF(S7="1",0.5,IF(S7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(S7="","",IF(S7="NE","",(IFERROR(IF(ISNUMBER(S7),S7,VALUE(S7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="U7" s="20">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="V7" s="18" t="n"/>
       <c r="W7" s="19">
-        <f>IF(V7="","",IF(V7="NE","",IF(V7="0",0,IF(V7="1",0.5,IF(V7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(V7="","",IF(V7="NE","",(IFERROR(IF(ISNUMBER(V7),V7,VALUE(V7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="X7" s="20">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="Y7" s="18" t="n"/>
       <c r="Z7" s="19">
-        <f>IF(Y7="","",IF(Y7="NE","",IF(Y7="0",0,IF(Y7="1",0.5,IF(Y7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(Y7="","",IF(Y7="NE","",(IFERROR(IF(ISNUMBER(Y7),Y7,VALUE(Y7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AA7" s="20">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="AB7" s="18" t="n"/>
       <c r="AC7" s="19">
-        <f>IF(AB7="","",IF(AB7="NE","",IF(AB7="0",0,IF(AB7="1",0.5,IF(AB7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AB7="","",IF(AB7="NE","",(IFERROR(IF(ISNUMBER(AB7),AB7,VALUE(AB7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AD7" s="20">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="AE7" s="18" t="n"/>
       <c r="AF7" s="19">
-        <f>IF(AE7="","",IF(AE7="NE","",IF(AE7="0",0,IF(AE7="1",0.5,IF(AE7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AE7="","",IF(AE7="NE","",(IFERROR(IF(ISNUMBER(AE7),AE7,VALUE(AE7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AG7" s="20">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="AH7" s="18" t="n"/>
       <c r="AI7" s="19">
-        <f>IF(AH7="","",IF(AH7="NE","",IF(AH7="0",0,IF(AH7="1",0.5,IF(AH7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AH7="","",IF(AH7="NE","",(IFERROR(IF(ISNUMBER(AH7),AH7,VALUE(AH7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AJ7" s="20">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="AK7" s="18" t="n"/>
       <c r="AL7" s="19">
-        <f>IF(AK7="","",IF(AK7="NE","",IF(AK7="0",0,IF(AK7="1",0.5,IF(AK7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AK7="","",IF(AK7="NE","",(IFERROR(IF(ISNUMBER(AK7),AK7,VALUE(AK7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AM7" s="20">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AN7" s="18" t="n"/>
       <c r="AO7" s="19">
-        <f>IF(AN7="","",IF(AN7="NE","",IF(AN7="0",0,IF(AN7="1",0.5,IF(AN7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AN7="","",IF(AN7="NE","",(IFERROR(IF(ISNUMBER(AN7),AN7,VALUE(AN7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AP7" s="20">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AQ7" s="18" t="n"/>
       <c r="AR7" s="19">
-        <f>IF(AQ7="","",IF(AQ7="NE","",IF(AQ7="0",0,IF(AQ7="1",0.5,IF(AQ7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AQ7="","",IF(AQ7="NE","",(IFERROR(IF(ISNUMBER(AQ7),AQ7,VALUE(AQ7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AS7" s="20">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="AT7" s="18" t="n"/>
       <c r="AU7" s="19">
-        <f>IF(AT7="","",IF(AT7="NE","",IF(AT7="0",0,IF(AT7="1",0.5,IF(AT7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AT7="","",IF(AT7="NE","",(IFERROR(IF(ISNUMBER(AT7),AT7,VALUE(AT7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AV7" s="20">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="AW7" s="18" t="n"/>
       <c r="AX7" s="19">
-        <f>IF(AW7="","",IF(AW7="NE","",IF(AW7="0",0,IF(AW7="1",0.5,IF(AW7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AW7="","",IF(AW7="NE","",(IFERROR(IF(ISNUMBER(AW7),AW7,VALUE(AW7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="AY7" s="20">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="AZ7" s="18" t="n"/>
       <c r="BA7" s="19">
-        <f>IF(AZ7="","",IF(AZ7="NE","",IF(AZ7="0",0,IF(AZ7="1",0.5,IF(AZ7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(AZ7="","",IF(AZ7="NE","",(IFERROR(IF(ISNUMBER(AZ7),AZ7,VALUE(AZ7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BB7" s="20">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="BC7" s="18" t="n"/>
       <c r="BD7" s="19">
-        <f>IF(BC7="","",IF(BC7="NE","",IF(BC7="0",0,IF(BC7="1",0.5,IF(BC7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BC7="","",IF(BC7="NE","",(IFERROR(IF(ISNUMBER(BC7),BC7,VALUE(BC7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BE7" s="20">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="BF7" s="18" t="n"/>
       <c r="BG7" s="19">
-        <f>IF(BF7="","",IF(BF7="NE","",IF(BF7="0",0,IF(BF7="1",0.5,IF(BF7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BF7="","",IF(BF7="NE","",(IFERROR(IF(ISNUMBER(BF7),BF7,VALUE(BF7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BH7" s="20">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="BI7" s="18" t="n"/>
       <c r="BJ7" s="19">
-        <f>IF(BI7="","",IF(BI7="NE","",IF(BI7="0",0,IF(BI7="1",0.5,IF(BI7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BI7="","",IF(BI7="NE","",(IFERROR(IF(ISNUMBER(BI7),BI7,VALUE(BI7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BK7" s="20">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="BL7" s="18" t="n"/>
       <c r="BM7" s="19">
-        <f>IF(BL7="","",IF(BL7="NE","",IF(BL7="0",0,IF(BL7="1",0.5,IF(BL7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BL7="","",IF(BL7="NE","",(IFERROR(IF(ISNUMBER(BL7),BL7,VALUE(BL7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BN7" s="20">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="BO7" s="18" t="n"/>
       <c r="BP7" s="19">
-        <f>IF(BO7="","",IF(BO7="NE","",IF(BO7="0",0,IF(BO7="1",0.5,IF(BO7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BO7="","",IF(BO7="NE","",(IFERROR(IF(ISNUMBER(BO7),BO7,VALUE(BO7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BQ7" s="20">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="BR7" s="18" t="n"/>
       <c r="BS7" s="19">
-        <f>IF(BR7="","",IF(BR7="NE","",IF(BR7="0",0,IF(BR7="1",0.5,IF(BR7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BR7="","",IF(BR7="NE","",(IFERROR(IF(ISNUMBER(BR7),BR7,VALUE(BR7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BT7" s="20">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="BU7" s="18" t="n"/>
       <c r="BV7" s="19">
-        <f>IF(BU7="","",IF(BU7="NE","",IF(BU7="0",0,IF(BU7="1",0.5,IF(BU7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BU7="","",IF(BU7="NE","",(IFERROR(IF(ISNUMBER(BU7),BU7,VALUE(BU7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BW7" s="20">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="BX7" s="18" t="n"/>
       <c r="BY7" s="19">
-        <f>IF(BX7="","",IF(BX7="NE","",IF(BX7="0",0,IF(BX7="1",0.5,IF(BX7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(BX7="","",IF(BX7="NE","",(IFERROR(IF(ISNUMBER(BX7),BX7,VALUE(BX7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="BZ7" s="20">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="CA7" s="18" t="n"/>
       <c r="CB7" s="19">
-        <f>IF(CA7="","",IF(CA7="NE","",IF(CA7="0",0,IF(CA7="1",0.5,IF(CA7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(CA7="","",IF(CA7="NE","",(IFERROR(IF(ISNUMBER(CA7),CA7,VALUE(CA7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="CC7" s="20">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="CD7" s="18" t="n"/>
       <c r="CE7" s="19">
-        <f>IF(CD7="","",IF(CD7="NE","",IF(CD7="0",0,IF(CD7="1",0.5,IF(CD7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(CD7="","",IF(CD7="NE","",(IFERROR(IF(ISNUMBER(CD7),CD7,VALUE(CD7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="CF7" s="20">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="CG7" s="18" t="n"/>
       <c r="CH7" s="19">
-        <f>IF(CG7="","",IF(CG7="NE","",IF(CG7="0",0,IF(CG7="1",0.5,IF(CG7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(CG7="","",IF(CG7="NE","",(IFERROR(IF(ISNUMBER(CG7),CG7,VALUE(CG7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="CI7" s="20">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="CJ7" s="18" t="n"/>
       <c r="CK7" s="19">
-        <f>IF(CJ7="","",IF(CJ7="NE","",IF(CJ7="0",0,IF(CJ7="1",0.5,IF(CJ7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(CJ7="","",IF(CJ7="NE","",(IFERROR(IF(ISNUMBER(CJ7),CJ7,VALUE(CJ7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="CL7" s="20">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="CM7" s="18" t="n"/>
       <c r="CN7" s="19">
-        <f>IF(CM7="","",IF(CM7="NE","",IF(CM7="0",0,IF(CM7="1",0.5,IF(CM7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(CM7="","",IF(CM7="NE","",(IFERROR(IF(ISNUMBER(CM7),CM7,VALUE(CM7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="CO7" s="20">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="CP7" s="18" t="n"/>
       <c r="CQ7" s="19">
-        <f>IF(CP7="","",IF(CP7="NE","",IF(CP7="0",0,IF(CP7="1",0.5,IF(CP7="2",1,0)))*$F7*$F$4*20))</f>
+        <f>IF(CP7="","",IF(CP7="NE","",(IFERROR(IF(ISNUMBER(CP7),CP7,VALUE(CP7)),0)/2)*$F7*$F$4*20))</f>
         <v/>
       </c>
       <c r="CR7" s="20">
@@ -3293,7 +3293,7 @@
       </c>
       <c r="G8" s="18" t="n"/>
       <c r="H8" s="19">
-        <f>IF(G8="","",IF(G8="NE","",IF(G8="0",0,IF(G8="1",0.5,IF(G8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(G8="","",IF(G8="NE","",(IFERROR(IF(ISNUMBER(G8),G8,VALUE(G8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="I8" s="20">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="J8" s="18" t="n"/>
       <c r="K8" s="19">
-        <f>IF(J8="","",IF(J8="NE","",IF(J8="0",0,IF(J8="1",0.5,IF(J8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(J8="","",IF(J8="NE","",(IFERROR(IF(ISNUMBER(J8),J8,VALUE(J8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="L8" s="20">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="M8" s="18" t="n"/>
       <c r="N8" s="19">
-        <f>IF(M8="","",IF(M8="NE","",IF(M8="0",0,IF(M8="1",0.5,IF(M8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(M8="","",IF(M8="NE","",(IFERROR(IF(ISNUMBER(M8),M8,VALUE(M8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="O8" s="20">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="P8" s="18" t="n"/>
       <c r="Q8" s="19">
-        <f>IF(P8="","",IF(P8="NE","",IF(P8="0",0,IF(P8="1",0.5,IF(P8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(P8="","",IF(P8="NE","",(IFERROR(IF(ISNUMBER(P8),P8,VALUE(P8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="R8" s="20">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="S8" s="18" t="n"/>
       <c r="T8" s="19">
-        <f>IF(S8="","",IF(S8="NE","",IF(S8="0",0,IF(S8="1",0.5,IF(S8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(S8="","",IF(S8="NE","",(IFERROR(IF(ISNUMBER(S8),S8,VALUE(S8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="U8" s="20">
@@ -3338,7 +3338,7 @@
       </c>
       <c r="V8" s="18" t="n"/>
       <c r="W8" s="19">
-        <f>IF(V8="","",IF(V8="NE","",IF(V8="0",0,IF(V8="1",0.5,IF(V8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(V8="","",IF(V8="NE","",(IFERROR(IF(ISNUMBER(V8),V8,VALUE(V8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="X8" s="20">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="Y8" s="18" t="n"/>
       <c r="Z8" s="19">
-        <f>IF(Y8="","",IF(Y8="NE","",IF(Y8="0",0,IF(Y8="1",0.5,IF(Y8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(Y8="","",IF(Y8="NE","",(IFERROR(IF(ISNUMBER(Y8),Y8,VALUE(Y8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AA8" s="20">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="AB8" s="18" t="n"/>
       <c r="AC8" s="19">
-        <f>IF(AB8="","",IF(AB8="NE","",IF(AB8="0",0,IF(AB8="1",0.5,IF(AB8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AB8="","",IF(AB8="NE","",(IFERROR(IF(ISNUMBER(AB8),AB8,VALUE(AB8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AD8" s="20">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="AE8" s="18" t="n"/>
       <c r="AF8" s="19">
-        <f>IF(AE8="","",IF(AE8="NE","",IF(AE8="0",0,IF(AE8="1",0.5,IF(AE8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AE8="","",IF(AE8="NE","",(IFERROR(IF(ISNUMBER(AE8),AE8,VALUE(AE8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AG8" s="20">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="AH8" s="18" t="n"/>
       <c r="AI8" s="19">
-        <f>IF(AH8="","",IF(AH8="NE","",IF(AH8="0",0,IF(AH8="1",0.5,IF(AH8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AH8="","",IF(AH8="NE","",(IFERROR(IF(ISNUMBER(AH8),AH8,VALUE(AH8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AJ8" s="20">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="AK8" s="18" t="n"/>
       <c r="AL8" s="19">
-        <f>IF(AK8="","",IF(AK8="NE","",IF(AK8="0",0,IF(AK8="1",0.5,IF(AK8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AK8="","",IF(AK8="NE","",(IFERROR(IF(ISNUMBER(AK8),AK8,VALUE(AK8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AM8" s="20">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="AN8" s="18" t="n"/>
       <c r="AO8" s="19">
-        <f>IF(AN8="","",IF(AN8="NE","",IF(AN8="0",0,IF(AN8="1",0.5,IF(AN8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AN8="","",IF(AN8="NE","",(IFERROR(IF(ISNUMBER(AN8),AN8,VALUE(AN8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AP8" s="20">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="AQ8" s="18" t="n"/>
       <c r="AR8" s="19">
-        <f>IF(AQ8="","",IF(AQ8="NE","",IF(AQ8="0",0,IF(AQ8="1",0.5,IF(AQ8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AQ8="","",IF(AQ8="NE","",(IFERROR(IF(ISNUMBER(AQ8),AQ8,VALUE(AQ8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AS8" s="20">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="AT8" s="18" t="n"/>
       <c r="AU8" s="19">
-        <f>IF(AT8="","",IF(AT8="NE","",IF(AT8="0",0,IF(AT8="1",0.5,IF(AT8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AT8="","",IF(AT8="NE","",(IFERROR(IF(ISNUMBER(AT8),AT8,VALUE(AT8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AV8" s="20">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="AW8" s="18" t="n"/>
       <c r="AX8" s="19">
-        <f>IF(AW8="","",IF(AW8="NE","",IF(AW8="0",0,IF(AW8="1",0.5,IF(AW8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AW8="","",IF(AW8="NE","",(IFERROR(IF(ISNUMBER(AW8),AW8,VALUE(AW8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="AY8" s="20">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="AZ8" s="18" t="n"/>
       <c r="BA8" s="19">
-        <f>IF(AZ8="","",IF(AZ8="NE","",IF(AZ8="0",0,IF(AZ8="1",0.5,IF(AZ8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(AZ8="","",IF(AZ8="NE","",(IFERROR(IF(ISNUMBER(AZ8),AZ8,VALUE(AZ8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BB8" s="20">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="BC8" s="18" t="n"/>
       <c r="BD8" s="19">
-        <f>IF(BC8="","",IF(BC8="NE","",IF(BC8="0",0,IF(BC8="1",0.5,IF(BC8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BC8="","",IF(BC8="NE","",(IFERROR(IF(ISNUMBER(BC8),BC8,VALUE(BC8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BE8" s="20">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="BF8" s="18" t="n"/>
       <c r="BG8" s="19">
-        <f>IF(BF8="","",IF(BF8="NE","",IF(BF8="0",0,IF(BF8="1",0.5,IF(BF8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BF8="","",IF(BF8="NE","",(IFERROR(IF(ISNUMBER(BF8),BF8,VALUE(BF8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BH8" s="20">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="BI8" s="18" t="n"/>
       <c r="BJ8" s="19">
-        <f>IF(BI8="","",IF(BI8="NE","",IF(BI8="0",0,IF(BI8="1",0.5,IF(BI8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BI8="","",IF(BI8="NE","",(IFERROR(IF(ISNUMBER(BI8),BI8,VALUE(BI8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BK8" s="20">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="BL8" s="18" t="n"/>
       <c r="BM8" s="19">
-        <f>IF(BL8="","",IF(BL8="NE","",IF(BL8="0",0,IF(BL8="1",0.5,IF(BL8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BL8="","",IF(BL8="NE","",(IFERROR(IF(ISNUMBER(BL8),BL8,VALUE(BL8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BN8" s="20">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="BO8" s="18" t="n"/>
       <c r="BP8" s="19">
-        <f>IF(BO8="","",IF(BO8="NE","",IF(BO8="0",0,IF(BO8="1",0.5,IF(BO8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BO8="","",IF(BO8="NE","",(IFERROR(IF(ISNUMBER(BO8),BO8,VALUE(BO8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BQ8" s="20">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="BR8" s="18" t="n"/>
       <c r="BS8" s="19">
-        <f>IF(BR8="","",IF(BR8="NE","",IF(BR8="0",0,IF(BR8="1",0.5,IF(BR8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BR8="","",IF(BR8="NE","",(IFERROR(IF(ISNUMBER(BR8),BR8,VALUE(BR8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BT8" s="20">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="BU8" s="18" t="n"/>
       <c r="BV8" s="19">
-        <f>IF(BU8="","",IF(BU8="NE","",IF(BU8="0",0,IF(BU8="1",0.5,IF(BU8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BU8="","",IF(BU8="NE","",(IFERROR(IF(ISNUMBER(BU8),BU8,VALUE(BU8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BW8" s="20">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="BX8" s="18" t="n"/>
       <c r="BY8" s="19">
-        <f>IF(BX8="","",IF(BX8="NE","",IF(BX8="0",0,IF(BX8="1",0.5,IF(BX8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(BX8="","",IF(BX8="NE","",(IFERROR(IF(ISNUMBER(BX8),BX8,VALUE(BX8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="BZ8" s="20">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="CA8" s="18" t="n"/>
       <c r="CB8" s="19">
-        <f>IF(CA8="","",IF(CA8="NE","",IF(CA8="0",0,IF(CA8="1",0.5,IF(CA8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(CA8="","",IF(CA8="NE","",(IFERROR(IF(ISNUMBER(CA8),CA8,VALUE(CA8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="CC8" s="20">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="CD8" s="18" t="n"/>
       <c r="CE8" s="19">
-        <f>IF(CD8="","",IF(CD8="NE","",IF(CD8="0",0,IF(CD8="1",0.5,IF(CD8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(CD8="","",IF(CD8="NE","",(IFERROR(IF(ISNUMBER(CD8),CD8,VALUE(CD8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="CF8" s="20">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="CG8" s="18" t="n"/>
       <c r="CH8" s="19">
-        <f>IF(CG8="","",IF(CG8="NE","",IF(CG8="0",0,IF(CG8="1",0.5,IF(CG8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(CG8="","",IF(CG8="NE","",(IFERROR(IF(ISNUMBER(CG8),CG8,VALUE(CG8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="CI8" s="20">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="CJ8" s="18" t="n"/>
       <c r="CK8" s="19">
-        <f>IF(CJ8="","",IF(CJ8="NE","",IF(CJ8="0",0,IF(CJ8="1",0.5,IF(CJ8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(CJ8="","",IF(CJ8="NE","",(IFERROR(IF(ISNUMBER(CJ8),CJ8,VALUE(CJ8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="CL8" s="20">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="CM8" s="18" t="n"/>
       <c r="CN8" s="19">
-        <f>IF(CM8="","",IF(CM8="NE","",IF(CM8="0",0,IF(CM8="1",0.5,IF(CM8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(CM8="","",IF(CM8="NE","",(IFERROR(IF(ISNUMBER(CM8),CM8,VALUE(CM8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="CO8" s="20">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="CP8" s="18" t="n"/>
       <c r="CQ8" s="19">
-        <f>IF(CP8="","",IF(CP8="NE","",IF(CP8="0",0,IF(CP8="1",0.5,IF(CP8="2",1,0)))*$F8*$F$4*20))</f>
+        <f>IF(CP8="","",IF(CP8="NE","",(IFERROR(IF(ISNUMBER(CP8),CP8,VALUE(CP8)),0)/2)*$F8*$F$4*20))</f>
         <v/>
       </c>
       <c r="CR8" s="20">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="G9" s="18" t="n"/>
       <c r="H9" s="19">
-        <f>IF(G9="","",IF(G9="NE","",IF(G9="0",0,IF(G9="1",0.5,IF(G9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(G9="","",IF(G9="NE","",(IFERROR(IF(ISNUMBER(G9),G9,VALUE(G9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="I9" s="20">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="J9" s="18" t="n"/>
       <c r="K9" s="19">
-        <f>IF(J9="","",IF(J9="NE","",IF(J9="0",0,IF(J9="1",0.5,IF(J9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(J9="","",IF(J9="NE","",(IFERROR(IF(ISNUMBER(J9),J9,VALUE(J9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="L9" s="20">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="M9" s="18" t="n"/>
       <c r="N9" s="19">
-        <f>IF(M9="","",IF(M9="NE","",IF(M9="0",0,IF(M9="1",0.5,IF(M9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(M9="","",IF(M9="NE","",(IFERROR(IF(ISNUMBER(M9),M9,VALUE(M9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="O9" s="20">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P9" s="18" t="n"/>
       <c r="Q9" s="19">
-        <f>IF(P9="","",IF(P9="NE","",IF(P9="0",0,IF(P9="1",0.5,IF(P9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(P9="","",IF(P9="NE","",(IFERROR(IF(ISNUMBER(P9),P9,VALUE(P9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="R9" s="20">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="S9" s="18" t="n"/>
       <c r="T9" s="19">
-        <f>IF(S9="","",IF(S9="NE","",IF(S9="0",0,IF(S9="1",0.5,IF(S9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(S9="","",IF(S9="NE","",(IFERROR(IF(ISNUMBER(S9),S9,VALUE(S9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="U9" s="20">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="V9" s="18" t="n"/>
       <c r="W9" s="19">
-        <f>IF(V9="","",IF(V9="NE","",IF(V9="0",0,IF(V9="1",0.5,IF(V9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(V9="","",IF(V9="NE","",(IFERROR(IF(ISNUMBER(V9),V9,VALUE(V9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="X9" s="20">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="Y9" s="18" t="n"/>
       <c r="Z9" s="19">
-        <f>IF(Y9="","",IF(Y9="NE","",IF(Y9="0",0,IF(Y9="1",0.5,IF(Y9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(Y9="","",IF(Y9="NE","",(IFERROR(IF(ISNUMBER(Y9),Y9,VALUE(Y9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AA9" s="20">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AB9" s="18" t="n"/>
       <c r="AC9" s="19">
-        <f>IF(AB9="","",IF(AB9="NE","",IF(AB9="0",0,IF(AB9="1",0.5,IF(AB9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AB9="","",IF(AB9="NE","",(IFERROR(IF(ISNUMBER(AB9),AB9,VALUE(AB9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AD9" s="20">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="AE9" s="18" t="n"/>
       <c r="AF9" s="19">
-        <f>IF(AE9="","",IF(AE9="NE","",IF(AE9="0",0,IF(AE9="1",0.5,IF(AE9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AE9="","",IF(AE9="NE","",(IFERROR(IF(ISNUMBER(AE9),AE9,VALUE(AE9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AG9" s="20">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="AH9" s="18" t="n"/>
       <c r="AI9" s="19">
-        <f>IF(AH9="","",IF(AH9="NE","",IF(AH9="0",0,IF(AH9="1",0.5,IF(AH9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AH9="","",IF(AH9="NE","",(IFERROR(IF(ISNUMBER(AH9),AH9,VALUE(AH9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AJ9" s="20">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="AK9" s="18" t="n"/>
       <c r="AL9" s="19">
-        <f>IF(AK9="","",IF(AK9="NE","",IF(AK9="0",0,IF(AK9="1",0.5,IF(AK9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AK9="","",IF(AK9="NE","",(IFERROR(IF(ISNUMBER(AK9),AK9,VALUE(AK9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AM9" s="20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="AN9" s="18" t="n"/>
       <c r="AO9" s="19">
-        <f>IF(AN9="","",IF(AN9="NE","",IF(AN9="0",0,IF(AN9="1",0.5,IF(AN9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AN9="","",IF(AN9="NE","",(IFERROR(IF(ISNUMBER(AN9),AN9,VALUE(AN9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AP9" s="20">
@@ -3699,7 +3699,7 @@
       </c>
       <c r="AQ9" s="18" t="n"/>
       <c r="AR9" s="19">
-        <f>IF(AQ9="","",IF(AQ9="NE","",IF(AQ9="0",0,IF(AQ9="1",0.5,IF(AQ9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AQ9="","",IF(AQ9="NE","",(IFERROR(IF(ISNUMBER(AQ9),AQ9,VALUE(AQ9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AS9" s="20">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="AT9" s="18" t="n"/>
       <c r="AU9" s="19">
-        <f>IF(AT9="","",IF(AT9="NE","",IF(AT9="0",0,IF(AT9="1",0.5,IF(AT9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AT9="","",IF(AT9="NE","",(IFERROR(IF(ISNUMBER(AT9),AT9,VALUE(AT9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AV9" s="20">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="AW9" s="18" t="n"/>
       <c r="AX9" s="19">
-        <f>IF(AW9="","",IF(AW9="NE","",IF(AW9="0",0,IF(AW9="1",0.5,IF(AW9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AW9="","",IF(AW9="NE","",(IFERROR(IF(ISNUMBER(AW9),AW9,VALUE(AW9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="AY9" s="20">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="AZ9" s="18" t="n"/>
       <c r="BA9" s="19">
-        <f>IF(AZ9="","",IF(AZ9="NE","",IF(AZ9="0",0,IF(AZ9="1",0.5,IF(AZ9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(AZ9="","",IF(AZ9="NE","",(IFERROR(IF(ISNUMBER(AZ9),AZ9,VALUE(AZ9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BB9" s="20">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="BC9" s="18" t="n"/>
       <c r="BD9" s="19">
-        <f>IF(BC9="","",IF(BC9="NE","",IF(BC9="0",0,IF(BC9="1",0.5,IF(BC9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BC9="","",IF(BC9="NE","",(IFERROR(IF(ISNUMBER(BC9),BC9,VALUE(BC9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BE9" s="20">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BF9" s="18" t="n"/>
       <c r="BG9" s="19">
-        <f>IF(BF9="","",IF(BF9="NE","",IF(BF9="0",0,IF(BF9="1",0.5,IF(BF9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BF9="","",IF(BF9="NE","",(IFERROR(IF(ISNUMBER(BF9),BF9,VALUE(BF9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BH9" s="20">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="BI9" s="18" t="n"/>
       <c r="BJ9" s="19">
-        <f>IF(BI9="","",IF(BI9="NE","",IF(BI9="0",0,IF(BI9="1",0.5,IF(BI9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BI9="","",IF(BI9="NE","",(IFERROR(IF(ISNUMBER(BI9),BI9,VALUE(BI9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BK9" s="20">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="BL9" s="18" t="n"/>
       <c r="BM9" s="19">
-        <f>IF(BL9="","",IF(BL9="NE","",IF(BL9="0",0,IF(BL9="1",0.5,IF(BL9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BL9="","",IF(BL9="NE","",(IFERROR(IF(ISNUMBER(BL9),BL9,VALUE(BL9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BN9" s="20">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="BO9" s="18" t="n"/>
       <c r="BP9" s="19">
-        <f>IF(BO9="","",IF(BO9="NE","",IF(BO9="0",0,IF(BO9="1",0.5,IF(BO9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BO9="","",IF(BO9="NE","",(IFERROR(IF(ISNUMBER(BO9),BO9,VALUE(BO9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BQ9" s="20">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="BR9" s="18" t="n"/>
       <c r="BS9" s="19">
-        <f>IF(BR9="","",IF(BR9="NE","",IF(BR9="0",0,IF(BR9="1",0.5,IF(BR9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BR9="","",IF(BR9="NE","",(IFERROR(IF(ISNUMBER(BR9),BR9,VALUE(BR9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BT9" s="20">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="BU9" s="18" t="n"/>
       <c r="BV9" s="19">
-        <f>IF(BU9="","",IF(BU9="NE","",IF(BU9="0",0,IF(BU9="1",0.5,IF(BU9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BU9="","",IF(BU9="NE","",(IFERROR(IF(ISNUMBER(BU9),BU9,VALUE(BU9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BW9" s="20">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="BX9" s="18" t="n"/>
       <c r="BY9" s="19">
-        <f>IF(BX9="","",IF(BX9="NE","",IF(BX9="0",0,IF(BX9="1",0.5,IF(BX9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(BX9="","",IF(BX9="NE","",(IFERROR(IF(ISNUMBER(BX9),BX9,VALUE(BX9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="BZ9" s="20">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="CA9" s="18" t="n"/>
       <c r="CB9" s="19">
-        <f>IF(CA9="","",IF(CA9="NE","",IF(CA9="0",0,IF(CA9="1",0.5,IF(CA9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(CA9="","",IF(CA9="NE","",(IFERROR(IF(ISNUMBER(CA9),CA9,VALUE(CA9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="CC9" s="20">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="CD9" s="18" t="n"/>
       <c r="CE9" s="19">
-        <f>IF(CD9="","",IF(CD9="NE","",IF(CD9="0",0,IF(CD9="1",0.5,IF(CD9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(CD9="","",IF(CD9="NE","",(IFERROR(IF(ISNUMBER(CD9),CD9,VALUE(CD9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="CF9" s="20">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="CG9" s="18" t="n"/>
       <c r="CH9" s="19">
-        <f>IF(CG9="","",IF(CG9="NE","",IF(CG9="0",0,IF(CG9="1",0.5,IF(CG9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(CG9="","",IF(CG9="NE","",(IFERROR(IF(ISNUMBER(CG9),CG9,VALUE(CG9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="CI9" s="20">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="CJ9" s="18" t="n"/>
       <c r="CK9" s="19">
-        <f>IF(CJ9="","",IF(CJ9="NE","",IF(CJ9="0",0,IF(CJ9="1",0.5,IF(CJ9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(CJ9="","",IF(CJ9="NE","",(IFERROR(IF(ISNUMBER(CJ9),CJ9,VALUE(CJ9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="CL9" s="20">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="CM9" s="18" t="n"/>
       <c r="CN9" s="19">
-        <f>IF(CM9="","",IF(CM9="NE","",IF(CM9="0",0,IF(CM9="1",0.5,IF(CM9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(CM9="","",IF(CM9="NE","",(IFERROR(IF(ISNUMBER(CM9),CM9,VALUE(CM9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="CO9" s="20">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="CP9" s="18" t="n"/>
       <c r="CQ9" s="19">
-        <f>IF(CP9="","",IF(CP9="NE","",IF(CP9="0",0,IF(CP9="1",0.5,IF(CP9="2",1,0)))*$F9*$F$4*20))</f>
+        <f>IF(CP9="","",IF(CP9="NE","",(IFERROR(IF(ISNUMBER(CP9),CP9,VALUE(CP9)),0)/2)*$F9*$F$4*20))</f>
         <v/>
       </c>
       <c r="CR9" s="20">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="G10" s="18" t="n"/>
       <c r="H10" s="19">
-        <f>IF(G10="","",IF(G10="NE","",IF(G10="0",0,IF(G10="1",0.5,IF(G10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(G10="","",IF(G10="NE","",(IFERROR(IF(ISNUMBER(G10),G10,VALUE(G10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="I10" s="20">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="J10" s="18" t="n"/>
       <c r="K10" s="19">
-        <f>IF(J10="","",IF(J10="NE","",IF(J10="0",0,IF(J10="1",0.5,IF(J10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(J10="","",IF(J10="NE","",(IFERROR(IF(ISNUMBER(J10),J10,VALUE(J10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="L10" s="20">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="M10" s="18" t="n"/>
       <c r="N10" s="19">
-        <f>IF(M10="","",IF(M10="NE","",IF(M10="0",0,IF(M10="1",0.5,IF(M10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(M10="","",IF(M10="NE","",(IFERROR(IF(ISNUMBER(M10),M10,VALUE(M10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="O10" s="20">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="P10" s="18" t="n"/>
       <c r="Q10" s="19">
-        <f>IF(P10="","",IF(P10="NE","",IF(P10="0",0,IF(P10="1",0.5,IF(P10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(P10="","",IF(P10="NE","",(IFERROR(IF(ISNUMBER(P10),P10,VALUE(P10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="R10" s="20">
@@ -3925,7 +3925,7 @@
       </c>
       <c r="S10" s="18" t="n"/>
       <c r="T10" s="19">
-        <f>IF(S10="","",IF(S10="NE","",IF(S10="0",0,IF(S10="1",0.5,IF(S10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(S10="","",IF(S10="NE","",(IFERROR(IF(ISNUMBER(S10),S10,VALUE(S10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="U10" s="20">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="V10" s="18" t="n"/>
       <c r="W10" s="19">
-        <f>IF(V10="","",IF(V10="NE","",IF(V10="0",0,IF(V10="1",0.5,IF(V10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(V10="","",IF(V10="NE","",(IFERROR(IF(ISNUMBER(V10),V10,VALUE(V10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="X10" s="20">
@@ -3943,7 +3943,7 @@
       </c>
       <c r="Y10" s="18" t="n"/>
       <c r="Z10" s="19">
-        <f>IF(Y10="","",IF(Y10="NE","",IF(Y10="0",0,IF(Y10="1",0.5,IF(Y10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(Y10="","",IF(Y10="NE","",(IFERROR(IF(ISNUMBER(Y10),Y10,VALUE(Y10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AA10" s="20">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="AB10" s="18" t="n"/>
       <c r="AC10" s="19">
-        <f>IF(AB10="","",IF(AB10="NE","",IF(AB10="0",0,IF(AB10="1",0.5,IF(AB10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AB10="","",IF(AB10="NE","",(IFERROR(IF(ISNUMBER(AB10),AB10,VALUE(AB10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AD10" s="20">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="AE10" s="18" t="n"/>
       <c r="AF10" s="19">
-        <f>IF(AE10="","",IF(AE10="NE","",IF(AE10="0",0,IF(AE10="1",0.5,IF(AE10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AE10="","",IF(AE10="NE","",(IFERROR(IF(ISNUMBER(AE10),AE10,VALUE(AE10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AG10" s="20">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AH10" s="18" t="n"/>
       <c r="AI10" s="19">
-        <f>IF(AH10="","",IF(AH10="NE","",IF(AH10="0",0,IF(AH10="1",0.5,IF(AH10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AH10="","",IF(AH10="NE","",(IFERROR(IF(ISNUMBER(AH10),AH10,VALUE(AH10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AJ10" s="20">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AK10" s="18" t="n"/>
       <c r="AL10" s="19">
-        <f>IF(AK10="","",IF(AK10="NE","",IF(AK10="0",0,IF(AK10="1",0.5,IF(AK10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AK10="","",IF(AK10="NE","",(IFERROR(IF(ISNUMBER(AK10),AK10,VALUE(AK10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AM10" s="20">
@@ -3988,7 +3988,7 @@
       </c>
       <c r="AN10" s="18" t="n"/>
       <c r="AO10" s="19">
-        <f>IF(AN10="","",IF(AN10="NE","",IF(AN10="0",0,IF(AN10="1",0.5,IF(AN10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AN10="","",IF(AN10="NE","",(IFERROR(IF(ISNUMBER(AN10),AN10,VALUE(AN10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AP10" s="20">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="AQ10" s="18" t="n"/>
       <c r="AR10" s="19">
-        <f>IF(AQ10="","",IF(AQ10="NE","",IF(AQ10="0",0,IF(AQ10="1",0.5,IF(AQ10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AQ10="","",IF(AQ10="NE","",(IFERROR(IF(ISNUMBER(AQ10),AQ10,VALUE(AQ10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AS10" s="20">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="AT10" s="18" t="n"/>
       <c r="AU10" s="19">
-        <f>IF(AT10="","",IF(AT10="NE","",IF(AT10="0",0,IF(AT10="1",0.5,IF(AT10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AT10="","",IF(AT10="NE","",(IFERROR(IF(ISNUMBER(AT10),AT10,VALUE(AT10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AV10" s="20">
@@ -4015,7 +4015,7 @@
       </c>
       <c r="AW10" s="18" t="n"/>
       <c r="AX10" s="19">
-        <f>IF(AW10="","",IF(AW10="NE","",IF(AW10="0",0,IF(AW10="1",0.5,IF(AW10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AW10="","",IF(AW10="NE","",(IFERROR(IF(ISNUMBER(AW10),AW10,VALUE(AW10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="AY10" s="20">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="AZ10" s="18" t="n"/>
       <c r="BA10" s="19">
-        <f>IF(AZ10="","",IF(AZ10="NE","",IF(AZ10="0",0,IF(AZ10="1",0.5,IF(AZ10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(AZ10="","",IF(AZ10="NE","",(IFERROR(IF(ISNUMBER(AZ10),AZ10,VALUE(AZ10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BB10" s="20">
@@ -4033,7 +4033,7 @@
       </c>
       <c r="BC10" s="18" t="n"/>
       <c r="BD10" s="19">
-        <f>IF(BC10="","",IF(BC10="NE","",IF(BC10="0",0,IF(BC10="1",0.5,IF(BC10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BC10="","",IF(BC10="NE","",(IFERROR(IF(ISNUMBER(BC10),BC10,VALUE(BC10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BE10" s="20">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="BF10" s="18" t="n"/>
       <c r="BG10" s="19">
-        <f>IF(BF10="","",IF(BF10="NE","",IF(BF10="0",0,IF(BF10="1",0.5,IF(BF10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BF10="","",IF(BF10="NE","",(IFERROR(IF(ISNUMBER(BF10),BF10,VALUE(BF10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BH10" s="20">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="BI10" s="18" t="n"/>
       <c r="BJ10" s="19">
-        <f>IF(BI10="","",IF(BI10="NE","",IF(BI10="0",0,IF(BI10="1",0.5,IF(BI10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BI10="","",IF(BI10="NE","",(IFERROR(IF(ISNUMBER(BI10),BI10,VALUE(BI10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BK10" s="20">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="BL10" s="18" t="n"/>
       <c r="BM10" s="19">
-        <f>IF(BL10="","",IF(BL10="NE","",IF(BL10="0",0,IF(BL10="1",0.5,IF(BL10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BL10="","",IF(BL10="NE","",(IFERROR(IF(ISNUMBER(BL10),BL10,VALUE(BL10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BN10" s="20">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="BO10" s="18" t="n"/>
       <c r="BP10" s="19">
-        <f>IF(BO10="","",IF(BO10="NE","",IF(BO10="0",0,IF(BO10="1",0.5,IF(BO10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BO10="","",IF(BO10="NE","",(IFERROR(IF(ISNUMBER(BO10),BO10,VALUE(BO10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BQ10" s="20">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="BR10" s="18" t="n"/>
       <c r="BS10" s="19">
-        <f>IF(BR10="","",IF(BR10="NE","",IF(BR10="0",0,IF(BR10="1",0.5,IF(BR10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BR10="","",IF(BR10="NE","",(IFERROR(IF(ISNUMBER(BR10),BR10,VALUE(BR10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BT10" s="20">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="BU10" s="18" t="n"/>
       <c r="BV10" s="19">
-        <f>IF(BU10="","",IF(BU10="NE","",IF(BU10="0",0,IF(BU10="1",0.5,IF(BU10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BU10="","",IF(BU10="NE","",(IFERROR(IF(ISNUMBER(BU10),BU10,VALUE(BU10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BW10" s="20">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="BX10" s="18" t="n"/>
       <c r="BY10" s="19">
-        <f>IF(BX10="","",IF(BX10="NE","",IF(BX10="0",0,IF(BX10="1",0.5,IF(BX10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(BX10="","",IF(BX10="NE","",(IFERROR(IF(ISNUMBER(BX10),BX10,VALUE(BX10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="BZ10" s="20">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="CA10" s="18" t="n"/>
       <c r="CB10" s="19">
-        <f>IF(CA10="","",IF(CA10="NE","",IF(CA10="0",0,IF(CA10="1",0.5,IF(CA10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(CA10="","",IF(CA10="NE","",(IFERROR(IF(ISNUMBER(CA10),CA10,VALUE(CA10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="CC10" s="20">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="CD10" s="18" t="n"/>
       <c r="CE10" s="19">
-        <f>IF(CD10="","",IF(CD10="NE","",IF(CD10="0",0,IF(CD10="1",0.5,IF(CD10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(CD10="","",IF(CD10="NE","",(IFERROR(IF(ISNUMBER(CD10),CD10,VALUE(CD10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="CF10" s="20">
@@ -4123,7 +4123,7 @@
       </c>
       <c r="CG10" s="18" t="n"/>
       <c r="CH10" s="19">
-        <f>IF(CG10="","",IF(CG10="NE","",IF(CG10="0",0,IF(CG10="1",0.5,IF(CG10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(CG10="","",IF(CG10="NE","",(IFERROR(IF(ISNUMBER(CG10),CG10,VALUE(CG10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="CI10" s="20">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="CJ10" s="18" t="n"/>
       <c r="CK10" s="19">
-        <f>IF(CJ10="","",IF(CJ10="NE","",IF(CJ10="0",0,IF(CJ10="1",0.5,IF(CJ10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(CJ10="","",IF(CJ10="NE","",(IFERROR(IF(ISNUMBER(CJ10),CJ10,VALUE(CJ10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="CL10" s="20">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="CM10" s="18" t="n"/>
       <c r="CN10" s="19">
-        <f>IF(CM10="","",IF(CM10="NE","",IF(CM10="0",0,IF(CM10="1",0.5,IF(CM10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(CM10="","",IF(CM10="NE","",(IFERROR(IF(ISNUMBER(CM10),CM10,VALUE(CM10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="CO10" s="20">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="CP10" s="18" t="n"/>
       <c r="CQ10" s="19">
-        <f>IF(CP10="","",IF(CP10="NE","",IF(CP10="0",0,IF(CP10="1",0.5,IF(CP10="2",1,0)))*$F10*$F$4*20))</f>
+        <f>IF(CP10="","",IF(CP10="NE","",(IFERROR(IF(ISNUMBER(CP10),CP10,VALUE(CP10)),0)/2)*$F10*$F$4*20))</f>
         <v/>
       </c>
       <c r="CR10" s="20">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G11" s="18" t="n"/>
       <c r="H11" s="19">
-        <f>IF(G11="","",IF(G11="NE","",IF(G11="0",0,IF(G11="1",0.5,IF(G11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(G11="","",IF(G11="NE","",(IFERROR(IF(ISNUMBER(G11),G11,VALUE(G11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="I11" s="20">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="J11" s="18" t="n"/>
       <c r="K11" s="19">
-        <f>IF(J11="","",IF(J11="NE","",IF(J11="0",0,IF(J11="1",0.5,IF(J11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(J11="","",IF(J11="NE","",(IFERROR(IF(ISNUMBER(J11),J11,VALUE(J11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="L11" s="20">
@@ -4205,7 +4205,7 @@
       </c>
       <c r="M11" s="18" t="n"/>
       <c r="N11" s="19">
-        <f>IF(M11="","",IF(M11="NE","",IF(M11="0",0,IF(M11="1",0.5,IF(M11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(M11="","",IF(M11="NE","",(IFERROR(IF(ISNUMBER(M11),M11,VALUE(M11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="O11" s="20">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="P11" s="18" t="n"/>
       <c r="Q11" s="19">
-        <f>IF(P11="","",IF(P11="NE","",IF(P11="0",0,IF(P11="1",0.5,IF(P11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(P11="","",IF(P11="NE","",(IFERROR(IF(ISNUMBER(P11),P11,VALUE(P11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="R11" s="20">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="S11" s="18" t="n"/>
       <c r="T11" s="19">
-        <f>IF(S11="","",IF(S11="NE","",IF(S11="0",0,IF(S11="1",0.5,IF(S11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(S11="","",IF(S11="NE","",(IFERROR(IF(ISNUMBER(S11),S11,VALUE(S11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="U11" s="20">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="V11" s="18" t="n"/>
       <c r="W11" s="19">
-        <f>IF(V11="","",IF(V11="NE","",IF(V11="0",0,IF(V11="1",0.5,IF(V11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(V11="","",IF(V11="NE","",(IFERROR(IF(ISNUMBER(V11),V11,VALUE(V11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="X11" s="20">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="Y11" s="18" t="n"/>
       <c r="Z11" s="19">
-        <f>IF(Y11="","",IF(Y11="NE","",IF(Y11="0",0,IF(Y11="1",0.5,IF(Y11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(Y11="","",IF(Y11="NE","",(IFERROR(IF(ISNUMBER(Y11),Y11,VALUE(Y11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AA11" s="20">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="AB11" s="18" t="n"/>
       <c r="AC11" s="19">
-        <f>IF(AB11="","",IF(AB11="NE","",IF(AB11="0",0,IF(AB11="1",0.5,IF(AB11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AB11="","",IF(AB11="NE","",(IFERROR(IF(ISNUMBER(AB11),AB11,VALUE(AB11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AD11" s="20">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="AE11" s="18" t="n"/>
       <c r="AF11" s="19">
-        <f>IF(AE11="","",IF(AE11="NE","",IF(AE11="0",0,IF(AE11="1",0.5,IF(AE11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AE11="","",IF(AE11="NE","",(IFERROR(IF(ISNUMBER(AE11),AE11,VALUE(AE11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AG11" s="20">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AH11" s="18" t="n"/>
       <c r="AI11" s="19">
-        <f>IF(AH11="","",IF(AH11="NE","",IF(AH11="0",0,IF(AH11="1",0.5,IF(AH11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AH11="","",IF(AH11="NE","",(IFERROR(IF(ISNUMBER(AH11),AH11,VALUE(AH11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AJ11" s="20">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AK11" s="18" t="n"/>
       <c r="AL11" s="19">
-        <f>IF(AK11="","",IF(AK11="NE","",IF(AK11="0",0,IF(AK11="1",0.5,IF(AK11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AK11="","",IF(AK11="NE","",(IFERROR(IF(ISNUMBER(AK11),AK11,VALUE(AK11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AM11" s="20">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AN11" s="18" t="n"/>
       <c r="AO11" s="19">
-        <f>IF(AN11="","",IF(AN11="NE","",IF(AN11="0",0,IF(AN11="1",0.5,IF(AN11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AN11="","",IF(AN11="NE","",(IFERROR(IF(ISNUMBER(AN11),AN11,VALUE(AN11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AP11" s="20">
@@ -4295,7 +4295,7 @@
       </c>
       <c r="AQ11" s="18" t="n"/>
       <c r="AR11" s="19">
-        <f>IF(AQ11="","",IF(AQ11="NE","",IF(AQ11="0",0,IF(AQ11="1",0.5,IF(AQ11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AQ11="","",IF(AQ11="NE","",(IFERROR(IF(ISNUMBER(AQ11),AQ11,VALUE(AQ11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AS11" s="20">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="AT11" s="18" t="n"/>
       <c r="AU11" s="19">
-        <f>IF(AT11="","",IF(AT11="NE","",IF(AT11="0",0,IF(AT11="1",0.5,IF(AT11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AT11="","",IF(AT11="NE","",(IFERROR(IF(ISNUMBER(AT11),AT11,VALUE(AT11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AV11" s="20">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="AW11" s="18" t="n"/>
       <c r="AX11" s="19">
-        <f>IF(AW11="","",IF(AW11="NE","",IF(AW11="0",0,IF(AW11="1",0.5,IF(AW11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AW11="","",IF(AW11="NE","",(IFERROR(IF(ISNUMBER(AW11),AW11,VALUE(AW11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="AY11" s="20">
@@ -4322,7 +4322,7 @@
       </c>
       <c r="AZ11" s="18" t="n"/>
       <c r="BA11" s="19">
-        <f>IF(AZ11="","",IF(AZ11="NE","",IF(AZ11="0",0,IF(AZ11="1",0.5,IF(AZ11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(AZ11="","",IF(AZ11="NE","",(IFERROR(IF(ISNUMBER(AZ11),AZ11,VALUE(AZ11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BB11" s="20">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="BC11" s="18" t="n"/>
       <c r="BD11" s="19">
-        <f>IF(BC11="","",IF(BC11="NE","",IF(BC11="0",0,IF(BC11="1",0.5,IF(BC11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BC11="","",IF(BC11="NE","",(IFERROR(IF(ISNUMBER(BC11),BC11,VALUE(BC11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BE11" s="20">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="BF11" s="18" t="n"/>
       <c r="BG11" s="19">
-        <f>IF(BF11="","",IF(BF11="NE","",IF(BF11="0",0,IF(BF11="1",0.5,IF(BF11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BF11="","",IF(BF11="NE","",(IFERROR(IF(ISNUMBER(BF11),BF11,VALUE(BF11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BH11" s="20">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="BI11" s="18" t="n"/>
       <c r="BJ11" s="19">
-        <f>IF(BI11="","",IF(BI11="NE","",IF(BI11="0",0,IF(BI11="1",0.5,IF(BI11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BI11="","",IF(BI11="NE","",(IFERROR(IF(ISNUMBER(BI11),BI11,VALUE(BI11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BK11" s="20">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="BL11" s="18" t="n"/>
       <c r="BM11" s="19">
-        <f>IF(BL11="","",IF(BL11="NE","",IF(BL11="0",0,IF(BL11="1",0.5,IF(BL11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BL11="","",IF(BL11="NE","",(IFERROR(IF(ISNUMBER(BL11),BL11,VALUE(BL11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BN11" s="20">
@@ -4367,7 +4367,7 @@
       </c>
       <c r="BO11" s="18" t="n"/>
       <c r="BP11" s="19">
-        <f>IF(BO11="","",IF(BO11="NE","",IF(BO11="0",0,IF(BO11="1",0.5,IF(BO11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BO11="","",IF(BO11="NE","",(IFERROR(IF(ISNUMBER(BO11),BO11,VALUE(BO11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BQ11" s="20">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="BR11" s="18" t="n"/>
       <c r="BS11" s="19">
-        <f>IF(BR11="","",IF(BR11="NE","",IF(BR11="0",0,IF(BR11="1",0.5,IF(BR11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BR11="","",IF(BR11="NE","",(IFERROR(IF(ISNUMBER(BR11),BR11,VALUE(BR11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BT11" s="20">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="BU11" s="18" t="n"/>
       <c r="BV11" s="19">
-        <f>IF(BU11="","",IF(BU11="NE","",IF(BU11="0",0,IF(BU11="1",0.5,IF(BU11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BU11="","",IF(BU11="NE","",(IFERROR(IF(ISNUMBER(BU11),BU11,VALUE(BU11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BW11" s="20">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="BX11" s="18" t="n"/>
       <c r="BY11" s="19">
-        <f>IF(BX11="","",IF(BX11="NE","",IF(BX11="0",0,IF(BX11="1",0.5,IF(BX11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(BX11="","",IF(BX11="NE","",(IFERROR(IF(ISNUMBER(BX11),BX11,VALUE(BX11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="BZ11" s="20">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="CA11" s="18" t="n"/>
       <c r="CB11" s="19">
-        <f>IF(CA11="","",IF(CA11="NE","",IF(CA11="0",0,IF(CA11="1",0.5,IF(CA11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(CA11="","",IF(CA11="NE","",(IFERROR(IF(ISNUMBER(CA11),CA11,VALUE(CA11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="CC11" s="20">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="CD11" s="18" t="n"/>
       <c r="CE11" s="19">
-        <f>IF(CD11="","",IF(CD11="NE","",IF(CD11="0",0,IF(CD11="1",0.5,IF(CD11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(CD11="","",IF(CD11="NE","",(IFERROR(IF(ISNUMBER(CD11),CD11,VALUE(CD11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="CF11" s="20">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="CG11" s="18" t="n"/>
       <c r="CH11" s="19">
-        <f>IF(CG11="","",IF(CG11="NE","",IF(CG11="0",0,IF(CG11="1",0.5,IF(CG11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(CG11="","",IF(CG11="NE","",(IFERROR(IF(ISNUMBER(CG11),CG11,VALUE(CG11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="CI11" s="20">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="CJ11" s="18" t="n"/>
       <c r="CK11" s="19">
-        <f>IF(CJ11="","",IF(CJ11="NE","",IF(CJ11="0",0,IF(CJ11="1",0.5,IF(CJ11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(CJ11="","",IF(CJ11="NE","",(IFERROR(IF(ISNUMBER(CJ11),CJ11,VALUE(CJ11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="CL11" s="20">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="CM11" s="18" t="n"/>
       <c r="CN11" s="19">
-        <f>IF(CM11="","",IF(CM11="NE","",IF(CM11="0",0,IF(CM11="1",0.5,IF(CM11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(CM11="","",IF(CM11="NE","",(IFERROR(IF(ISNUMBER(CM11),CM11,VALUE(CM11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="CO11" s="20">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="CP11" s="18" t="n"/>
       <c r="CQ11" s="19">
-        <f>IF(CP11="","",IF(CP11="NE","",IF(CP11="0",0,IF(CP11="1",0.5,IF(CP11="2",1,0)))*$F11*$F$4*20))</f>
+        <f>IF(CP11="","",IF(CP11="NE","",(IFERROR(IF(ISNUMBER(CP11),CP11,VALUE(CP11)),0)/2)*$F11*$F$4*20))</f>
         <v/>
       </c>
       <c r="CR11" s="20">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="G13" s="18" t="n"/>
       <c r="H13" s="19">
-        <f>IF(G13="","",IF(G13="NE","",IF(G13="0",0,IF(G13="1",0.5,IF(G13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(G13="","",IF(G13="NE","",(IFERROR(IF(ISNUMBER(G13),G13,VALUE(G13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="I13" s="20">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="J13" s="18" t="n"/>
       <c r="K13" s="19">
-        <f>IF(J13="","",IF(J13="NE","",IF(J13="0",0,IF(J13="1",0.5,IF(J13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(J13="","",IF(J13="NE","",(IFERROR(IF(ISNUMBER(J13),J13,VALUE(J13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="L13" s="20">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="M13" s="18" t="n"/>
       <c r="N13" s="19">
-        <f>IF(M13="","",IF(M13="NE","",IF(M13="0",0,IF(M13="1",0.5,IF(M13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(M13="","",IF(M13="NE","",(IFERROR(IF(ISNUMBER(M13),M13,VALUE(M13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="O13" s="20">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="P13" s="18" t="n"/>
       <c r="Q13" s="19">
-        <f>IF(P13="","",IF(P13="NE","",IF(P13="0",0,IF(P13="1",0.5,IF(P13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(P13="","",IF(P13="NE","",(IFERROR(IF(ISNUMBER(P13),P13,VALUE(P13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="R13" s="20">
@@ -4633,7 +4633,7 @@
       </c>
       <c r="S13" s="18" t="n"/>
       <c r="T13" s="19">
-        <f>IF(S13="","",IF(S13="NE","",IF(S13="0",0,IF(S13="1",0.5,IF(S13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(S13="","",IF(S13="NE","",(IFERROR(IF(ISNUMBER(S13),S13,VALUE(S13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="U13" s="20">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="V13" s="18" t="n"/>
       <c r="W13" s="19">
-        <f>IF(V13="","",IF(V13="NE","",IF(V13="0",0,IF(V13="1",0.5,IF(V13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(V13="","",IF(V13="NE","",(IFERROR(IF(ISNUMBER(V13),V13,VALUE(V13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="X13" s="20">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="Y13" s="18" t="n"/>
       <c r="Z13" s="19">
-        <f>IF(Y13="","",IF(Y13="NE","",IF(Y13="0",0,IF(Y13="1",0.5,IF(Y13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(Y13="","",IF(Y13="NE","",(IFERROR(IF(ISNUMBER(Y13),Y13,VALUE(Y13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA13" s="20">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="AB13" s="18" t="n"/>
       <c r="AC13" s="19">
-        <f>IF(AB13="","",IF(AB13="NE","",IF(AB13="0",0,IF(AB13="1",0.5,IF(AB13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AB13="","",IF(AB13="NE","",(IFERROR(IF(ISNUMBER(AB13),AB13,VALUE(AB13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD13" s="20">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="AE13" s="18" t="n"/>
       <c r="AF13" s="19">
-        <f>IF(AE13="","",IF(AE13="NE","",IF(AE13="0",0,IF(AE13="1",0.5,IF(AE13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AE13="","",IF(AE13="NE","",(IFERROR(IF(ISNUMBER(AE13),AE13,VALUE(AE13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG13" s="20">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="AH13" s="18" t="n"/>
       <c r="AI13" s="19">
-        <f>IF(AH13="","",IF(AH13="NE","",IF(AH13="0",0,IF(AH13="1",0.5,IF(AH13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AH13="","",IF(AH13="NE","",(IFERROR(IF(ISNUMBER(AH13),AH13,VALUE(AH13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ13" s="20">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="AK13" s="18" t="n"/>
       <c r="AL13" s="19">
-        <f>IF(AK13="","",IF(AK13="NE","",IF(AK13="0",0,IF(AK13="1",0.5,IF(AK13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AK13="","",IF(AK13="NE","",(IFERROR(IF(ISNUMBER(AK13),AK13,VALUE(AK13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM13" s="20">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="AN13" s="18" t="n"/>
       <c r="AO13" s="19">
-        <f>IF(AN13="","",IF(AN13="NE","",IF(AN13="0",0,IF(AN13="1",0.5,IF(AN13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AN13="","",IF(AN13="NE","",(IFERROR(IF(ISNUMBER(AN13),AN13,VALUE(AN13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP13" s="20">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="AQ13" s="18" t="n"/>
       <c r="AR13" s="19">
-        <f>IF(AQ13="","",IF(AQ13="NE","",IF(AQ13="0",0,IF(AQ13="1",0.5,IF(AQ13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AQ13="","",IF(AQ13="NE","",(IFERROR(IF(ISNUMBER(AQ13),AQ13,VALUE(AQ13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS13" s="20">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="AT13" s="18" t="n"/>
       <c r="AU13" s="19">
-        <f>IF(AT13="","",IF(AT13="NE","",IF(AT13="0",0,IF(AT13="1",0.5,IF(AT13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AT13="","",IF(AT13="NE","",(IFERROR(IF(ISNUMBER(AT13),AT13,VALUE(AT13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV13" s="20">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="AW13" s="18" t="n"/>
       <c r="AX13" s="19">
-        <f>IF(AW13="","",IF(AW13="NE","",IF(AW13="0",0,IF(AW13="1",0.5,IF(AW13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AW13="","",IF(AW13="NE","",(IFERROR(IF(ISNUMBER(AW13),AW13,VALUE(AW13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY13" s="20">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="AZ13" s="18" t="n"/>
       <c r="BA13" s="19">
-        <f>IF(AZ13="","",IF(AZ13="NE","",IF(AZ13="0",0,IF(AZ13="1",0.5,IF(AZ13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(AZ13="","",IF(AZ13="NE","",(IFERROR(IF(ISNUMBER(AZ13),AZ13,VALUE(AZ13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB13" s="20">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="BC13" s="18" t="n"/>
       <c r="BD13" s="19">
-        <f>IF(BC13="","",IF(BC13="NE","",IF(BC13="0",0,IF(BC13="1",0.5,IF(BC13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BC13="","",IF(BC13="NE","",(IFERROR(IF(ISNUMBER(BC13),BC13,VALUE(BC13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE13" s="20">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="BF13" s="18" t="n"/>
       <c r="BG13" s="19">
-        <f>IF(BF13="","",IF(BF13="NE","",IF(BF13="0",0,IF(BF13="1",0.5,IF(BF13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BF13="","",IF(BF13="NE","",(IFERROR(IF(ISNUMBER(BF13),BF13,VALUE(BF13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH13" s="20">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="BI13" s="18" t="n"/>
       <c r="BJ13" s="19">
-        <f>IF(BI13="","",IF(BI13="NE","",IF(BI13="0",0,IF(BI13="1",0.5,IF(BI13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BI13="","",IF(BI13="NE","",(IFERROR(IF(ISNUMBER(BI13),BI13,VALUE(BI13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK13" s="20">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="BL13" s="18" t="n"/>
       <c r="BM13" s="19">
-        <f>IF(BL13="","",IF(BL13="NE","",IF(BL13="0",0,IF(BL13="1",0.5,IF(BL13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BL13="","",IF(BL13="NE","",(IFERROR(IF(ISNUMBER(BL13),BL13,VALUE(BL13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN13" s="20">
@@ -4777,7 +4777,7 @@
       </c>
       <c r="BO13" s="18" t="n"/>
       <c r="BP13" s="19">
-        <f>IF(BO13="","",IF(BO13="NE","",IF(BO13="0",0,IF(BO13="1",0.5,IF(BO13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BO13="","",IF(BO13="NE","",(IFERROR(IF(ISNUMBER(BO13),BO13,VALUE(BO13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ13" s="20">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="BR13" s="18" t="n"/>
       <c r="BS13" s="19">
-        <f>IF(BR13="","",IF(BR13="NE","",IF(BR13="0",0,IF(BR13="1",0.5,IF(BR13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BR13="","",IF(BR13="NE","",(IFERROR(IF(ISNUMBER(BR13),BR13,VALUE(BR13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT13" s="20">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="BU13" s="18" t="n"/>
       <c r="BV13" s="19">
-        <f>IF(BU13="","",IF(BU13="NE","",IF(BU13="0",0,IF(BU13="1",0.5,IF(BU13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BU13="","",IF(BU13="NE","",(IFERROR(IF(ISNUMBER(BU13),BU13,VALUE(BU13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW13" s="20">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="BX13" s="18" t="n"/>
       <c r="BY13" s="19">
-        <f>IF(BX13="","",IF(BX13="NE","",IF(BX13="0",0,IF(BX13="1",0.5,IF(BX13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(BX13="","",IF(BX13="NE","",(IFERROR(IF(ISNUMBER(BX13),BX13,VALUE(BX13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ13" s="20">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="CA13" s="18" t="n"/>
       <c r="CB13" s="19">
-        <f>IF(CA13="","",IF(CA13="NE","",IF(CA13="0",0,IF(CA13="1",0.5,IF(CA13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(CA13="","",IF(CA13="NE","",(IFERROR(IF(ISNUMBER(CA13),CA13,VALUE(CA13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC13" s="20">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="CD13" s="18" t="n"/>
       <c r="CE13" s="19">
-        <f>IF(CD13="","",IF(CD13="NE","",IF(CD13="0",0,IF(CD13="1",0.5,IF(CD13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(CD13="","",IF(CD13="NE","",(IFERROR(IF(ISNUMBER(CD13),CD13,VALUE(CD13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF13" s="20">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="CG13" s="18" t="n"/>
       <c r="CH13" s="19">
-        <f>IF(CG13="","",IF(CG13="NE","",IF(CG13="0",0,IF(CG13="1",0.5,IF(CG13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(CG13="","",IF(CG13="NE","",(IFERROR(IF(ISNUMBER(CG13),CG13,VALUE(CG13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI13" s="20">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="CJ13" s="18" t="n"/>
       <c r="CK13" s="19">
-        <f>IF(CJ13="","",IF(CJ13="NE","",IF(CJ13="0",0,IF(CJ13="1",0.5,IF(CJ13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(CJ13="","",IF(CJ13="NE","",(IFERROR(IF(ISNUMBER(CJ13),CJ13,VALUE(CJ13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL13" s="20">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="CM13" s="18" t="n"/>
       <c r="CN13" s="19">
-        <f>IF(CM13="","",IF(CM13="NE","",IF(CM13="0",0,IF(CM13="1",0.5,IF(CM13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(CM13="","",IF(CM13="NE","",(IFERROR(IF(ISNUMBER(CM13),CM13,VALUE(CM13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO13" s="20">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="CP13" s="18" t="n"/>
       <c r="CQ13" s="19">
-        <f>IF(CP13="","",IF(CP13="NE","",IF(CP13="0",0,IF(CP13="1",0.5,IF(CP13="2",1,0)))*$F13*$F$12*20))</f>
+        <f>IF(CP13="","",IF(CP13="NE","",(IFERROR(IF(ISNUMBER(CP13),CP13,VALUE(CP13)),0)/2)*$F13*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR13" s="20">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="G14" s="18" t="n"/>
       <c r="H14" s="19">
-        <f>IF(G14="","",IF(G14="NE","",IF(G14="0",0,IF(G14="1",0.5,IF(G14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(G14="","",IF(G14="NE","",(IFERROR(IF(ISNUMBER(G14),G14,VALUE(G14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="I14" s="20">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="J14" s="18" t="n"/>
       <c r="K14" s="19">
-        <f>IF(J14="","",IF(J14="NE","",IF(J14="0",0,IF(J14="1",0.5,IF(J14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(J14="","",IF(J14="NE","",(IFERROR(IF(ISNUMBER(J14),J14,VALUE(J14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="L14" s="20">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="M14" s="18" t="n"/>
       <c r="N14" s="19">
-        <f>IF(M14="","",IF(M14="NE","",IF(M14="0",0,IF(M14="1",0.5,IF(M14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(M14="","",IF(M14="NE","",(IFERROR(IF(ISNUMBER(M14),M14,VALUE(M14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="O14" s="20">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P14" s="18" t="n"/>
       <c r="Q14" s="19">
-        <f>IF(P14="","",IF(P14="NE","",IF(P14="0",0,IF(P14="1",0.5,IF(P14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(P14="","",IF(P14="NE","",(IFERROR(IF(ISNUMBER(P14),P14,VALUE(P14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="R14" s="20">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="S14" s="18" t="n"/>
       <c r="T14" s="19">
-        <f>IF(S14="","",IF(S14="NE","",IF(S14="0",0,IF(S14="1",0.5,IF(S14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(S14="","",IF(S14="NE","",(IFERROR(IF(ISNUMBER(S14),S14,VALUE(S14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="U14" s="20">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V14" s="18" t="n"/>
       <c r="W14" s="19">
-        <f>IF(V14="","",IF(V14="NE","",IF(V14="0",0,IF(V14="1",0.5,IF(V14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(V14="","",IF(V14="NE","",(IFERROR(IF(ISNUMBER(V14),V14,VALUE(V14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="X14" s="20">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="Y14" s="18" t="n"/>
       <c r="Z14" s="19">
-        <f>IF(Y14="","",IF(Y14="NE","",IF(Y14="0",0,IF(Y14="1",0.5,IF(Y14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(Y14="","",IF(Y14="NE","",(IFERROR(IF(ISNUMBER(Y14),Y14,VALUE(Y14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA14" s="20">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="AB14" s="18" t="n"/>
       <c r="AC14" s="19">
-        <f>IF(AB14="","",IF(AB14="NE","",IF(AB14="0",0,IF(AB14="1",0.5,IF(AB14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AB14="","",IF(AB14="NE","",(IFERROR(IF(ISNUMBER(AB14),AB14,VALUE(AB14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD14" s="20">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="AE14" s="18" t="n"/>
       <c r="AF14" s="19">
-        <f>IF(AE14="","",IF(AE14="NE","",IF(AE14="0",0,IF(AE14="1",0.5,IF(AE14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AE14="","",IF(AE14="NE","",(IFERROR(IF(ISNUMBER(AE14),AE14,VALUE(AE14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG14" s="20">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="AH14" s="18" t="n"/>
       <c r="AI14" s="19">
-        <f>IF(AH14="","",IF(AH14="NE","",IF(AH14="0",0,IF(AH14="1",0.5,IF(AH14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AH14="","",IF(AH14="NE","",(IFERROR(IF(ISNUMBER(AH14),AH14,VALUE(AH14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ14" s="20">
@@ -4985,7 +4985,7 @@
       </c>
       <c r="AK14" s="18" t="n"/>
       <c r="AL14" s="19">
-        <f>IF(AK14="","",IF(AK14="NE","",IF(AK14="0",0,IF(AK14="1",0.5,IF(AK14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AK14="","",IF(AK14="NE","",(IFERROR(IF(ISNUMBER(AK14),AK14,VALUE(AK14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM14" s="20">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="AN14" s="18" t="n"/>
       <c r="AO14" s="19">
-        <f>IF(AN14="","",IF(AN14="NE","",IF(AN14="0",0,IF(AN14="1",0.5,IF(AN14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AN14="","",IF(AN14="NE","",(IFERROR(IF(ISNUMBER(AN14),AN14,VALUE(AN14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP14" s="20">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AQ14" s="18" t="n"/>
       <c r="AR14" s="19">
-        <f>IF(AQ14="","",IF(AQ14="NE","",IF(AQ14="0",0,IF(AQ14="1",0.5,IF(AQ14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AQ14="","",IF(AQ14="NE","",(IFERROR(IF(ISNUMBER(AQ14),AQ14,VALUE(AQ14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS14" s="20">
@@ -5012,7 +5012,7 @@
       </c>
       <c r="AT14" s="18" t="n"/>
       <c r="AU14" s="19">
-        <f>IF(AT14="","",IF(AT14="NE","",IF(AT14="0",0,IF(AT14="1",0.5,IF(AT14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AT14="","",IF(AT14="NE","",(IFERROR(IF(ISNUMBER(AT14),AT14,VALUE(AT14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV14" s="20">
@@ -5021,7 +5021,7 @@
       </c>
       <c r="AW14" s="18" t="n"/>
       <c r="AX14" s="19">
-        <f>IF(AW14="","",IF(AW14="NE","",IF(AW14="0",0,IF(AW14="1",0.5,IF(AW14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AW14="","",IF(AW14="NE","",(IFERROR(IF(ISNUMBER(AW14),AW14,VALUE(AW14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY14" s="20">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AZ14" s="18" t="n"/>
       <c r="BA14" s="19">
-        <f>IF(AZ14="","",IF(AZ14="NE","",IF(AZ14="0",0,IF(AZ14="1",0.5,IF(AZ14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(AZ14="","",IF(AZ14="NE","",(IFERROR(IF(ISNUMBER(AZ14),AZ14,VALUE(AZ14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB14" s="20">
@@ -5039,7 +5039,7 @@
       </c>
       <c r="BC14" s="18" t="n"/>
       <c r="BD14" s="19">
-        <f>IF(BC14="","",IF(BC14="NE","",IF(BC14="0",0,IF(BC14="1",0.5,IF(BC14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BC14="","",IF(BC14="NE","",(IFERROR(IF(ISNUMBER(BC14),BC14,VALUE(BC14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE14" s="20">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="BF14" s="18" t="n"/>
       <c r="BG14" s="19">
-        <f>IF(BF14="","",IF(BF14="NE","",IF(BF14="0",0,IF(BF14="1",0.5,IF(BF14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BF14="","",IF(BF14="NE","",(IFERROR(IF(ISNUMBER(BF14),BF14,VALUE(BF14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH14" s="20">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="BI14" s="18" t="n"/>
       <c r="BJ14" s="19">
-        <f>IF(BI14="","",IF(BI14="NE","",IF(BI14="0",0,IF(BI14="1",0.5,IF(BI14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BI14="","",IF(BI14="NE","",(IFERROR(IF(ISNUMBER(BI14),BI14,VALUE(BI14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK14" s="20">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="BL14" s="18" t="n"/>
       <c r="BM14" s="19">
-        <f>IF(BL14="","",IF(BL14="NE","",IF(BL14="0",0,IF(BL14="1",0.5,IF(BL14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BL14="","",IF(BL14="NE","",(IFERROR(IF(ISNUMBER(BL14),BL14,VALUE(BL14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN14" s="20">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="BO14" s="18" t="n"/>
       <c r="BP14" s="19">
-        <f>IF(BO14="","",IF(BO14="NE","",IF(BO14="0",0,IF(BO14="1",0.5,IF(BO14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BO14="","",IF(BO14="NE","",(IFERROR(IF(ISNUMBER(BO14),BO14,VALUE(BO14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ14" s="20">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="BR14" s="18" t="n"/>
       <c r="BS14" s="19">
-        <f>IF(BR14="","",IF(BR14="NE","",IF(BR14="0",0,IF(BR14="1",0.5,IF(BR14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BR14="","",IF(BR14="NE","",(IFERROR(IF(ISNUMBER(BR14),BR14,VALUE(BR14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT14" s="20">
@@ -5093,7 +5093,7 @@
       </c>
       <c r="BU14" s="18" t="n"/>
       <c r="BV14" s="19">
-        <f>IF(BU14="","",IF(BU14="NE","",IF(BU14="0",0,IF(BU14="1",0.5,IF(BU14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BU14="","",IF(BU14="NE","",(IFERROR(IF(ISNUMBER(BU14),BU14,VALUE(BU14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW14" s="20">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="BX14" s="18" t="n"/>
       <c r="BY14" s="19">
-        <f>IF(BX14="","",IF(BX14="NE","",IF(BX14="0",0,IF(BX14="1",0.5,IF(BX14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(BX14="","",IF(BX14="NE","",(IFERROR(IF(ISNUMBER(BX14),BX14,VALUE(BX14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ14" s="20">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="CA14" s="18" t="n"/>
       <c r="CB14" s="19">
-        <f>IF(CA14="","",IF(CA14="NE","",IF(CA14="0",0,IF(CA14="1",0.5,IF(CA14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(CA14="","",IF(CA14="NE","",(IFERROR(IF(ISNUMBER(CA14),CA14,VALUE(CA14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC14" s="20">
@@ -5120,7 +5120,7 @@
       </c>
       <c r="CD14" s="18" t="n"/>
       <c r="CE14" s="19">
-        <f>IF(CD14="","",IF(CD14="NE","",IF(CD14="0",0,IF(CD14="1",0.5,IF(CD14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(CD14="","",IF(CD14="NE","",(IFERROR(IF(ISNUMBER(CD14),CD14,VALUE(CD14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF14" s="20">
@@ -5129,7 +5129,7 @@
       </c>
       <c r="CG14" s="18" t="n"/>
       <c r="CH14" s="19">
-        <f>IF(CG14="","",IF(CG14="NE","",IF(CG14="0",0,IF(CG14="1",0.5,IF(CG14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(CG14="","",IF(CG14="NE","",(IFERROR(IF(ISNUMBER(CG14),CG14,VALUE(CG14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI14" s="20">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="CJ14" s="18" t="n"/>
       <c r="CK14" s="19">
-        <f>IF(CJ14="","",IF(CJ14="NE","",IF(CJ14="0",0,IF(CJ14="1",0.5,IF(CJ14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(CJ14="","",IF(CJ14="NE","",(IFERROR(IF(ISNUMBER(CJ14),CJ14,VALUE(CJ14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL14" s="20">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="CM14" s="18" t="n"/>
       <c r="CN14" s="19">
-        <f>IF(CM14="","",IF(CM14="NE","",IF(CM14="0",0,IF(CM14="1",0.5,IF(CM14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(CM14="","",IF(CM14="NE","",(IFERROR(IF(ISNUMBER(CM14),CM14,VALUE(CM14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO14" s="20">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="CP14" s="18" t="n"/>
       <c r="CQ14" s="19">
-        <f>IF(CP14="","",IF(CP14="NE","",IF(CP14="0",0,IF(CP14="1",0.5,IF(CP14="2",1,0)))*$F14*$F$12*20))</f>
+        <f>IF(CP14="","",IF(CP14="NE","",(IFERROR(IF(ISNUMBER(CP14),CP14,VALUE(CP14)),0)/2)*$F14*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR14" s="20">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="G15" s="18" t="n"/>
       <c r="H15" s="19">
-        <f>IF(G15="","",IF(G15="NE","",IF(G15="0",0,IF(G15="1",0.5,IF(G15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(G15="","",IF(G15="NE","",(IFERROR(IF(ISNUMBER(G15),G15,VALUE(G15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="I15" s="20">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="J15" s="18" t="n"/>
       <c r="K15" s="19">
-        <f>IF(J15="","",IF(J15="NE","",IF(J15="0",0,IF(J15="1",0.5,IF(J15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(J15="","",IF(J15="NE","",(IFERROR(IF(ISNUMBER(J15),J15,VALUE(J15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="L15" s="20">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="M15" s="18" t="n"/>
       <c r="N15" s="19">
-        <f>IF(M15="","",IF(M15="NE","",IF(M15="0",0,IF(M15="1",0.5,IF(M15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(M15="","",IF(M15="NE","",(IFERROR(IF(ISNUMBER(M15),M15,VALUE(M15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="O15" s="20">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="P15" s="18" t="n"/>
       <c r="Q15" s="19">
-        <f>IF(P15="","",IF(P15="NE","",IF(P15="0",0,IF(P15="1",0.5,IF(P15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(P15="","",IF(P15="NE","",(IFERROR(IF(ISNUMBER(P15),P15,VALUE(P15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="R15" s="20">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="S15" s="18" t="n"/>
       <c r="T15" s="19">
-        <f>IF(S15="","",IF(S15="NE","",IF(S15="0",0,IF(S15="1",0.5,IF(S15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(S15="","",IF(S15="NE","",(IFERROR(IF(ISNUMBER(S15),S15,VALUE(S15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="U15" s="20">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="V15" s="18" t="n"/>
       <c r="W15" s="19">
-        <f>IF(V15="","",IF(V15="NE","",IF(V15="0",0,IF(V15="1",0.5,IF(V15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(V15="","",IF(V15="NE","",(IFERROR(IF(ISNUMBER(V15),V15,VALUE(V15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="X15" s="20">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="Y15" s="18" t="n"/>
       <c r="Z15" s="19">
-        <f>IF(Y15="","",IF(Y15="NE","",IF(Y15="0",0,IF(Y15="1",0.5,IF(Y15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(Y15="","",IF(Y15="NE","",(IFERROR(IF(ISNUMBER(Y15),Y15,VALUE(Y15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA15" s="20">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="AB15" s="18" t="n"/>
       <c r="AC15" s="19">
-        <f>IF(AB15="","",IF(AB15="NE","",IF(AB15="0",0,IF(AB15="1",0.5,IF(AB15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AB15="","",IF(AB15="NE","",(IFERROR(IF(ISNUMBER(AB15),AB15,VALUE(AB15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD15" s="20">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="AE15" s="18" t="n"/>
       <c r="AF15" s="19">
-        <f>IF(AE15="","",IF(AE15="NE","",IF(AE15="0",0,IF(AE15="1",0.5,IF(AE15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AE15="","",IF(AE15="NE","",(IFERROR(IF(ISNUMBER(AE15),AE15,VALUE(AE15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG15" s="20">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="AH15" s="18" t="n"/>
       <c r="AI15" s="19">
-        <f>IF(AH15="","",IF(AH15="NE","",IF(AH15="0",0,IF(AH15="1",0.5,IF(AH15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AH15="","",IF(AH15="NE","",(IFERROR(IF(ISNUMBER(AH15),AH15,VALUE(AH15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ15" s="20">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="AK15" s="18" t="n"/>
       <c r="AL15" s="19">
-        <f>IF(AK15="","",IF(AK15="NE","",IF(AK15="0",0,IF(AK15="1",0.5,IF(AK15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AK15="","",IF(AK15="NE","",(IFERROR(IF(ISNUMBER(AK15),AK15,VALUE(AK15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM15" s="20">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="AN15" s="18" t="n"/>
       <c r="AO15" s="19">
-        <f>IF(AN15="","",IF(AN15="NE","",IF(AN15="0",0,IF(AN15="1",0.5,IF(AN15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AN15="","",IF(AN15="NE","",(IFERROR(IF(ISNUMBER(AN15),AN15,VALUE(AN15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP15" s="20">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="AQ15" s="18" t="n"/>
       <c r="AR15" s="19">
-        <f>IF(AQ15="","",IF(AQ15="NE","",IF(AQ15="0",0,IF(AQ15="1",0.5,IF(AQ15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AQ15="","",IF(AQ15="NE","",(IFERROR(IF(ISNUMBER(AQ15),AQ15,VALUE(AQ15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS15" s="20">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="AT15" s="18" t="n"/>
       <c r="AU15" s="19">
-        <f>IF(AT15="","",IF(AT15="NE","",IF(AT15="0",0,IF(AT15="1",0.5,IF(AT15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AT15="","",IF(AT15="NE","",(IFERROR(IF(ISNUMBER(AT15),AT15,VALUE(AT15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV15" s="20">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="AW15" s="18" t="n"/>
       <c r="AX15" s="19">
-        <f>IF(AW15="","",IF(AW15="NE","",IF(AW15="0",0,IF(AW15="1",0.5,IF(AW15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AW15="","",IF(AW15="NE","",(IFERROR(IF(ISNUMBER(AW15),AW15,VALUE(AW15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY15" s="20">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="AZ15" s="18" t="n"/>
       <c r="BA15" s="19">
-        <f>IF(AZ15="","",IF(AZ15="NE","",IF(AZ15="0",0,IF(AZ15="1",0.5,IF(AZ15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(AZ15="","",IF(AZ15="NE","",(IFERROR(IF(ISNUMBER(AZ15),AZ15,VALUE(AZ15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB15" s="20">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="BC15" s="18" t="n"/>
       <c r="BD15" s="19">
-        <f>IF(BC15="","",IF(BC15="NE","",IF(BC15="0",0,IF(BC15="1",0.5,IF(BC15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BC15="","",IF(BC15="NE","",(IFERROR(IF(ISNUMBER(BC15),BC15,VALUE(BC15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE15" s="20">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="BF15" s="18" t="n"/>
       <c r="BG15" s="19">
-        <f>IF(BF15="","",IF(BF15="NE","",IF(BF15="0",0,IF(BF15="1",0.5,IF(BF15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BF15="","",IF(BF15="NE","",(IFERROR(IF(ISNUMBER(BF15),BF15,VALUE(BF15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH15" s="20">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="BI15" s="18" t="n"/>
       <c r="BJ15" s="19">
-        <f>IF(BI15="","",IF(BI15="NE","",IF(BI15="0",0,IF(BI15="1",0.5,IF(BI15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BI15="","",IF(BI15="NE","",(IFERROR(IF(ISNUMBER(BI15),BI15,VALUE(BI15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK15" s="20">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="BL15" s="18" t="n"/>
       <c r="BM15" s="19">
-        <f>IF(BL15="","",IF(BL15="NE","",IF(BL15="0",0,IF(BL15="1",0.5,IF(BL15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BL15="","",IF(BL15="NE","",(IFERROR(IF(ISNUMBER(BL15),BL15,VALUE(BL15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN15" s="20">
@@ -5373,7 +5373,7 @@
       </c>
       <c r="BO15" s="18" t="n"/>
       <c r="BP15" s="19">
-        <f>IF(BO15="","",IF(BO15="NE","",IF(BO15="0",0,IF(BO15="1",0.5,IF(BO15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BO15="","",IF(BO15="NE","",(IFERROR(IF(ISNUMBER(BO15),BO15,VALUE(BO15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ15" s="20">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BR15" s="18" t="n"/>
       <c r="BS15" s="19">
-        <f>IF(BR15="","",IF(BR15="NE","",IF(BR15="0",0,IF(BR15="1",0.5,IF(BR15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BR15="","",IF(BR15="NE","",(IFERROR(IF(ISNUMBER(BR15),BR15,VALUE(BR15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT15" s="20">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="BU15" s="18" t="n"/>
       <c r="BV15" s="19">
-        <f>IF(BU15="","",IF(BU15="NE","",IF(BU15="0",0,IF(BU15="1",0.5,IF(BU15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BU15="","",IF(BU15="NE","",(IFERROR(IF(ISNUMBER(BU15),BU15,VALUE(BU15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW15" s="20">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="BX15" s="18" t="n"/>
       <c r="BY15" s="19">
-        <f>IF(BX15="","",IF(BX15="NE","",IF(BX15="0",0,IF(BX15="1",0.5,IF(BX15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(BX15="","",IF(BX15="NE","",(IFERROR(IF(ISNUMBER(BX15),BX15,VALUE(BX15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ15" s="20">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="CA15" s="18" t="n"/>
       <c r="CB15" s="19">
-        <f>IF(CA15="","",IF(CA15="NE","",IF(CA15="0",0,IF(CA15="1",0.5,IF(CA15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(CA15="","",IF(CA15="NE","",(IFERROR(IF(ISNUMBER(CA15),CA15,VALUE(CA15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC15" s="20">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="CD15" s="18" t="n"/>
       <c r="CE15" s="19">
-        <f>IF(CD15="","",IF(CD15="NE","",IF(CD15="0",0,IF(CD15="1",0.5,IF(CD15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(CD15="","",IF(CD15="NE","",(IFERROR(IF(ISNUMBER(CD15),CD15,VALUE(CD15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF15" s="20">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="CG15" s="18" t="n"/>
       <c r="CH15" s="19">
-        <f>IF(CG15="","",IF(CG15="NE","",IF(CG15="0",0,IF(CG15="1",0.5,IF(CG15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(CG15="","",IF(CG15="NE","",(IFERROR(IF(ISNUMBER(CG15),CG15,VALUE(CG15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI15" s="20">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="CJ15" s="18" t="n"/>
       <c r="CK15" s="19">
-        <f>IF(CJ15="","",IF(CJ15="NE","",IF(CJ15="0",0,IF(CJ15="1",0.5,IF(CJ15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(CJ15="","",IF(CJ15="NE","",(IFERROR(IF(ISNUMBER(CJ15),CJ15,VALUE(CJ15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL15" s="20">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="CM15" s="18" t="n"/>
       <c r="CN15" s="19">
-        <f>IF(CM15="","",IF(CM15="NE","",IF(CM15="0",0,IF(CM15="1",0.5,IF(CM15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(CM15="","",IF(CM15="NE","",(IFERROR(IF(ISNUMBER(CM15),CM15,VALUE(CM15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO15" s="20">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="CP15" s="18" t="n"/>
       <c r="CQ15" s="19">
-        <f>IF(CP15="","",IF(CP15="NE","",IF(CP15="0",0,IF(CP15="1",0.5,IF(CP15="2",1,0)))*$F15*$F$12*20))</f>
+        <f>IF(CP15="","",IF(CP15="NE","",(IFERROR(IF(ISNUMBER(CP15),CP15,VALUE(CP15)),0)/2)*$F15*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR15" s="20">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="G16" s="18" t="n"/>
       <c r="H16" s="19">
-        <f>IF(G16="","",IF(G16="NE","",IF(G16="0",0,IF(G16="1",0.5,IF(G16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(G16="","",IF(G16="NE","",(IFERROR(IF(ISNUMBER(G16),G16,VALUE(G16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="I16" s="20">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="J16" s="18" t="n"/>
       <c r="K16" s="19">
-        <f>IF(J16="","",IF(J16="NE","",IF(J16="0",0,IF(J16="1",0.5,IF(J16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(J16="","",IF(J16="NE","",(IFERROR(IF(ISNUMBER(J16),J16,VALUE(J16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="L16" s="20">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="M16" s="18" t="n"/>
       <c r="N16" s="19">
-        <f>IF(M16="","",IF(M16="NE","",IF(M16="0",0,IF(M16="1",0.5,IF(M16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(M16="","",IF(M16="NE","",(IFERROR(IF(ISNUMBER(M16),M16,VALUE(M16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="O16" s="20">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="P16" s="18" t="n"/>
       <c r="Q16" s="19">
-        <f>IF(P16="","",IF(P16="NE","",IF(P16="0",0,IF(P16="1",0.5,IF(P16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(P16="","",IF(P16="NE","",(IFERROR(IF(ISNUMBER(P16),P16,VALUE(P16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="R16" s="20">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="S16" s="18" t="n"/>
       <c r="T16" s="19">
-        <f>IF(S16="","",IF(S16="NE","",IF(S16="0",0,IF(S16="1",0.5,IF(S16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(S16="","",IF(S16="NE","",(IFERROR(IF(ISNUMBER(S16),S16,VALUE(S16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="U16" s="20">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="V16" s="18" t="n"/>
       <c r="W16" s="19">
-        <f>IF(V16="","",IF(V16="NE","",IF(V16="0",0,IF(V16="1",0.5,IF(V16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(V16="","",IF(V16="NE","",(IFERROR(IF(ISNUMBER(V16),V16,VALUE(V16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="X16" s="20">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Y16" s="18" t="n"/>
       <c r="Z16" s="19">
-        <f>IF(Y16="","",IF(Y16="NE","",IF(Y16="0",0,IF(Y16="1",0.5,IF(Y16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(Y16="","",IF(Y16="NE","",(IFERROR(IF(ISNUMBER(Y16),Y16,VALUE(Y16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA16" s="20">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="AB16" s="18" t="n"/>
       <c r="AC16" s="19">
-        <f>IF(AB16="","",IF(AB16="NE","",IF(AB16="0",0,IF(AB16="1",0.5,IF(AB16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AB16="","",IF(AB16="NE","",(IFERROR(IF(ISNUMBER(AB16),AB16,VALUE(AB16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD16" s="20">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="AE16" s="18" t="n"/>
       <c r="AF16" s="19">
-        <f>IF(AE16="","",IF(AE16="NE","",IF(AE16="0",0,IF(AE16="1",0.5,IF(AE16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AE16="","",IF(AE16="NE","",(IFERROR(IF(ISNUMBER(AE16),AE16,VALUE(AE16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG16" s="20">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="AH16" s="18" t="n"/>
       <c r="AI16" s="19">
-        <f>IF(AH16="","",IF(AH16="NE","",IF(AH16="0",0,IF(AH16="1",0.5,IF(AH16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AH16="","",IF(AH16="NE","",(IFERROR(IF(ISNUMBER(AH16),AH16,VALUE(AH16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ16" s="20">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="AK16" s="18" t="n"/>
       <c r="AL16" s="19">
-        <f>IF(AK16="","",IF(AK16="NE","",IF(AK16="0",0,IF(AK16="1",0.5,IF(AK16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AK16="","",IF(AK16="NE","",(IFERROR(IF(ISNUMBER(AK16),AK16,VALUE(AK16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM16" s="20">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AN16" s="18" t="n"/>
       <c r="AO16" s="19">
-        <f>IF(AN16="","",IF(AN16="NE","",IF(AN16="0",0,IF(AN16="1",0.5,IF(AN16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AN16="","",IF(AN16="NE","",(IFERROR(IF(ISNUMBER(AN16),AN16,VALUE(AN16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP16" s="20">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="AQ16" s="18" t="n"/>
       <c r="AR16" s="19">
-        <f>IF(AQ16="","",IF(AQ16="NE","",IF(AQ16="0",0,IF(AQ16="1",0.5,IF(AQ16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AQ16="","",IF(AQ16="NE","",(IFERROR(IF(ISNUMBER(AQ16),AQ16,VALUE(AQ16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS16" s="20">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="AT16" s="18" t="n"/>
       <c r="AU16" s="19">
-        <f>IF(AT16="","",IF(AT16="NE","",IF(AT16="0",0,IF(AT16="1",0.5,IF(AT16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AT16="","",IF(AT16="NE","",(IFERROR(IF(ISNUMBER(AT16),AT16,VALUE(AT16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV16" s="20">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="AW16" s="18" t="n"/>
       <c r="AX16" s="19">
-        <f>IF(AW16="","",IF(AW16="NE","",IF(AW16="0",0,IF(AW16="1",0.5,IF(AW16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AW16="","",IF(AW16="NE","",(IFERROR(IF(ISNUMBER(AW16),AW16,VALUE(AW16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY16" s="20">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="AZ16" s="18" t="n"/>
       <c r="BA16" s="19">
-        <f>IF(AZ16="","",IF(AZ16="NE","",IF(AZ16="0",0,IF(AZ16="1",0.5,IF(AZ16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(AZ16="","",IF(AZ16="NE","",(IFERROR(IF(ISNUMBER(AZ16),AZ16,VALUE(AZ16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB16" s="20">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="BC16" s="18" t="n"/>
       <c r="BD16" s="19">
-        <f>IF(BC16="","",IF(BC16="NE","",IF(BC16="0",0,IF(BC16="1",0.5,IF(BC16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BC16="","",IF(BC16="NE","",(IFERROR(IF(ISNUMBER(BC16),BC16,VALUE(BC16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE16" s="20">
@@ -5644,7 +5644,7 @@
       </c>
       <c r="BF16" s="18" t="n"/>
       <c r="BG16" s="19">
-        <f>IF(BF16="","",IF(BF16="NE","",IF(BF16="0",0,IF(BF16="1",0.5,IF(BF16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BF16="","",IF(BF16="NE","",(IFERROR(IF(ISNUMBER(BF16),BF16,VALUE(BF16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH16" s="20">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="BI16" s="18" t="n"/>
       <c r="BJ16" s="19">
-        <f>IF(BI16="","",IF(BI16="NE","",IF(BI16="0",0,IF(BI16="1",0.5,IF(BI16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BI16="","",IF(BI16="NE","",(IFERROR(IF(ISNUMBER(BI16),BI16,VALUE(BI16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK16" s="20">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="BL16" s="18" t="n"/>
       <c r="BM16" s="19">
-        <f>IF(BL16="","",IF(BL16="NE","",IF(BL16="0",0,IF(BL16="1",0.5,IF(BL16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BL16="","",IF(BL16="NE","",(IFERROR(IF(ISNUMBER(BL16),BL16,VALUE(BL16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN16" s="20">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="BO16" s="18" t="n"/>
       <c r="BP16" s="19">
-        <f>IF(BO16="","",IF(BO16="NE","",IF(BO16="0",0,IF(BO16="1",0.5,IF(BO16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BO16="","",IF(BO16="NE","",(IFERROR(IF(ISNUMBER(BO16),BO16,VALUE(BO16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ16" s="20">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="BR16" s="18" t="n"/>
       <c r="BS16" s="19">
-        <f>IF(BR16="","",IF(BR16="NE","",IF(BR16="0",0,IF(BR16="1",0.5,IF(BR16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BR16="","",IF(BR16="NE","",(IFERROR(IF(ISNUMBER(BR16),BR16,VALUE(BR16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT16" s="20">
@@ -5689,7 +5689,7 @@
       </c>
       <c r="BU16" s="18" t="n"/>
       <c r="BV16" s="19">
-        <f>IF(BU16="","",IF(BU16="NE","",IF(BU16="0",0,IF(BU16="1",0.5,IF(BU16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BU16="","",IF(BU16="NE","",(IFERROR(IF(ISNUMBER(BU16),BU16,VALUE(BU16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW16" s="20">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="BX16" s="18" t="n"/>
       <c r="BY16" s="19">
-        <f>IF(BX16="","",IF(BX16="NE","",IF(BX16="0",0,IF(BX16="1",0.5,IF(BX16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(BX16="","",IF(BX16="NE","",(IFERROR(IF(ISNUMBER(BX16),BX16,VALUE(BX16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ16" s="20">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="CA16" s="18" t="n"/>
       <c r="CB16" s="19">
-        <f>IF(CA16="","",IF(CA16="NE","",IF(CA16="0",0,IF(CA16="1",0.5,IF(CA16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(CA16="","",IF(CA16="NE","",(IFERROR(IF(ISNUMBER(CA16),CA16,VALUE(CA16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC16" s="20">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="CD16" s="18" t="n"/>
       <c r="CE16" s="19">
-        <f>IF(CD16="","",IF(CD16="NE","",IF(CD16="0",0,IF(CD16="1",0.5,IF(CD16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(CD16="","",IF(CD16="NE","",(IFERROR(IF(ISNUMBER(CD16),CD16,VALUE(CD16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF16" s="20">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="CG16" s="18" t="n"/>
       <c r="CH16" s="19">
-        <f>IF(CG16="","",IF(CG16="NE","",IF(CG16="0",0,IF(CG16="1",0.5,IF(CG16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(CG16="","",IF(CG16="NE","",(IFERROR(IF(ISNUMBER(CG16),CG16,VALUE(CG16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI16" s="20">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="CJ16" s="18" t="n"/>
       <c r="CK16" s="19">
-        <f>IF(CJ16="","",IF(CJ16="NE","",IF(CJ16="0",0,IF(CJ16="1",0.5,IF(CJ16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(CJ16="","",IF(CJ16="NE","",(IFERROR(IF(ISNUMBER(CJ16),CJ16,VALUE(CJ16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL16" s="20">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="CM16" s="18" t="n"/>
       <c r="CN16" s="19">
-        <f>IF(CM16="","",IF(CM16="NE","",IF(CM16="0",0,IF(CM16="1",0.5,IF(CM16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(CM16="","",IF(CM16="NE","",(IFERROR(IF(ISNUMBER(CM16),CM16,VALUE(CM16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO16" s="20">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="CP16" s="18" t="n"/>
       <c r="CQ16" s="19">
-        <f>IF(CP16="","",IF(CP16="NE","",IF(CP16="0",0,IF(CP16="1",0.5,IF(CP16="2",1,0)))*$F16*$F$12*20))</f>
+        <f>IF(CP16="","",IF(CP16="NE","",(IFERROR(IF(ISNUMBER(CP16),CP16,VALUE(CP16)),0)/2)*$F16*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR16" s="20">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="G17" s="18" t="n"/>
       <c r="H17" s="19">
-        <f>IF(G17="","",IF(G17="NE","",IF(G17="0",0,IF(G17="1",0.5,IF(G17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(G17="","",IF(G17="NE","",(IFERROR(IF(ISNUMBER(G17),G17,VALUE(G17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="I17" s="20">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="J17" s="18" t="n"/>
       <c r="K17" s="19">
-        <f>IF(J17="","",IF(J17="NE","",IF(J17="0",0,IF(J17="1",0.5,IF(J17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(J17="","",IF(J17="NE","",(IFERROR(IF(ISNUMBER(J17),J17,VALUE(J17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="L17" s="20">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="M17" s="18" t="n"/>
       <c r="N17" s="19">
-        <f>IF(M17="","",IF(M17="NE","",IF(M17="0",0,IF(M17="1",0.5,IF(M17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(M17="","",IF(M17="NE","",(IFERROR(IF(ISNUMBER(M17),M17,VALUE(M17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="O17" s="20">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="P17" s="18" t="n"/>
       <c r="Q17" s="19">
-        <f>IF(P17="","",IF(P17="NE","",IF(P17="0",0,IF(P17="1",0.5,IF(P17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(P17="","",IF(P17="NE","",(IFERROR(IF(ISNUMBER(P17),P17,VALUE(P17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="R17" s="20">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="S17" s="18" t="n"/>
       <c r="T17" s="19">
-        <f>IF(S17="","",IF(S17="NE","",IF(S17="0",0,IF(S17="1",0.5,IF(S17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(S17="","",IF(S17="NE","",(IFERROR(IF(ISNUMBER(S17),S17,VALUE(S17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="U17" s="20">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="V17" s="18" t="n"/>
       <c r="W17" s="19">
-        <f>IF(V17="","",IF(V17="NE","",IF(V17="0",0,IF(V17="1",0.5,IF(V17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(V17="","",IF(V17="NE","",(IFERROR(IF(ISNUMBER(V17),V17,VALUE(V17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="X17" s="20">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="Y17" s="18" t="n"/>
       <c r="Z17" s="19">
-        <f>IF(Y17="","",IF(Y17="NE","",IF(Y17="0",0,IF(Y17="1",0.5,IF(Y17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(Y17="","",IF(Y17="NE","",(IFERROR(IF(ISNUMBER(Y17),Y17,VALUE(Y17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA17" s="20">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="AB17" s="18" t="n"/>
       <c r="AC17" s="19">
-        <f>IF(AB17="","",IF(AB17="NE","",IF(AB17="0",0,IF(AB17="1",0.5,IF(AB17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AB17="","",IF(AB17="NE","",(IFERROR(IF(ISNUMBER(AB17),AB17,VALUE(AB17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD17" s="20">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AE17" s="18" t="n"/>
       <c r="AF17" s="19">
-        <f>IF(AE17="","",IF(AE17="NE","",IF(AE17="0",0,IF(AE17="1",0.5,IF(AE17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AE17="","",IF(AE17="NE","",(IFERROR(IF(ISNUMBER(AE17),AE17,VALUE(AE17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG17" s="20">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="AH17" s="18" t="n"/>
       <c r="AI17" s="19">
-        <f>IF(AH17="","",IF(AH17="NE","",IF(AH17="0",0,IF(AH17="1",0.5,IF(AH17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AH17="","",IF(AH17="NE","",(IFERROR(IF(ISNUMBER(AH17),AH17,VALUE(AH17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ17" s="20">
@@ -5879,7 +5879,7 @@
       </c>
       <c r="AK17" s="18" t="n"/>
       <c r="AL17" s="19">
-        <f>IF(AK17="","",IF(AK17="NE","",IF(AK17="0",0,IF(AK17="1",0.5,IF(AK17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AK17="","",IF(AK17="NE","",(IFERROR(IF(ISNUMBER(AK17),AK17,VALUE(AK17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM17" s="20">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="AN17" s="18" t="n"/>
       <c r="AO17" s="19">
-        <f>IF(AN17="","",IF(AN17="NE","",IF(AN17="0",0,IF(AN17="1",0.5,IF(AN17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AN17="","",IF(AN17="NE","",(IFERROR(IF(ISNUMBER(AN17),AN17,VALUE(AN17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP17" s="20">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="AQ17" s="18" t="n"/>
       <c r="AR17" s="19">
-        <f>IF(AQ17="","",IF(AQ17="NE","",IF(AQ17="0",0,IF(AQ17="1",0.5,IF(AQ17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AQ17="","",IF(AQ17="NE","",(IFERROR(IF(ISNUMBER(AQ17),AQ17,VALUE(AQ17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS17" s="20">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="AT17" s="18" t="n"/>
       <c r="AU17" s="19">
-        <f>IF(AT17="","",IF(AT17="NE","",IF(AT17="0",0,IF(AT17="1",0.5,IF(AT17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AT17="","",IF(AT17="NE","",(IFERROR(IF(ISNUMBER(AT17),AT17,VALUE(AT17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV17" s="20">
@@ -5915,7 +5915,7 @@
       </c>
       <c r="AW17" s="18" t="n"/>
       <c r="AX17" s="19">
-        <f>IF(AW17="","",IF(AW17="NE","",IF(AW17="0",0,IF(AW17="1",0.5,IF(AW17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AW17="","",IF(AW17="NE","",(IFERROR(IF(ISNUMBER(AW17),AW17,VALUE(AW17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY17" s="20">
@@ -5924,7 +5924,7 @@
       </c>
       <c r="AZ17" s="18" t="n"/>
       <c r="BA17" s="19">
-        <f>IF(AZ17="","",IF(AZ17="NE","",IF(AZ17="0",0,IF(AZ17="1",0.5,IF(AZ17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(AZ17="","",IF(AZ17="NE","",(IFERROR(IF(ISNUMBER(AZ17),AZ17,VALUE(AZ17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB17" s="20">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="BC17" s="18" t="n"/>
       <c r="BD17" s="19">
-        <f>IF(BC17="","",IF(BC17="NE","",IF(BC17="0",0,IF(BC17="1",0.5,IF(BC17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BC17="","",IF(BC17="NE","",(IFERROR(IF(ISNUMBER(BC17),BC17,VALUE(BC17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE17" s="20">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="BF17" s="18" t="n"/>
       <c r="BG17" s="19">
-        <f>IF(BF17="","",IF(BF17="NE","",IF(BF17="0",0,IF(BF17="1",0.5,IF(BF17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BF17="","",IF(BF17="NE","",(IFERROR(IF(ISNUMBER(BF17),BF17,VALUE(BF17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH17" s="20">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="BI17" s="18" t="n"/>
       <c r="BJ17" s="19">
-        <f>IF(BI17="","",IF(BI17="NE","",IF(BI17="0",0,IF(BI17="1",0.5,IF(BI17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BI17="","",IF(BI17="NE","",(IFERROR(IF(ISNUMBER(BI17),BI17,VALUE(BI17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK17" s="20">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="BL17" s="18" t="n"/>
       <c r="BM17" s="19">
-        <f>IF(BL17="","",IF(BL17="NE","",IF(BL17="0",0,IF(BL17="1",0.5,IF(BL17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BL17="","",IF(BL17="NE","",(IFERROR(IF(ISNUMBER(BL17),BL17,VALUE(BL17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN17" s="20">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="BO17" s="18" t="n"/>
       <c r="BP17" s="19">
-        <f>IF(BO17="","",IF(BO17="NE","",IF(BO17="0",0,IF(BO17="1",0.5,IF(BO17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BO17="","",IF(BO17="NE","",(IFERROR(IF(ISNUMBER(BO17),BO17,VALUE(BO17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ17" s="20">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="BR17" s="18" t="n"/>
       <c r="BS17" s="19">
-        <f>IF(BR17="","",IF(BR17="NE","",IF(BR17="0",0,IF(BR17="1",0.5,IF(BR17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BR17="","",IF(BR17="NE","",(IFERROR(IF(ISNUMBER(BR17),BR17,VALUE(BR17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT17" s="20">
@@ -5987,7 +5987,7 @@
       </c>
       <c r="BU17" s="18" t="n"/>
       <c r="BV17" s="19">
-        <f>IF(BU17="","",IF(BU17="NE","",IF(BU17="0",0,IF(BU17="1",0.5,IF(BU17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BU17="","",IF(BU17="NE","",(IFERROR(IF(ISNUMBER(BU17),BU17,VALUE(BU17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW17" s="20">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="BX17" s="18" t="n"/>
       <c r="BY17" s="19">
-        <f>IF(BX17="","",IF(BX17="NE","",IF(BX17="0",0,IF(BX17="1",0.5,IF(BX17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(BX17="","",IF(BX17="NE","",(IFERROR(IF(ISNUMBER(BX17),BX17,VALUE(BX17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ17" s="20">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="CA17" s="18" t="n"/>
       <c r="CB17" s="19">
-        <f>IF(CA17="","",IF(CA17="NE","",IF(CA17="0",0,IF(CA17="1",0.5,IF(CA17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(CA17="","",IF(CA17="NE","",(IFERROR(IF(ISNUMBER(CA17),CA17,VALUE(CA17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC17" s="20">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="CD17" s="18" t="n"/>
       <c r="CE17" s="19">
-        <f>IF(CD17="","",IF(CD17="NE","",IF(CD17="0",0,IF(CD17="1",0.5,IF(CD17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(CD17="","",IF(CD17="NE","",(IFERROR(IF(ISNUMBER(CD17),CD17,VALUE(CD17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF17" s="20">
@@ -6023,7 +6023,7 @@
       </c>
       <c r="CG17" s="18" t="n"/>
       <c r="CH17" s="19">
-        <f>IF(CG17="","",IF(CG17="NE","",IF(CG17="0",0,IF(CG17="1",0.5,IF(CG17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(CG17="","",IF(CG17="NE","",(IFERROR(IF(ISNUMBER(CG17),CG17,VALUE(CG17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI17" s="20">
@@ -6032,7 +6032,7 @@
       </c>
       <c r="CJ17" s="18" t="n"/>
       <c r="CK17" s="19">
-        <f>IF(CJ17="","",IF(CJ17="NE","",IF(CJ17="0",0,IF(CJ17="1",0.5,IF(CJ17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(CJ17="","",IF(CJ17="NE","",(IFERROR(IF(ISNUMBER(CJ17),CJ17,VALUE(CJ17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL17" s="20">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="CM17" s="18" t="n"/>
       <c r="CN17" s="19">
-        <f>IF(CM17="","",IF(CM17="NE","",IF(CM17="0",0,IF(CM17="1",0.5,IF(CM17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(CM17="","",IF(CM17="NE","",(IFERROR(IF(ISNUMBER(CM17),CM17,VALUE(CM17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO17" s="20">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="CP17" s="18" t="n"/>
       <c r="CQ17" s="19">
-        <f>IF(CP17="","",IF(CP17="NE","",IF(CP17="0",0,IF(CP17="1",0.5,IF(CP17="2",1,0)))*$F17*$F$12*20))</f>
+        <f>IF(CP17="","",IF(CP17="NE","",(IFERROR(IF(ISNUMBER(CP17),CP17,VALUE(CP17)),0)/2)*$F17*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR17" s="20">
@@ -6087,7 +6087,7 @@
       </c>
       <c r="G18" s="18" t="n"/>
       <c r="H18" s="19">
-        <f>IF(G18="","",IF(G18="NE","",IF(G18="0",0,IF(G18="1",0.5,IF(G18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(G18="","",IF(G18="NE","",(IFERROR(IF(ISNUMBER(G18),G18,VALUE(G18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="I18" s="20">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="J18" s="18" t="n"/>
       <c r="K18" s="19">
-        <f>IF(J18="","",IF(J18="NE","",IF(J18="0",0,IF(J18="1",0.5,IF(J18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(J18="","",IF(J18="NE","",(IFERROR(IF(ISNUMBER(J18),J18,VALUE(J18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="L18" s="20">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="M18" s="18" t="n"/>
       <c r="N18" s="19">
-        <f>IF(M18="","",IF(M18="NE","",IF(M18="0",0,IF(M18="1",0.5,IF(M18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(M18="","",IF(M18="NE","",(IFERROR(IF(ISNUMBER(M18),M18,VALUE(M18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="O18" s="20">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="P18" s="18" t="n"/>
       <c r="Q18" s="19">
-        <f>IF(P18="","",IF(P18="NE","",IF(P18="0",0,IF(P18="1",0.5,IF(P18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(P18="","",IF(P18="NE","",(IFERROR(IF(ISNUMBER(P18),P18,VALUE(P18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="R18" s="20">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="S18" s="18" t="n"/>
       <c r="T18" s="19">
-        <f>IF(S18="","",IF(S18="NE","",IF(S18="0",0,IF(S18="1",0.5,IF(S18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(S18="","",IF(S18="NE","",(IFERROR(IF(ISNUMBER(S18),S18,VALUE(S18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="U18" s="20">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="V18" s="18" t="n"/>
       <c r="W18" s="19">
-        <f>IF(V18="","",IF(V18="NE","",IF(V18="0",0,IF(V18="1",0.5,IF(V18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(V18="","",IF(V18="NE","",(IFERROR(IF(ISNUMBER(V18),V18,VALUE(V18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="X18" s="20">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="Y18" s="18" t="n"/>
       <c r="Z18" s="19">
-        <f>IF(Y18="","",IF(Y18="NE","",IF(Y18="0",0,IF(Y18="1",0.5,IF(Y18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(Y18="","",IF(Y18="NE","",(IFERROR(IF(ISNUMBER(Y18),Y18,VALUE(Y18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA18" s="20">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AB18" s="18" t="n"/>
       <c r="AC18" s="19">
-        <f>IF(AB18="","",IF(AB18="NE","",IF(AB18="0",0,IF(AB18="1",0.5,IF(AB18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AB18="","",IF(AB18="NE","",(IFERROR(IF(ISNUMBER(AB18),AB18,VALUE(AB18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD18" s="20">
@@ -6159,7 +6159,7 @@
       </c>
       <c r="AE18" s="18" t="n"/>
       <c r="AF18" s="19">
-        <f>IF(AE18="","",IF(AE18="NE","",IF(AE18="0",0,IF(AE18="1",0.5,IF(AE18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AE18="","",IF(AE18="NE","",(IFERROR(IF(ISNUMBER(AE18),AE18,VALUE(AE18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG18" s="20">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="AH18" s="18" t="n"/>
       <c r="AI18" s="19">
-        <f>IF(AH18="","",IF(AH18="NE","",IF(AH18="0",0,IF(AH18="1",0.5,IF(AH18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AH18="","",IF(AH18="NE","",(IFERROR(IF(ISNUMBER(AH18),AH18,VALUE(AH18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ18" s="20">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AK18" s="18" t="n"/>
       <c r="AL18" s="19">
-        <f>IF(AK18="","",IF(AK18="NE","",IF(AK18="0",0,IF(AK18="1",0.5,IF(AK18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AK18="","",IF(AK18="NE","",(IFERROR(IF(ISNUMBER(AK18),AK18,VALUE(AK18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM18" s="20">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="AN18" s="18" t="n"/>
       <c r="AO18" s="19">
-        <f>IF(AN18="","",IF(AN18="NE","",IF(AN18="0",0,IF(AN18="1",0.5,IF(AN18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AN18="","",IF(AN18="NE","",(IFERROR(IF(ISNUMBER(AN18),AN18,VALUE(AN18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP18" s="20">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="AQ18" s="18" t="n"/>
       <c r="AR18" s="19">
-        <f>IF(AQ18="","",IF(AQ18="NE","",IF(AQ18="0",0,IF(AQ18="1",0.5,IF(AQ18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AQ18="","",IF(AQ18="NE","",(IFERROR(IF(ISNUMBER(AQ18),AQ18,VALUE(AQ18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS18" s="20">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AT18" s="18" t="n"/>
       <c r="AU18" s="19">
-        <f>IF(AT18="","",IF(AT18="NE","",IF(AT18="0",0,IF(AT18="1",0.5,IF(AT18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AT18="","",IF(AT18="NE","",(IFERROR(IF(ISNUMBER(AT18),AT18,VALUE(AT18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV18" s="20">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="AW18" s="18" t="n"/>
       <c r="AX18" s="19">
-        <f>IF(AW18="","",IF(AW18="NE","",IF(AW18="0",0,IF(AW18="1",0.5,IF(AW18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AW18="","",IF(AW18="NE","",(IFERROR(IF(ISNUMBER(AW18),AW18,VALUE(AW18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY18" s="20">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="AZ18" s="18" t="n"/>
       <c r="BA18" s="19">
-        <f>IF(AZ18="","",IF(AZ18="NE","",IF(AZ18="0",0,IF(AZ18="1",0.5,IF(AZ18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(AZ18="","",IF(AZ18="NE","",(IFERROR(IF(ISNUMBER(AZ18),AZ18,VALUE(AZ18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB18" s="20">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="BC18" s="18" t="n"/>
       <c r="BD18" s="19">
-        <f>IF(BC18="","",IF(BC18="NE","",IF(BC18="0",0,IF(BC18="1",0.5,IF(BC18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BC18="","",IF(BC18="NE","",(IFERROR(IF(ISNUMBER(BC18),BC18,VALUE(BC18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE18" s="20">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="BF18" s="18" t="n"/>
       <c r="BG18" s="19">
-        <f>IF(BF18="","",IF(BF18="NE","",IF(BF18="0",0,IF(BF18="1",0.5,IF(BF18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BF18="","",IF(BF18="NE","",(IFERROR(IF(ISNUMBER(BF18),BF18,VALUE(BF18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH18" s="20">
@@ -6249,7 +6249,7 @@
       </c>
       <c r="BI18" s="18" t="n"/>
       <c r="BJ18" s="19">
-        <f>IF(BI18="","",IF(BI18="NE","",IF(BI18="0",0,IF(BI18="1",0.5,IF(BI18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BI18="","",IF(BI18="NE","",(IFERROR(IF(ISNUMBER(BI18),BI18,VALUE(BI18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK18" s="20">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="BL18" s="18" t="n"/>
       <c r="BM18" s="19">
-        <f>IF(BL18="","",IF(BL18="NE","",IF(BL18="0",0,IF(BL18="1",0.5,IF(BL18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BL18="","",IF(BL18="NE","",(IFERROR(IF(ISNUMBER(BL18),BL18,VALUE(BL18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN18" s="20">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="BO18" s="18" t="n"/>
       <c r="BP18" s="19">
-        <f>IF(BO18="","",IF(BO18="NE","",IF(BO18="0",0,IF(BO18="1",0.5,IF(BO18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BO18="","",IF(BO18="NE","",(IFERROR(IF(ISNUMBER(BO18),BO18,VALUE(BO18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ18" s="20">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="BR18" s="18" t="n"/>
       <c r="BS18" s="19">
-        <f>IF(BR18="","",IF(BR18="NE","",IF(BR18="0",0,IF(BR18="1",0.5,IF(BR18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BR18="","",IF(BR18="NE","",(IFERROR(IF(ISNUMBER(BR18),BR18,VALUE(BR18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT18" s="20">
@@ -6285,7 +6285,7 @@
       </c>
       <c r="BU18" s="18" t="n"/>
       <c r="BV18" s="19">
-        <f>IF(BU18="","",IF(BU18="NE","",IF(BU18="0",0,IF(BU18="1",0.5,IF(BU18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BU18="","",IF(BU18="NE","",(IFERROR(IF(ISNUMBER(BU18),BU18,VALUE(BU18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW18" s="20">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="BX18" s="18" t="n"/>
       <c r="BY18" s="19">
-        <f>IF(BX18="","",IF(BX18="NE","",IF(BX18="0",0,IF(BX18="1",0.5,IF(BX18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(BX18="","",IF(BX18="NE","",(IFERROR(IF(ISNUMBER(BX18),BX18,VALUE(BX18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ18" s="20">
@@ -6303,7 +6303,7 @@
       </c>
       <c r="CA18" s="18" t="n"/>
       <c r="CB18" s="19">
-        <f>IF(CA18="","",IF(CA18="NE","",IF(CA18="0",0,IF(CA18="1",0.5,IF(CA18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(CA18="","",IF(CA18="NE","",(IFERROR(IF(ISNUMBER(CA18),CA18,VALUE(CA18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC18" s="20">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="CD18" s="18" t="n"/>
       <c r="CE18" s="19">
-        <f>IF(CD18="","",IF(CD18="NE","",IF(CD18="0",0,IF(CD18="1",0.5,IF(CD18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(CD18="","",IF(CD18="NE","",(IFERROR(IF(ISNUMBER(CD18),CD18,VALUE(CD18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF18" s="20">
@@ -6321,7 +6321,7 @@
       </c>
       <c r="CG18" s="18" t="n"/>
       <c r="CH18" s="19">
-        <f>IF(CG18="","",IF(CG18="NE","",IF(CG18="0",0,IF(CG18="1",0.5,IF(CG18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(CG18="","",IF(CG18="NE","",(IFERROR(IF(ISNUMBER(CG18),CG18,VALUE(CG18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI18" s="20">
@@ -6330,7 +6330,7 @@
       </c>
       <c r="CJ18" s="18" t="n"/>
       <c r="CK18" s="19">
-        <f>IF(CJ18="","",IF(CJ18="NE","",IF(CJ18="0",0,IF(CJ18="1",0.5,IF(CJ18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(CJ18="","",IF(CJ18="NE","",(IFERROR(IF(ISNUMBER(CJ18),CJ18,VALUE(CJ18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL18" s="20">
@@ -6339,7 +6339,7 @@
       </c>
       <c r="CM18" s="18" t="n"/>
       <c r="CN18" s="19">
-        <f>IF(CM18="","",IF(CM18="NE","",IF(CM18="0",0,IF(CM18="1",0.5,IF(CM18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(CM18="","",IF(CM18="NE","",(IFERROR(IF(ISNUMBER(CM18),CM18,VALUE(CM18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO18" s="20">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="CP18" s="18" t="n"/>
       <c r="CQ18" s="19">
-        <f>IF(CP18="","",IF(CP18="NE","",IF(CP18="0",0,IF(CP18="1",0.5,IF(CP18="2",1,0)))*$F18*$F$12*20))</f>
+        <f>IF(CP18="","",IF(CP18="NE","",(IFERROR(IF(ISNUMBER(CP18),CP18,VALUE(CP18)),0)/2)*$F18*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR18" s="20">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="G19" s="18" t="n"/>
       <c r="H19" s="19">
-        <f>IF(G19="","",IF(G19="NE","",IF(G19="0",0,IF(G19="1",0.5,IF(G19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(G19="","",IF(G19="NE","",(IFERROR(IF(ISNUMBER(G19),G19,VALUE(G19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="I19" s="20">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="J19" s="18" t="n"/>
       <c r="K19" s="19">
-        <f>IF(J19="","",IF(J19="NE","",IF(J19="0",0,IF(J19="1",0.5,IF(J19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(J19="","",IF(J19="NE","",(IFERROR(IF(ISNUMBER(J19),J19,VALUE(J19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="L19" s="20">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="M19" s="18" t="n"/>
       <c r="N19" s="19">
-        <f>IF(M19="","",IF(M19="NE","",IF(M19="0",0,IF(M19="1",0.5,IF(M19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(M19="","",IF(M19="NE","",(IFERROR(IF(ISNUMBER(M19),M19,VALUE(M19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="O19" s="20">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="P19" s="18" t="n"/>
       <c r="Q19" s="19">
-        <f>IF(P19="","",IF(P19="NE","",IF(P19="0",0,IF(P19="1",0.5,IF(P19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(P19="","",IF(P19="NE","",(IFERROR(IF(ISNUMBER(P19),P19,VALUE(P19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="R19" s="20">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="S19" s="18" t="n"/>
       <c r="T19" s="19">
-        <f>IF(S19="","",IF(S19="NE","",IF(S19="0",0,IF(S19="1",0.5,IF(S19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(S19="","",IF(S19="NE","",(IFERROR(IF(ISNUMBER(S19),S19,VALUE(S19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="U19" s="20">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="V19" s="18" t="n"/>
       <c r="W19" s="19">
-        <f>IF(V19="","",IF(V19="NE","",IF(V19="0",0,IF(V19="1",0.5,IF(V19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(V19="","",IF(V19="NE","",(IFERROR(IF(ISNUMBER(V19),V19,VALUE(V19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="X19" s="20">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="Y19" s="18" t="n"/>
       <c r="Z19" s="19">
-        <f>IF(Y19="","",IF(Y19="NE","",IF(Y19="0",0,IF(Y19="1",0.5,IF(Y19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(Y19="","",IF(Y19="NE","",(IFERROR(IF(ISNUMBER(Y19),Y19,VALUE(Y19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA19" s="20">
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB19" s="18" t="n"/>
       <c r="AC19" s="19">
-        <f>IF(AB19="","",IF(AB19="NE","",IF(AB19="0",0,IF(AB19="1",0.5,IF(AB19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AB19="","",IF(AB19="NE","",(IFERROR(IF(ISNUMBER(AB19),AB19,VALUE(AB19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD19" s="20">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="AE19" s="18" t="n"/>
       <c r="AF19" s="19">
-        <f>IF(AE19="","",IF(AE19="NE","",IF(AE19="0",0,IF(AE19="1",0.5,IF(AE19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AE19="","",IF(AE19="NE","",(IFERROR(IF(ISNUMBER(AE19),AE19,VALUE(AE19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG19" s="20">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="AH19" s="18" t="n"/>
       <c r="AI19" s="19">
-        <f>IF(AH19="","",IF(AH19="NE","",IF(AH19="0",0,IF(AH19="1",0.5,IF(AH19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AH19="","",IF(AH19="NE","",(IFERROR(IF(ISNUMBER(AH19),AH19,VALUE(AH19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ19" s="20">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="AK19" s="18" t="n"/>
       <c r="AL19" s="19">
-        <f>IF(AK19="","",IF(AK19="NE","",IF(AK19="0",0,IF(AK19="1",0.5,IF(AK19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AK19="","",IF(AK19="NE","",(IFERROR(IF(ISNUMBER(AK19),AK19,VALUE(AK19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM19" s="20">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="AN19" s="18" t="n"/>
       <c r="AO19" s="19">
-        <f>IF(AN19="","",IF(AN19="NE","",IF(AN19="0",0,IF(AN19="1",0.5,IF(AN19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AN19="","",IF(AN19="NE","",(IFERROR(IF(ISNUMBER(AN19),AN19,VALUE(AN19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP19" s="20">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="AQ19" s="18" t="n"/>
       <c r="AR19" s="19">
-        <f>IF(AQ19="","",IF(AQ19="NE","",IF(AQ19="0",0,IF(AQ19="1",0.5,IF(AQ19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AQ19="","",IF(AQ19="NE","",(IFERROR(IF(ISNUMBER(AQ19),AQ19,VALUE(AQ19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS19" s="20">
@@ -6502,7 +6502,7 @@
       </c>
       <c r="AT19" s="18" t="n"/>
       <c r="AU19" s="19">
-        <f>IF(AT19="","",IF(AT19="NE","",IF(AT19="0",0,IF(AT19="1",0.5,IF(AT19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AT19="","",IF(AT19="NE","",(IFERROR(IF(ISNUMBER(AT19),AT19,VALUE(AT19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV19" s="20">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="AW19" s="18" t="n"/>
       <c r="AX19" s="19">
-        <f>IF(AW19="","",IF(AW19="NE","",IF(AW19="0",0,IF(AW19="1",0.5,IF(AW19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AW19="","",IF(AW19="NE","",(IFERROR(IF(ISNUMBER(AW19),AW19,VALUE(AW19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY19" s="20">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="AZ19" s="18" t="n"/>
       <c r="BA19" s="19">
-        <f>IF(AZ19="","",IF(AZ19="NE","",IF(AZ19="0",0,IF(AZ19="1",0.5,IF(AZ19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(AZ19="","",IF(AZ19="NE","",(IFERROR(IF(ISNUMBER(AZ19),AZ19,VALUE(AZ19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB19" s="20">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="BC19" s="18" t="n"/>
       <c r="BD19" s="19">
-        <f>IF(BC19="","",IF(BC19="NE","",IF(BC19="0",0,IF(BC19="1",0.5,IF(BC19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BC19="","",IF(BC19="NE","",(IFERROR(IF(ISNUMBER(BC19),BC19,VALUE(BC19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE19" s="20">
@@ -6538,7 +6538,7 @@
       </c>
       <c r="BF19" s="18" t="n"/>
       <c r="BG19" s="19">
-        <f>IF(BF19="","",IF(BF19="NE","",IF(BF19="0",0,IF(BF19="1",0.5,IF(BF19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BF19="","",IF(BF19="NE","",(IFERROR(IF(ISNUMBER(BF19),BF19,VALUE(BF19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH19" s="20">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="BI19" s="18" t="n"/>
       <c r="BJ19" s="19">
-        <f>IF(BI19="","",IF(BI19="NE","",IF(BI19="0",0,IF(BI19="1",0.5,IF(BI19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BI19="","",IF(BI19="NE","",(IFERROR(IF(ISNUMBER(BI19),BI19,VALUE(BI19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK19" s="20">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="BL19" s="18" t="n"/>
       <c r="BM19" s="19">
-        <f>IF(BL19="","",IF(BL19="NE","",IF(BL19="0",0,IF(BL19="1",0.5,IF(BL19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BL19="","",IF(BL19="NE","",(IFERROR(IF(ISNUMBER(BL19),BL19,VALUE(BL19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN19" s="20">
@@ -6565,7 +6565,7 @@
       </c>
       <c r="BO19" s="18" t="n"/>
       <c r="BP19" s="19">
-        <f>IF(BO19="","",IF(BO19="NE","",IF(BO19="0",0,IF(BO19="1",0.5,IF(BO19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BO19="","",IF(BO19="NE","",(IFERROR(IF(ISNUMBER(BO19),BO19,VALUE(BO19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ19" s="20">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="BR19" s="18" t="n"/>
       <c r="BS19" s="19">
-        <f>IF(BR19="","",IF(BR19="NE","",IF(BR19="0",0,IF(BR19="1",0.5,IF(BR19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BR19="","",IF(BR19="NE","",(IFERROR(IF(ISNUMBER(BR19),BR19,VALUE(BR19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT19" s="20">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="BU19" s="18" t="n"/>
       <c r="BV19" s="19">
-        <f>IF(BU19="","",IF(BU19="NE","",IF(BU19="0",0,IF(BU19="1",0.5,IF(BU19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BU19="","",IF(BU19="NE","",(IFERROR(IF(ISNUMBER(BU19),BU19,VALUE(BU19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW19" s="20">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="BX19" s="18" t="n"/>
       <c r="BY19" s="19">
-        <f>IF(BX19="","",IF(BX19="NE","",IF(BX19="0",0,IF(BX19="1",0.5,IF(BX19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(BX19="","",IF(BX19="NE","",(IFERROR(IF(ISNUMBER(BX19),BX19,VALUE(BX19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ19" s="20">
@@ -6601,7 +6601,7 @@
       </c>
       <c r="CA19" s="18" t="n"/>
       <c r="CB19" s="19">
-        <f>IF(CA19="","",IF(CA19="NE","",IF(CA19="0",0,IF(CA19="1",0.5,IF(CA19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(CA19="","",IF(CA19="NE","",(IFERROR(IF(ISNUMBER(CA19),CA19,VALUE(CA19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC19" s="20">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="CD19" s="18" t="n"/>
       <c r="CE19" s="19">
-        <f>IF(CD19="","",IF(CD19="NE","",IF(CD19="0",0,IF(CD19="1",0.5,IF(CD19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(CD19="","",IF(CD19="NE","",(IFERROR(IF(ISNUMBER(CD19),CD19,VALUE(CD19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF19" s="20">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="CG19" s="18" t="n"/>
       <c r="CH19" s="19">
-        <f>IF(CG19="","",IF(CG19="NE","",IF(CG19="0",0,IF(CG19="1",0.5,IF(CG19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(CG19="","",IF(CG19="NE","",(IFERROR(IF(ISNUMBER(CG19),CG19,VALUE(CG19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI19" s="20">
@@ -6628,7 +6628,7 @@
       </c>
       <c r="CJ19" s="18" t="n"/>
       <c r="CK19" s="19">
-        <f>IF(CJ19="","",IF(CJ19="NE","",IF(CJ19="0",0,IF(CJ19="1",0.5,IF(CJ19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(CJ19="","",IF(CJ19="NE","",(IFERROR(IF(ISNUMBER(CJ19),CJ19,VALUE(CJ19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL19" s="20">
@@ -6637,7 +6637,7 @@
       </c>
       <c r="CM19" s="18" t="n"/>
       <c r="CN19" s="19">
-        <f>IF(CM19="","",IF(CM19="NE","",IF(CM19="0",0,IF(CM19="1",0.5,IF(CM19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(CM19="","",IF(CM19="NE","",(IFERROR(IF(ISNUMBER(CM19),CM19,VALUE(CM19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO19" s="20">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="CP19" s="18" t="n"/>
       <c r="CQ19" s="19">
-        <f>IF(CP19="","",IF(CP19="NE","",IF(CP19="0",0,IF(CP19="1",0.5,IF(CP19="2",1,0)))*$F19*$F$12*20))</f>
+        <f>IF(CP19="","",IF(CP19="NE","",(IFERROR(IF(ISNUMBER(CP19),CP19,VALUE(CP19)),0)/2)*$F19*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR19" s="20">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="G20" s="18" t="n"/>
       <c r="H20" s="19">
-        <f>IF(G20="","",IF(G20="NE","",IF(G20="0",0,IF(G20="1",0.5,IF(G20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(G20="","",IF(G20="NE","",(IFERROR(IF(ISNUMBER(G20),G20,VALUE(G20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="I20" s="20">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="J20" s="18" t="n"/>
       <c r="K20" s="19">
-        <f>IF(J20="","",IF(J20="NE","",IF(J20="0",0,IF(J20="1",0.5,IF(J20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(J20="","",IF(J20="NE","",(IFERROR(IF(ISNUMBER(J20),J20,VALUE(J20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="L20" s="20">
@@ -6701,7 +6701,7 @@
       </c>
       <c r="M20" s="18" t="n"/>
       <c r="N20" s="19">
-        <f>IF(M20="","",IF(M20="NE","",IF(M20="0",0,IF(M20="1",0.5,IF(M20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(M20="","",IF(M20="NE","",(IFERROR(IF(ISNUMBER(M20),M20,VALUE(M20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="O20" s="20">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="P20" s="18" t="n"/>
       <c r="Q20" s="19">
-        <f>IF(P20="","",IF(P20="NE","",IF(P20="0",0,IF(P20="1",0.5,IF(P20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(P20="","",IF(P20="NE","",(IFERROR(IF(ISNUMBER(P20),P20,VALUE(P20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="R20" s="20">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="S20" s="18" t="n"/>
       <c r="T20" s="19">
-        <f>IF(S20="","",IF(S20="NE","",IF(S20="0",0,IF(S20="1",0.5,IF(S20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(S20="","",IF(S20="NE","",(IFERROR(IF(ISNUMBER(S20),S20,VALUE(S20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="U20" s="20">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="V20" s="18" t="n"/>
       <c r="W20" s="19">
-        <f>IF(V20="","",IF(V20="NE","",IF(V20="0",0,IF(V20="1",0.5,IF(V20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(V20="","",IF(V20="NE","",(IFERROR(IF(ISNUMBER(V20),V20,VALUE(V20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="X20" s="20">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="Y20" s="18" t="n"/>
       <c r="Z20" s="19">
-        <f>IF(Y20="","",IF(Y20="NE","",IF(Y20="0",0,IF(Y20="1",0.5,IF(Y20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(Y20="","",IF(Y20="NE","",(IFERROR(IF(ISNUMBER(Y20),Y20,VALUE(Y20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AA20" s="20">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="AB20" s="18" t="n"/>
       <c r="AC20" s="19">
-        <f>IF(AB20="","",IF(AB20="NE","",IF(AB20="0",0,IF(AB20="1",0.5,IF(AB20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AB20="","",IF(AB20="NE","",(IFERROR(IF(ISNUMBER(AB20),AB20,VALUE(AB20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AD20" s="20">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="AE20" s="18" t="n"/>
       <c r="AF20" s="19">
-        <f>IF(AE20="","",IF(AE20="NE","",IF(AE20="0",0,IF(AE20="1",0.5,IF(AE20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AE20="","",IF(AE20="NE","",(IFERROR(IF(ISNUMBER(AE20),AE20,VALUE(AE20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AG20" s="20">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AH20" s="18" t="n"/>
       <c r="AI20" s="19">
-        <f>IF(AH20="","",IF(AH20="NE","",IF(AH20="0",0,IF(AH20="1",0.5,IF(AH20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AH20="","",IF(AH20="NE","",(IFERROR(IF(ISNUMBER(AH20),AH20,VALUE(AH20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AJ20" s="20">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="AK20" s="18" t="n"/>
       <c r="AL20" s="19">
-        <f>IF(AK20="","",IF(AK20="NE","",IF(AK20="0",0,IF(AK20="1",0.5,IF(AK20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AK20="","",IF(AK20="NE","",(IFERROR(IF(ISNUMBER(AK20),AK20,VALUE(AK20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AM20" s="20">
@@ -6782,7 +6782,7 @@
       </c>
       <c r="AN20" s="18" t="n"/>
       <c r="AO20" s="19">
-        <f>IF(AN20="","",IF(AN20="NE","",IF(AN20="0",0,IF(AN20="1",0.5,IF(AN20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AN20="","",IF(AN20="NE","",(IFERROR(IF(ISNUMBER(AN20),AN20,VALUE(AN20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AP20" s="20">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="AQ20" s="18" t="n"/>
       <c r="AR20" s="19">
-        <f>IF(AQ20="","",IF(AQ20="NE","",IF(AQ20="0",0,IF(AQ20="1",0.5,IF(AQ20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AQ20="","",IF(AQ20="NE","",(IFERROR(IF(ISNUMBER(AQ20),AQ20,VALUE(AQ20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AS20" s="20">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="AT20" s="18" t="n"/>
       <c r="AU20" s="19">
-        <f>IF(AT20="","",IF(AT20="NE","",IF(AT20="0",0,IF(AT20="1",0.5,IF(AT20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AT20="","",IF(AT20="NE","",(IFERROR(IF(ISNUMBER(AT20),AT20,VALUE(AT20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AV20" s="20">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="AW20" s="18" t="n"/>
       <c r="AX20" s="19">
-        <f>IF(AW20="","",IF(AW20="NE","",IF(AW20="0",0,IF(AW20="1",0.5,IF(AW20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AW20="","",IF(AW20="NE","",(IFERROR(IF(ISNUMBER(AW20),AW20,VALUE(AW20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="AY20" s="20">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="AZ20" s="18" t="n"/>
       <c r="BA20" s="19">
-        <f>IF(AZ20="","",IF(AZ20="NE","",IF(AZ20="0",0,IF(AZ20="1",0.5,IF(AZ20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(AZ20="","",IF(AZ20="NE","",(IFERROR(IF(ISNUMBER(AZ20),AZ20,VALUE(AZ20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BB20" s="20">
@@ -6827,7 +6827,7 @@
       </c>
       <c r="BC20" s="18" t="n"/>
       <c r="BD20" s="19">
-        <f>IF(BC20="","",IF(BC20="NE","",IF(BC20="0",0,IF(BC20="1",0.5,IF(BC20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BC20="","",IF(BC20="NE","",(IFERROR(IF(ISNUMBER(BC20),BC20,VALUE(BC20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BE20" s="20">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="BF20" s="18" t="n"/>
       <c r="BG20" s="19">
-        <f>IF(BF20="","",IF(BF20="NE","",IF(BF20="0",0,IF(BF20="1",0.5,IF(BF20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BF20="","",IF(BF20="NE","",(IFERROR(IF(ISNUMBER(BF20),BF20,VALUE(BF20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BH20" s="20">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="BI20" s="18" t="n"/>
       <c r="BJ20" s="19">
-        <f>IF(BI20="","",IF(BI20="NE","",IF(BI20="0",0,IF(BI20="1",0.5,IF(BI20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BI20="","",IF(BI20="NE","",(IFERROR(IF(ISNUMBER(BI20),BI20,VALUE(BI20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BK20" s="20">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="BL20" s="18" t="n"/>
       <c r="BM20" s="19">
-        <f>IF(BL20="","",IF(BL20="NE","",IF(BL20="0",0,IF(BL20="1",0.5,IF(BL20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BL20="","",IF(BL20="NE","",(IFERROR(IF(ISNUMBER(BL20),BL20,VALUE(BL20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BN20" s="20">
@@ -6863,7 +6863,7 @@
       </c>
       <c r="BO20" s="18" t="n"/>
       <c r="BP20" s="19">
-        <f>IF(BO20="","",IF(BO20="NE","",IF(BO20="0",0,IF(BO20="1",0.5,IF(BO20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BO20="","",IF(BO20="NE","",(IFERROR(IF(ISNUMBER(BO20),BO20,VALUE(BO20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BQ20" s="20">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="BR20" s="18" t="n"/>
       <c r="BS20" s="19">
-        <f>IF(BR20="","",IF(BR20="NE","",IF(BR20="0",0,IF(BR20="1",0.5,IF(BR20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BR20="","",IF(BR20="NE","",(IFERROR(IF(ISNUMBER(BR20),BR20,VALUE(BR20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BT20" s="20">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="BU20" s="18" t="n"/>
       <c r="BV20" s="19">
-        <f>IF(BU20="","",IF(BU20="NE","",IF(BU20="0",0,IF(BU20="1",0.5,IF(BU20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BU20="","",IF(BU20="NE","",(IFERROR(IF(ISNUMBER(BU20),BU20,VALUE(BU20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BW20" s="20">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="BX20" s="18" t="n"/>
       <c r="BY20" s="19">
-        <f>IF(BX20="","",IF(BX20="NE","",IF(BX20="0",0,IF(BX20="1",0.5,IF(BX20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(BX20="","",IF(BX20="NE","",(IFERROR(IF(ISNUMBER(BX20),BX20,VALUE(BX20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="BZ20" s="20">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="CA20" s="18" t="n"/>
       <c r="CB20" s="19">
-        <f>IF(CA20="","",IF(CA20="NE","",IF(CA20="0",0,IF(CA20="1",0.5,IF(CA20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(CA20="","",IF(CA20="NE","",(IFERROR(IF(ISNUMBER(CA20),CA20,VALUE(CA20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="CC20" s="20">
@@ -6908,7 +6908,7 @@
       </c>
       <c r="CD20" s="18" t="n"/>
       <c r="CE20" s="19">
-        <f>IF(CD20="","",IF(CD20="NE","",IF(CD20="0",0,IF(CD20="1",0.5,IF(CD20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(CD20="","",IF(CD20="NE","",(IFERROR(IF(ISNUMBER(CD20),CD20,VALUE(CD20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="CF20" s="20">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="CG20" s="18" t="n"/>
       <c r="CH20" s="19">
-        <f>IF(CG20="","",IF(CG20="NE","",IF(CG20="0",0,IF(CG20="1",0.5,IF(CG20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(CG20="","",IF(CG20="NE","",(IFERROR(IF(ISNUMBER(CG20),CG20,VALUE(CG20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="CI20" s="20">
@@ -6926,7 +6926,7 @@
       </c>
       <c r="CJ20" s="18" t="n"/>
       <c r="CK20" s="19">
-        <f>IF(CJ20="","",IF(CJ20="NE","",IF(CJ20="0",0,IF(CJ20="1",0.5,IF(CJ20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(CJ20="","",IF(CJ20="NE","",(IFERROR(IF(ISNUMBER(CJ20),CJ20,VALUE(CJ20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="CL20" s="20">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="CM20" s="18" t="n"/>
       <c r="CN20" s="19">
-        <f>IF(CM20="","",IF(CM20="NE","",IF(CM20="0",0,IF(CM20="1",0.5,IF(CM20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(CM20="","",IF(CM20="NE","",(IFERROR(IF(ISNUMBER(CM20),CM20,VALUE(CM20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="CO20" s="20">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="CP20" s="18" t="n"/>
       <c r="CQ20" s="19">
-        <f>IF(CP20="","",IF(CP20="NE","",IF(CP20="0",0,IF(CP20="1",0.5,IF(CP20="2",1,0)))*$F20*$F$12*20))</f>
+        <f>IF(CP20="","",IF(CP20="NE","",(IFERROR(IF(ISNUMBER(CP20),CP20,VALUE(CP20)),0)/2)*$F20*$F$12*20))</f>
         <v/>
       </c>
       <c r="CR20" s="20">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="G22" s="18" t="n"/>
       <c r="H22" s="19">
-        <f>IF(G22="","",IF(G22="NE","",IF(G22="0",0,IF(G22="1",0.5,IF(G22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(G22="","",IF(G22="NE","",(IFERROR(IF(ISNUMBER(G22),G22,VALUE(G22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="I22" s="20">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="J22" s="18" t="n"/>
       <c r="K22" s="19">
-        <f>IF(J22="","",IF(J22="NE","",IF(J22="0",0,IF(J22="1",0.5,IF(J22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(J22="","",IF(J22="NE","",(IFERROR(IF(ISNUMBER(J22),J22,VALUE(J22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="L22" s="20">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="M22" s="18" t="n"/>
       <c r="N22" s="19">
-        <f>IF(M22="","",IF(M22="NE","",IF(M22="0",0,IF(M22="1",0.5,IF(M22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(M22="","",IF(M22="NE","",(IFERROR(IF(ISNUMBER(M22),M22,VALUE(M22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="O22" s="20">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="P22" s="18" t="n"/>
       <c r="Q22" s="19">
-        <f>IF(P22="","",IF(P22="NE","",IF(P22="0",0,IF(P22="1",0.5,IF(P22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(P22="","",IF(P22="NE","",(IFERROR(IF(ISNUMBER(P22),P22,VALUE(P22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="R22" s="20">
@@ -7129,7 +7129,7 @@
       </c>
       <c r="S22" s="18" t="n"/>
       <c r="T22" s="19">
-        <f>IF(S22="","",IF(S22="NE","",IF(S22="0",0,IF(S22="1",0.5,IF(S22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(S22="","",IF(S22="NE","",(IFERROR(IF(ISNUMBER(S22),S22,VALUE(S22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="U22" s="20">
@@ -7138,7 +7138,7 @@
       </c>
       <c r="V22" s="18" t="n"/>
       <c r="W22" s="19">
-        <f>IF(V22="","",IF(V22="NE","",IF(V22="0",0,IF(V22="1",0.5,IF(V22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(V22="","",IF(V22="NE","",(IFERROR(IF(ISNUMBER(V22),V22,VALUE(V22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="X22" s="20">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="Y22" s="18" t="n"/>
       <c r="Z22" s="19">
-        <f>IF(Y22="","",IF(Y22="NE","",IF(Y22="0",0,IF(Y22="1",0.5,IF(Y22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(Y22="","",IF(Y22="NE","",(IFERROR(IF(ISNUMBER(Y22),Y22,VALUE(Y22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AA22" s="20">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="AB22" s="18" t="n"/>
       <c r="AC22" s="19">
-        <f>IF(AB22="","",IF(AB22="NE","",IF(AB22="0",0,IF(AB22="1",0.5,IF(AB22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AB22="","",IF(AB22="NE","",(IFERROR(IF(ISNUMBER(AB22),AB22,VALUE(AB22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AD22" s="20">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="AE22" s="18" t="n"/>
       <c r="AF22" s="19">
-        <f>IF(AE22="","",IF(AE22="NE","",IF(AE22="0",0,IF(AE22="1",0.5,IF(AE22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AE22="","",IF(AE22="NE","",(IFERROR(IF(ISNUMBER(AE22),AE22,VALUE(AE22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AG22" s="20">
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AH22" s="18" t="n"/>
       <c r="AI22" s="19">
-        <f>IF(AH22="","",IF(AH22="NE","",IF(AH22="0",0,IF(AH22="1",0.5,IF(AH22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AH22="","",IF(AH22="NE","",(IFERROR(IF(ISNUMBER(AH22),AH22,VALUE(AH22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AJ22" s="20">
@@ -7183,7 +7183,7 @@
       </c>
       <c r="AK22" s="18" t="n"/>
       <c r="AL22" s="19">
-        <f>IF(AK22="","",IF(AK22="NE","",IF(AK22="0",0,IF(AK22="1",0.5,IF(AK22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AK22="","",IF(AK22="NE","",(IFERROR(IF(ISNUMBER(AK22),AK22,VALUE(AK22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AM22" s="20">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="AN22" s="18" t="n"/>
       <c r="AO22" s="19">
-        <f>IF(AN22="","",IF(AN22="NE","",IF(AN22="0",0,IF(AN22="1",0.5,IF(AN22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AN22="","",IF(AN22="NE","",(IFERROR(IF(ISNUMBER(AN22),AN22,VALUE(AN22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AP22" s="20">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="AQ22" s="18" t="n"/>
       <c r="AR22" s="19">
-        <f>IF(AQ22="","",IF(AQ22="NE","",IF(AQ22="0",0,IF(AQ22="1",0.5,IF(AQ22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AQ22="","",IF(AQ22="NE","",(IFERROR(IF(ISNUMBER(AQ22),AQ22,VALUE(AQ22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AS22" s="20">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="AT22" s="18" t="n"/>
       <c r="AU22" s="19">
-        <f>IF(AT22="","",IF(AT22="NE","",IF(AT22="0",0,IF(AT22="1",0.5,IF(AT22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AT22="","",IF(AT22="NE","",(IFERROR(IF(ISNUMBER(AT22),AT22,VALUE(AT22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AV22" s="20">
@@ -7219,7 +7219,7 @@
       </c>
       <c r="AW22" s="18" t="n"/>
       <c r="AX22" s="19">
-        <f>IF(AW22="","",IF(AW22="NE","",IF(AW22="0",0,IF(AW22="1",0.5,IF(AW22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AW22="","",IF(AW22="NE","",(IFERROR(IF(ISNUMBER(AW22),AW22,VALUE(AW22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="AY22" s="20">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="AZ22" s="18" t="n"/>
       <c r="BA22" s="19">
-        <f>IF(AZ22="","",IF(AZ22="NE","",IF(AZ22="0",0,IF(AZ22="1",0.5,IF(AZ22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(AZ22="","",IF(AZ22="NE","",(IFERROR(IF(ISNUMBER(AZ22),AZ22,VALUE(AZ22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BB22" s="20">
@@ -7237,7 +7237,7 @@
       </c>
       <c r="BC22" s="18" t="n"/>
       <c r="BD22" s="19">
-        <f>IF(BC22="","",IF(BC22="NE","",IF(BC22="0",0,IF(BC22="1",0.5,IF(BC22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BC22="","",IF(BC22="NE","",(IFERROR(IF(ISNUMBER(BC22),BC22,VALUE(BC22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BE22" s="20">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BF22" s="18" t="n"/>
       <c r="BG22" s="19">
-        <f>IF(BF22="","",IF(BF22="NE","",IF(BF22="0",0,IF(BF22="1",0.5,IF(BF22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BF22="","",IF(BF22="NE","",(IFERROR(IF(ISNUMBER(BF22),BF22,VALUE(BF22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BH22" s="20">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="BI22" s="18" t="n"/>
       <c r="BJ22" s="19">
-        <f>IF(BI22="","",IF(BI22="NE","",IF(BI22="0",0,IF(BI22="1",0.5,IF(BI22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BI22="","",IF(BI22="NE","",(IFERROR(IF(ISNUMBER(BI22),BI22,VALUE(BI22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BK22" s="20">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="BL22" s="18" t="n"/>
       <c r="BM22" s="19">
-        <f>IF(BL22="","",IF(BL22="NE","",IF(BL22="0",0,IF(BL22="1",0.5,IF(BL22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BL22="","",IF(BL22="NE","",(IFERROR(IF(ISNUMBER(BL22),BL22,VALUE(BL22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BN22" s="20">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="BO22" s="18" t="n"/>
       <c r="BP22" s="19">
-        <f>IF(BO22="","",IF(BO22="NE","",IF(BO22="0",0,IF(BO22="1",0.5,IF(BO22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BO22="","",IF(BO22="NE","",(IFERROR(IF(ISNUMBER(BO22),BO22,VALUE(BO22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BQ22" s="20">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="BR22" s="18" t="n"/>
       <c r="BS22" s="19">
-        <f>IF(BR22="","",IF(BR22="NE","",IF(BR22="0",0,IF(BR22="1",0.5,IF(BR22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BR22="","",IF(BR22="NE","",(IFERROR(IF(ISNUMBER(BR22),BR22,VALUE(BR22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BT22" s="20">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BU22" s="18" t="n"/>
       <c r="BV22" s="19">
-        <f>IF(BU22="","",IF(BU22="NE","",IF(BU22="0",0,IF(BU22="1",0.5,IF(BU22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BU22="","",IF(BU22="NE","",(IFERROR(IF(ISNUMBER(BU22),BU22,VALUE(BU22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BW22" s="20">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="BX22" s="18" t="n"/>
       <c r="BY22" s="19">
-        <f>IF(BX22="","",IF(BX22="NE","",IF(BX22="0",0,IF(BX22="1",0.5,IF(BX22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(BX22="","",IF(BX22="NE","",(IFERROR(IF(ISNUMBER(BX22),BX22,VALUE(BX22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="BZ22" s="20">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="CA22" s="18" t="n"/>
       <c r="CB22" s="19">
-        <f>IF(CA22="","",IF(CA22="NE","",IF(CA22="0",0,IF(CA22="1",0.5,IF(CA22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(CA22="","",IF(CA22="NE","",(IFERROR(IF(ISNUMBER(CA22),CA22,VALUE(CA22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="CC22" s="20">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="CD22" s="18" t="n"/>
       <c r="CE22" s="19">
-        <f>IF(CD22="","",IF(CD22="NE","",IF(CD22="0",0,IF(CD22="1",0.5,IF(CD22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(CD22="","",IF(CD22="NE","",(IFERROR(IF(ISNUMBER(CD22),CD22,VALUE(CD22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="CF22" s="20">
@@ -7327,7 +7327,7 @@
       </c>
       <c r="CG22" s="18" t="n"/>
       <c r="CH22" s="19">
-        <f>IF(CG22="","",IF(CG22="NE","",IF(CG22="0",0,IF(CG22="1",0.5,IF(CG22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(CG22="","",IF(CG22="NE","",(IFERROR(IF(ISNUMBER(CG22),CG22,VALUE(CG22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="CI22" s="20">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="CJ22" s="18" t="n"/>
       <c r="CK22" s="19">
-        <f>IF(CJ22="","",IF(CJ22="NE","",IF(CJ22="0",0,IF(CJ22="1",0.5,IF(CJ22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(CJ22="","",IF(CJ22="NE","",(IFERROR(IF(ISNUMBER(CJ22),CJ22,VALUE(CJ22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="CL22" s="20">
@@ -7345,7 +7345,7 @@
       </c>
       <c r="CM22" s="18" t="n"/>
       <c r="CN22" s="19">
-        <f>IF(CM22="","",IF(CM22="NE","",IF(CM22="0",0,IF(CM22="1",0.5,IF(CM22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(CM22="","",IF(CM22="NE","",(IFERROR(IF(ISNUMBER(CM22),CM22,VALUE(CM22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="CO22" s="20">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="CP22" s="18" t="n"/>
       <c r="CQ22" s="19">
-        <f>IF(CP22="","",IF(CP22="NE","",IF(CP22="0",0,IF(CP22="1",0.5,IF(CP22="2",1,0)))*$F22*$F$21*20))</f>
+        <f>IF(CP22="","",IF(CP22="NE","",(IFERROR(IF(ISNUMBER(CP22),CP22,VALUE(CP22)),0)/2)*$F22*$F$21*20))</f>
         <v/>
       </c>
       <c r="CR22" s="20">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="G23" s="18" t="n"/>
       <c r="H23" s="19">
-        <f>IF(G23="","",IF(G23="NE","",IF(G23="0",0,IF(G23="1",0.5,IF(G23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(G23="","",IF(G23="NE","",(IFERROR(IF(ISNUMBER(G23),G23,VALUE(G23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="I23" s="20">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="J23" s="18" t="n"/>
       <c r="K23" s="19">
-        <f>IF(J23="","",IF(J23="NE","",IF(J23="0",0,IF(J23="1",0.5,IF(J23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(J23="","",IF(J23="NE","",(IFERROR(IF(ISNUMBER(J23),J23,VALUE(J23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="L23" s="20">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="M23" s="18" t="n"/>
       <c r="N23" s="19">
-        <f>IF(M23="","",IF(M23="NE","",IF(M23="0",0,IF(M23="1",0.5,IF(M23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(M23="","",IF(M23="NE","",(IFERROR(IF(ISNUMBER(M23),M23,VALUE(M23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="O23" s="20">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="P23" s="18" t="n"/>
       <c r="Q23" s="19">
-        <f>IF(P23="","",IF(P23="NE","",IF(P23="0",0,IF(P23="1",0.5,IF(P23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(P23="","",IF(P23="NE","",(IFERROR(IF(ISNUMBER(P23),P23,VALUE(P23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="R23" s="20">
@@ -7427,7 +7427,7 @@
       </c>
       <c r="S23" s="18" t="n"/>
       <c r="T23" s="19">
-        <f>IF(S23="","",IF(S23="NE","",IF(S23="0",0,IF(S23="1",0.5,IF(S23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(S23="","",IF(S23="NE","",(IFERROR(IF(ISNUMBER(S23),S23,VALUE(S23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="U23" s="20">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="V23" s="18" t="n"/>
       <c r="W23" s="19">
-        <f>IF(V23="","",IF(V23="NE","",IF(V23="0",0,IF(V23="1",0.5,IF(V23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(V23="","",IF(V23="NE","",(IFERROR(IF(ISNUMBER(V23),V23,VALUE(V23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="X23" s="20">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="Y23" s="18" t="n"/>
       <c r="Z23" s="19">
-        <f>IF(Y23="","",IF(Y23="NE","",IF(Y23="0",0,IF(Y23="1",0.5,IF(Y23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(Y23="","",IF(Y23="NE","",(IFERROR(IF(ISNUMBER(Y23),Y23,VALUE(Y23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AA23" s="20">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AB23" s="18" t="n"/>
       <c r="AC23" s="19">
-        <f>IF(AB23="","",IF(AB23="NE","",IF(AB23="0",0,IF(AB23="1",0.5,IF(AB23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AB23="","",IF(AB23="NE","",(IFERROR(IF(ISNUMBER(AB23),AB23,VALUE(AB23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AD23" s="20">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="AE23" s="18" t="n"/>
       <c r="AF23" s="19">
-        <f>IF(AE23="","",IF(AE23="NE","",IF(AE23="0",0,IF(AE23="1",0.5,IF(AE23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AE23="","",IF(AE23="NE","",(IFERROR(IF(ISNUMBER(AE23),AE23,VALUE(AE23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AG23" s="20">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="AH23" s="18" t="n"/>
       <c r="AI23" s="19">
-        <f>IF(AH23="","",IF(AH23="NE","",IF(AH23="0",0,IF(AH23="1",0.5,IF(AH23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AH23="","",IF(AH23="NE","",(IFERROR(IF(ISNUMBER(AH23),AH23,VALUE(AH23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AJ23" s="20">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="AK23" s="18" t="n"/>
       <c r="AL23" s="19">
-        <f>IF(AK23="","",IF(AK23="NE","",IF(AK23="0",0,IF(AK23="1",0.5,IF(AK23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AK23="","",IF(AK23="NE","",(IFERROR(IF(ISNUMBER(AK23),AK23,VALUE(AK23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AM23" s="20">
@@ -7490,7 +7490,7 @@
       </c>
       <c r="AN23" s="18" t="n"/>
       <c r="AO23" s="19">
-        <f>IF(AN23="","",IF(AN23="NE","",IF(AN23="0",0,IF(AN23="1",0.5,IF(AN23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AN23="","",IF(AN23="NE","",(IFERROR(IF(ISNUMBER(AN23),AN23,VALUE(AN23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AP23" s="20">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="AQ23" s="18" t="n"/>
       <c r="AR23" s="19">
-        <f>IF(AQ23="","",IF(AQ23="NE","",IF(AQ23="0",0,IF(AQ23="1",0.5,IF(AQ23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AQ23="","",IF(AQ23="NE","",(IFERROR(IF(ISNUMBER(AQ23),AQ23,VALUE(AQ23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AS23" s="20">
@@ -7508,7 +7508,7 @@
       </c>
       <c r="AT23" s="18" t="n"/>
       <c r="AU23" s="19">
-        <f>IF(AT23="","",IF(AT23="NE","",IF(AT23="0",0,IF(AT23="1",0.5,IF(AT23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AT23="","",IF(AT23="NE","",(IFERROR(IF(ISNUMBER(AT23),AT23,VALUE(AT23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AV23" s="20">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="AW23" s="18" t="n"/>
       <c r="AX23" s="19">
-        <f>IF(AW23="","",IF(AW23="NE","",IF(AW23="0",0,IF(AW23="1",0.5,IF(AW23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AW23="","",IF(AW23="NE","",(IFERROR(IF(ISNUMBER(AW23),AW23,VALUE(AW23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="AY23" s="20">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="AZ23" s="18" t="n"/>
       <c r="BA23" s="19">
-        <f>IF(AZ23="","",IF(AZ23="NE","",IF(AZ23="0",0,IF(AZ23="1",0.5,IF(AZ23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(AZ23="","",IF(AZ23="NE","",(IFERROR(IF(ISNUMBER(AZ23),AZ23,VALUE(AZ23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BB23" s="20">
@@ -7535,7 +7535,7 @@
       </c>
       <c r="BC23" s="18" t="n"/>
       <c r="BD23" s="19">
-        <f>IF(BC23="","",IF(BC23="NE","",IF(BC23="0",0,IF(BC23="1",0.5,IF(BC23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BC23="","",IF(BC23="NE","",(IFERROR(IF(ISNUMBER(BC23),BC23,VALUE(BC23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BE23" s="20">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="BF23" s="18" t="n"/>
       <c r="BG23" s="19">
-        <f>IF(BF23="","",IF(BF23="NE","",IF(BF23="0",0,IF(BF23="1",0.5,IF(BF23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BF23="","",IF(BF23="NE","",(IFERROR(IF(ISNUMBER(BF23),BF23,VALUE(BF23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BH23" s="20">
@@ -7553,7 +7553,7 @@
       </c>
       <c r="BI23" s="18" t="n"/>
       <c r="BJ23" s="19">
-        <f>IF(BI23="","",IF(BI23="NE","",IF(BI23="0",0,IF(BI23="1",0.5,IF(BI23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BI23="","",IF(BI23="NE","",(IFERROR(IF(ISNUMBER(BI23),BI23,VALUE(BI23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BK23" s="20">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="BL23" s="18" t="n"/>
       <c r="BM23" s="19">
-        <f>IF(BL23="","",IF(BL23="NE","",IF(BL23="0",0,IF(BL23="1",0.5,IF(BL23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BL23="","",IF(BL23="NE","",(IFERROR(IF(ISNUMBER(BL23),BL23,VALUE(BL23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BN23" s="20">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="BO23" s="18" t="n"/>
       <c r="BP23" s="19">
-        <f>IF(BO23="","",IF(BO23="NE","",IF(BO23="0",0,IF(BO23="1",0.5,IF(BO23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BO23="","",IF(BO23="NE","",(IFERROR(IF(ISNUMBER(BO23),BO23,VALUE(BO23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BQ23" s="20">
@@ -7580,7 +7580,7 @@
       </c>
       <c r="BR23" s="18" t="n"/>
       <c r="BS23" s="19">
-        <f>IF(BR23="","",IF(BR23="NE","",IF(BR23="0",0,IF(BR23="1",0.5,IF(BR23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BR23="","",IF(BR23="NE","",(IFERROR(IF(ISNUMBER(BR23),BR23,VALUE(BR23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BT23" s="20">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="BU23" s="18" t="n"/>
       <c r="BV23" s="19">
-        <f>IF(BU23="","",IF(BU23="NE","",IF(BU23="0",0,IF(BU23="1",0.5,IF(BU23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BU23="","",IF(BU23="NE","",(IFERROR(IF(ISNUMBER(BU23),BU23,VALUE(BU23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BW23" s="20">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="BX23" s="18" t="n"/>
       <c r="BY23" s="19">
-        <f>IF(BX23="","",IF(BX23="NE","",IF(BX23="0",0,IF(BX23="1",0.5,IF(BX23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(BX23="","",IF(BX23="NE","",(IFERROR(IF(ISNUMBER(BX23),BX23,VALUE(BX23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="BZ23" s="20">
@@ -7607,7 +7607,7 @@
       </c>
       <c r="CA23" s="18" t="n"/>
       <c r="CB23" s="19">
-        <f>IF(CA23="","",IF(CA23="NE","",IF(CA23="0",0,IF(CA23="1",0.5,IF(CA23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(CA23="","",IF(CA23="NE","",(IFERROR(IF(ISNUMBER(CA23),CA23,VALUE(CA23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="CC23" s="20">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="CD23" s="18" t="n"/>
       <c r="CE23" s="19">
-        <f>IF(CD23="","",IF(CD23="NE","",IF(CD23="0",0,IF(CD23="1",0.5,IF(CD23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(CD23="","",IF(CD23="NE","",(IFERROR(IF(ISNUMBER(CD23),CD23,VALUE(CD23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="CF23" s="20">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="CG23" s="18" t="n"/>
       <c r="CH23" s="19">
-        <f>IF(CG23="","",IF(CG23="NE","",IF(CG23="0",0,IF(CG23="1",0.5,IF(CG23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(CG23="","",IF(CG23="NE","",(IFERROR(IF(ISNUMBER(CG23),CG23,VALUE(CG23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="CI23" s="20">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="CJ23" s="18" t="n"/>
       <c r="CK23" s="19">
-        <f>IF(CJ23="","",IF(CJ23="NE","",IF(CJ23="0",0,IF(CJ23="1",0.5,IF(CJ23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(CJ23="","",IF(CJ23="NE","",(IFERROR(IF(ISNUMBER(CJ23),CJ23,VALUE(CJ23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="CL23" s="20">
@@ -7643,7 +7643,7 @@
       </c>
       <c r="CM23" s="18" t="n"/>
       <c r="CN23" s="19">
-        <f>IF(CM23="","",IF(CM23="NE","",IF(CM23="0",0,IF(CM23="1",0.5,IF(CM23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(CM23="","",IF(CM23="NE","",(IFERROR(IF(ISNUMBER(CM23),CM23,VALUE(CM23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="CO23" s="20">
@@ -7652,7 +7652,7 @@
       </c>
       <c r="CP23" s="18" t="n"/>
       <c r="CQ23" s="19">
-        <f>IF(CP23="","",IF(CP23="NE","",IF(CP23="0",0,IF(CP23="1",0.5,IF(CP23="2",1,0)))*$F23*$F$21*20))</f>
+        <f>IF(CP23="","",IF(CP23="NE","",(IFERROR(IF(ISNUMBER(CP23),CP23,VALUE(CP23)),0)/2)*$F23*$F$21*20))</f>
         <v/>
       </c>
       <c r="CR23" s="20">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="G24" s="18" t="n"/>
       <c r="H24" s="19">
-        <f>IF(G24="","",IF(G24="NE","",IF(G24="0",0,IF(G24="1",0.5,IF(G24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(G24="","",IF(G24="NE","",(IFERROR(IF(ISNUMBER(G24),G24,VALUE(G24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="I24" s="20">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="J24" s="18" t="n"/>
       <c r="K24" s="19">
-        <f>IF(J24="","",IF(J24="NE","",IF(J24="0",0,IF(J24="1",0.5,IF(J24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(J24="","",IF(J24="NE","",(IFERROR(IF(ISNUMBER(J24),J24,VALUE(J24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="L24" s="20">
@@ -7707,7 +7707,7 @@
       </c>
       <c r="M24" s="18" t="n"/>
       <c r="N24" s="19">
-        <f>IF(M24="","",IF(M24="NE","",IF(M24="0",0,IF(M24="1",0.5,IF(M24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(M24="","",IF(M24="NE","",(IFERROR(IF(ISNUMBER(M24),M24,VALUE(M24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="O24" s="20">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="P24" s="18" t="n"/>
       <c r="Q24" s="19">
-        <f>IF(P24="","",IF(P24="NE","",IF(P24="0",0,IF(P24="1",0.5,IF(P24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(P24="","",IF(P24="NE","",(IFERROR(IF(ISNUMBER(P24),P24,VALUE(P24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="R24" s="20">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="S24" s="18" t="n"/>
       <c r="T24" s="19">
-        <f>IF(S24="","",IF(S24="NE","",IF(S24="0",0,IF(S24="1",0.5,IF(S24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(S24="","",IF(S24="NE","",(IFERROR(IF(ISNUMBER(S24),S24,VALUE(S24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="U24" s="20">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="V24" s="18" t="n"/>
       <c r="W24" s="19">
-        <f>IF(V24="","",IF(V24="NE","",IF(V24="0",0,IF(V24="1",0.5,IF(V24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(V24="","",IF(V24="NE","",(IFERROR(IF(ISNUMBER(V24),V24,VALUE(V24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="X24" s="20">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="Y24" s="18" t="n"/>
       <c r="Z24" s="19">
-        <f>IF(Y24="","",IF(Y24="NE","",IF(Y24="0",0,IF(Y24="1",0.5,IF(Y24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(Y24="","",IF(Y24="NE","",(IFERROR(IF(ISNUMBER(Y24),Y24,VALUE(Y24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AA24" s="20">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="AB24" s="18" t="n"/>
       <c r="AC24" s="19">
-        <f>IF(AB24="","",IF(AB24="NE","",IF(AB24="0",0,IF(AB24="1",0.5,IF(AB24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AB24="","",IF(AB24="NE","",(IFERROR(IF(ISNUMBER(AB24),AB24,VALUE(AB24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AD24" s="20">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="AE24" s="18" t="n"/>
       <c r="AF24" s="19">
-        <f>IF(AE24="","",IF(AE24="NE","",IF(AE24="0",0,IF(AE24="1",0.5,IF(AE24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AE24="","",IF(AE24="NE","",(IFERROR(IF(ISNUMBER(AE24),AE24,VALUE(AE24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AG24" s="20">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="AH24" s="18" t="n"/>
       <c r="AI24" s="19">
-        <f>IF(AH24="","",IF(AH24="NE","",IF(AH24="0",0,IF(AH24="1",0.5,IF(AH24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AH24="","",IF(AH24="NE","",(IFERROR(IF(ISNUMBER(AH24),AH24,VALUE(AH24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AJ24" s="20">
@@ -7779,7 +7779,7 @@
       </c>
       <c r="AK24" s="18" t="n"/>
       <c r="AL24" s="19">
-        <f>IF(AK24="","",IF(AK24="NE","",IF(AK24="0",0,IF(AK24="1",0.5,IF(AK24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AK24="","",IF(AK24="NE","",(IFERROR(IF(ISNUMBER(AK24),AK24,VALUE(AK24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AM24" s="20">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="AN24" s="18" t="n"/>
       <c r="AO24" s="19">
-        <f>IF(AN24="","",IF(AN24="NE","",IF(AN24="0",0,IF(AN24="1",0.5,IF(AN24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AN24="","",IF(AN24="NE","",(IFERROR(IF(ISNUMBER(AN24),AN24,VALUE(AN24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AP24" s="20">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="AQ24" s="18" t="n"/>
       <c r="AR24" s="19">
-        <f>IF(AQ24="","",IF(AQ24="NE","",IF(AQ24="0",0,IF(AQ24="1",0.5,IF(AQ24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AQ24="","",IF(AQ24="NE","",(IFERROR(IF(ISNUMBER(AQ24),AQ24,VALUE(AQ24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AS24" s="20">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="AT24" s="18" t="n"/>
       <c r="AU24" s="19">
-        <f>IF(AT24="","",IF(AT24="NE","",IF(AT24="0",0,IF(AT24="1",0.5,IF(AT24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AT24="","",IF(AT24="NE","",(IFERROR(IF(ISNUMBER(AT24),AT24,VALUE(AT24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AV24" s="20">
@@ -7815,7 +7815,7 @@
       </c>
       <c r="AW24" s="18" t="n"/>
       <c r="AX24" s="19">
-        <f>IF(AW24="","",IF(AW24="NE","",IF(AW24="0",0,IF(AW24="1",0.5,IF(AW24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AW24="","",IF(AW24="NE","",(IFERROR(IF(ISNUMBER(AW24),AW24,VALUE(AW24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="AY24" s="20">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="AZ24" s="18" t="n"/>
       <c r="BA24" s="19">
-        <f>IF(AZ24="","",IF(AZ24="NE","",IF(AZ24="0",0,IF(AZ24="1",0.5,IF(AZ24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(AZ24="","",IF(AZ24="NE","",(IFERROR(IF(ISNUMBER(AZ24),AZ24,VALUE(AZ24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BB24" s="20">
@@ -7833,7 +7833,7 @@
       </c>
       <c r="BC24" s="18" t="n"/>
       <c r="BD24" s="19">
-        <f>IF(BC24="","",IF(BC24="NE","",IF(BC24="0",0,IF(BC24="1",0.5,IF(BC24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BC24="","",IF(BC24="NE","",(IFERROR(IF(ISNUMBER(BC24),BC24,VALUE(BC24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BE24" s="20">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="BF24" s="18" t="n"/>
       <c r="BG24" s="19">
-        <f>IF(BF24="","",IF(BF24="NE","",IF(BF24="0",0,IF(BF24="1",0.5,IF(BF24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BF24="","",IF(BF24="NE","",(IFERROR(IF(ISNUMBER(BF24),BF24,VALUE(BF24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BH24" s="20">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="BI24" s="18" t="n"/>
       <c r="BJ24" s="19">
-        <f>IF(BI24="","",IF(BI24="NE","",IF(BI24="0",0,IF(BI24="1",0.5,IF(BI24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BI24="","",IF(BI24="NE","",(IFERROR(IF(ISNUMBER(BI24),BI24,VALUE(BI24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BK24" s="20">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="BL24" s="18" t="n"/>
       <c r="BM24" s="19">
-        <f>IF(BL24="","",IF(BL24="NE","",IF(BL24="0",0,IF(BL24="1",0.5,IF(BL24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BL24="","",IF(BL24="NE","",(IFERROR(IF(ISNUMBER(BL24),BL24,VALUE(BL24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BN24" s="20">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="BO24" s="18" t="n"/>
       <c r="BP24" s="19">
-        <f>IF(BO24="","",IF(BO24="NE","",IF(BO24="0",0,IF(BO24="1",0.5,IF(BO24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BO24="","",IF(BO24="NE","",(IFERROR(IF(ISNUMBER(BO24),BO24,VALUE(BO24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BQ24" s="20">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="BR24" s="18" t="n"/>
       <c r="BS24" s="19">
-        <f>IF(BR24="","",IF(BR24="NE","",IF(BR24="0",0,IF(BR24="1",0.5,IF(BR24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BR24="","",IF(BR24="NE","",(IFERROR(IF(ISNUMBER(BR24),BR24,VALUE(BR24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BT24" s="20">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="BU24" s="18" t="n"/>
       <c r="BV24" s="19">
-        <f>IF(BU24="","",IF(BU24="NE","",IF(BU24="0",0,IF(BU24="1",0.5,IF(BU24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BU24="","",IF(BU24="NE","",(IFERROR(IF(ISNUMBER(BU24),BU24,VALUE(BU24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BW24" s="20">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="BX24" s="18" t="n"/>
       <c r="BY24" s="19">
-        <f>IF(BX24="","",IF(BX24="NE","",IF(BX24="0",0,IF(BX24="1",0.5,IF(BX24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(BX24="","",IF(BX24="NE","",(IFERROR(IF(ISNUMBER(BX24),BX24,VALUE(BX24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="BZ24" s="20">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="CA24" s="18" t="n"/>
       <c r="CB24" s="19">
-        <f>IF(CA24="","",IF(CA24="NE","",IF(CA24="0",0,IF(CA24="1",0.5,IF(CA24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(CA24="","",IF(CA24="NE","",(IFERROR(IF(ISNUMBER(CA24),CA24,VALUE(CA24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="CC24" s="20">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="CD24" s="18" t="n"/>
       <c r="CE24" s="19">
-        <f>IF(CD24="","",IF(CD24="NE","",IF(CD24="0",0,IF(CD24="1",0.5,IF(CD24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(CD24="","",IF(CD24="NE","",(IFERROR(IF(ISNUMBER(CD24),CD24,VALUE(CD24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="CF24" s="20">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="CG24" s="18" t="n"/>
       <c r="CH24" s="19">
-        <f>IF(CG24="","",IF(CG24="NE","",IF(CG24="0",0,IF(CG24="1",0.5,IF(CG24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(CG24="","",IF(CG24="NE","",(IFERROR(IF(ISNUMBER(CG24),CG24,VALUE(CG24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="CI24" s="20">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="CJ24" s="18" t="n"/>
       <c r="CK24" s="19">
-        <f>IF(CJ24="","",IF(CJ24="NE","",IF(CJ24="0",0,IF(CJ24="1",0.5,IF(CJ24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(CJ24="","",IF(CJ24="NE","",(IFERROR(IF(ISNUMBER(CJ24),CJ24,VALUE(CJ24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="CL24" s="20">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="CM24" s="18" t="n"/>
       <c r="CN24" s="19">
-        <f>IF(CM24="","",IF(CM24="NE","",IF(CM24="0",0,IF(CM24="1",0.5,IF(CM24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(CM24="","",IF(CM24="NE","",(IFERROR(IF(ISNUMBER(CM24),CM24,VALUE(CM24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="CO24" s="20">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="CP24" s="18" t="n"/>
       <c r="CQ24" s="19">
-        <f>IF(CP24="","",IF(CP24="NE","",IF(CP24="0",0,IF(CP24="1",0.5,IF(CP24="2",1,0)))*$F24*$F$21*20))</f>
+        <f>IF(CP24="","",IF(CP24="NE","",(IFERROR(IF(ISNUMBER(CP24),CP24,VALUE(CP24)),0)/2)*$F24*$F$21*20))</f>
         <v/>
       </c>
       <c r="CR24" s="20">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="G25" s="18" t="n"/>
       <c r="H25" s="19">
-        <f>IF(G25="","",IF(G25="NE","",IF(G25="0",0,IF(G25="1",0.5,IF(G25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(G25="","",IF(G25="NE","",(IFERROR(IF(ISNUMBER(G25),G25,VALUE(G25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="I25" s="20">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="J25" s="18" t="n"/>
       <c r="K25" s="19">
-        <f>IF(J25="","",IF(J25="NE","",IF(J25="0",0,IF(J25="1",0.5,IF(J25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(J25="","",IF(J25="NE","",(IFERROR(IF(ISNUMBER(J25),J25,VALUE(J25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="L25" s="20">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="M25" s="18" t="n"/>
       <c r="N25" s="19">
-        <f>IF(M25="","",IF(M25="NE","",IF(M25="0",0,IF(M25="1",0.5,IF(M25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(M25="","",IF(M25="NE","",(IFERROR(IF(ISNUMBER(M25),M25,VALUE(M25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="O25" s="20">
@@ -8014,7 +8014,7 @@
       </c>
       <c r="P25" s="18" t="n"/>
       <c r="Q25" s="19">
-        <f>IF(P25="","",IF(P25="NE","",IF(P25="0",0,IF(P25="1",0.5,IF(P25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(P25="","",IF(P25="NE","",(IFERROR(IF(ISNUMBER(P25),P25,VALUE(P25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="R25" s="20">
@@ -8023,7 +8023,7 @@
       </c>
       <c r="S25" s="18" t="n"/>
       <c r="T25" s="19">
-        <f>IF(S25="","",IF(S25="NE","",IF(S25="0",0,IF(S25="1",0.5,IF(S25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(S25="","",IF(S25="NE","",(IFERROR(IF(ISNUMBER(S25),S25,VALUE(S25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="U25" s="20">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="V25" s="18" t="n"/>
       <c r="W25" s="19">
-        <f>IF(V25="","",IF(V25="NE","",IF(V25="0",0,IF(V25="1",0.5,IF(V25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(V25="","",IF(V25="NE","",(IFERROR(IF(ISNUMBER(V25),V25,VALUE(V25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="X25" s="20">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="Y25" s="18" t="n"/>
       <c r="Z25" s="19">
-        <f>IF(Y25="","",IF(Y25="NE","",IF(Y25="0",0,IF(Y25="1",0.5,IF(Y25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(Y25="","",IF(Y25="NE","",(IFERROR(IF(ISNUMBER(Y25),Y25,VALUE(Y25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AA25" s="20">
@@ -8050,7 +8050,7 @@
       </c>
       <c r="AB25" s="18" t="n"/>
       <c r="AC25" s="19">
-        <f>IF(AB25="","",IF(AB25="NE","",IF(AB25="0",0,IF(AB25="1",0.5,IF(AB25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AB25="","",IF(AB25="NE","",(IFERROR(IF(ISNUMBER(AB25),AB25,VALUE(AB25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AD25" s="20">
@@ -8059,7 +8059,7 @@
       </c>
       <c r="AE25" s="18" t="n"/>
       <c r="AF25" s="19">
-        <f>IF(AE25="","",IF(AE25="NE","",IF(AE25="0",0,IF(AE25="1",0.5,IF(AE25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AE25="","",IF(AE25="NE","",(IFERROR(IF(ISNUMBER(AE25),AE25,VALUE(AE25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AG25" s="20">
@@ -8068,7 +8068,7 @@
       </c>
       <c r="AH25" s="18" t="n"/>
       <c r="AI25" s="19">
-        <f>IF(AH25="","",IF(AH25="NE","",IF(AH25="0",0,IF(AH25="1",0.5,IF(AH25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AH25="","",IF(AH25="NE","",(IFERROR(IF(ISNUMBER(AH25),AH25,VALUE(AH25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AJ25" s="20">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AK25" s="18" t="n"/>
       <c r="AL25" s="19">
-        <f>IF(AK25="","",IF(AK25="NE","",IF(AK25="0",0,IF(AK25="1",0.5,IF(AK25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AK25="","",IF(AK25="NE","",(IFERROR(IF(ISNUMBER(AK25),AK25,VALUE(AK25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AM25" s="20">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="AN25" s="18" t="n"/>
       <c r="AO25" s="19">
-        <f>IF(AN25="","",IF(AN25="NE","",IF(AN25="0",0,IF(AN25="1",0.5,IF(AN25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AN25="","",IF(AN25="NE","",(IFERROR(IF(ISNUMBER(AN25),AN25,VALUE(AN25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AP25" s="20">
@@ -8095,7 +8095,7 @@
       </c>
       <c r="AQ25" s="18" t="n"/>
       <c r="AR25" s="19">
-        <f>IF(AQ25="","",IF(AQ25="NE","",IF(AQ25="0",0,IF(AQ25="1",0.5,IF(AQ25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AQ25="","",IF(AQ25="NE","",(IFERROR(IF(ISNUMBER(AQ25),AQ25,VALUE(AQ25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AS25" s="20">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AT25" s="18" t="n"/>
       <c r="AU25" s="19">
-        <f>IF(AT25="","",IF(AT25="NE","",IF(AT25="0",0,IF(AT25="1",0.5,IF(AT25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AT25="","",IF(AT25="NE","",(IFERROR(IF(ISNUMBER(AT25),AT25,VALUE(AT25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AV25" s="20">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="AW25" s="18" t="n"/>
       <c r="AX25" s="19">
-        <f>IF(AW25="","",IF(AW25="NE","",IF(AW25="0",0,IF(AW25="1",0.5,IF(AW25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AW25="","",IF(AW25="NE","",(IFERROR(IF(ISNUMBER(AW25),AW25,VALUE(AW25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="AY25" s="20">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="AZ25" s="18" t="n"/>
       <c r="BA25" s="19">
-        <f>IF(AZ25="","",IF(AZ25="NE","",IF(AZ25="0",0,IF(AZ25="1",0.5,IF(AZ25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(AZ25="","",IF(AZ25="NE","",(IFERROR(IF(ISNUMBER(AZ25),AZ25,VALUE(AZ25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BB25" s="20">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="BC25" s="18" t="n"/>
       <c r="BD25" s="19">
-        <f>IF(BC25="","",IF(BC25="NE","",IF(BC25="0",0,IF(BC25="1",0.5,IF(BC25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BC25="","",IF(BC25="NE","",(IFERROR(IF(ISNUMBER(BC25),BC25,VALUE(BC25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BE25" s="20">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="BF25" s="18" t="n"/>
       <c r="BG25" s="19">
-        <f>IF(BF25="","",IF(BF25="NE","",IF(BF25="0",0,IF(BF25="1",0.5,IF(BF25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BF25="","",IF(BF25="NE","",(IFERROR(IF(ISNUMBER(BF25),BF25,VALUE(BF25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BH25" s="20">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="BI25" s="18" t="n"/>
       <c r="BJ25" s="19">
-        <f>IF(BI25="","",IF(BI25="NE","",IF(BI25="0",0,IF(BI25="1",0.5,IF(BI25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BI25="","",IF(BI25="NE","",(IFERROR(IF(ISNUMBER(BI25),BI25,VALUE(BI25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BK25" s="20">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="BL25" s="18" t="n"/>
       <c r="BM25" s="19">
-        <f>IF(BL25="","",IF(BL25="NE","",IF(BL25="0",0,IF(BL25="1",0.5,IF(BL25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BL25="","",IF(BL25="NE","",(IFERROR(IF(ISNUMBER(BL25),BL25,VALUE(BL25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BN25" s="20">
@@ -8167,7 +8167,7 @@
       </c>
       <c r="BO25" s="18" t="n"/>
       <c r="BP25" s="19">
-        <f>IF(BO25="","",IF(BO25="NE","",IF(BO25="0",0,IF(BO25="1",0.5,IF(BO25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BO25="","",IF(BO25="NE","",(IFERROR(IF(ISNUMBER(BO25),BO25,VALUE(BO25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BQ25" s="20">
@@ -8176,7 +8176,7 @@
       </c>
       <c r="BR25" s="18" t="n"/>
       <c r="BS25" s="19">
-        <f>IF(BR25="","",IF(BR25="NE","",IF(BR25="0",0,IF(BR25="1",0.5,IF(BR25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BR25="","",IF(BR25="NE","",(IFERROR(IF(ISNUMBER(BR25),BR25,VALUE(BR25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BT25" s="20">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="BU25" s="18" t="n"/>
       <c r="BV25" s="19">
-        <f>IF(BU25="","",IF(BU25="NE","",IF(BU25="0",0,IF(BU25="1",0.5,IF(BU25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BU25="","",IF(BU25="NE","",(IFERROR(IF(ISNUMBER(BU25),BU25,VALUE(BU25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BW25" s="20">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="BX25" s="18" t="n"/>
       <c r="BY25" s="19">
-        <f>IF(BX25="","",IF(BX25="NE","",IF(BX25="0",0,IF(BX25="1",0.5,IF(BX25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(BX25="","",IF(BX25="NE","",(IFERROR(IF(ISNUMBER(BX25),BX25,VALUE(BX25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="BZ25" s="20">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="CA25" s="18" t="n"/>
       <c r="CB25" s="19">
-        <f>IF(CA25="","",IF(CA25="NE","",IF(CA25="0",0,IF(CA25="1",0.5,IF(CA25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(CA25="","",IF(CA25="NE","",(IFERROR(IF(ISNUMBER(CA25),CA25,VALUE(CA25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="CC25" s="20">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="CD25" s="18" t="n"/>
       <c r="CE25" s="19">
-        <f>IF(CD25="","",IF(CD25="NE","",IF(CD25="0",0,IF(CD25="1",0.5,IF(CD25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(CD25="","",IF(CD25="NE","",(IFERROR(IF(ISNUMBER(CD25),CD25,VALUE(CD25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="CF25" s="20">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="CG25" s="18" t="n"/>
       <c r="CH25" s="19">
-        <f>IF(CG25="","",IF(CG25="NE","",IF(CG25="0",0,IF(CG25="1",0.5,IF(CG25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(CG25="","",IF(CG25="NE","",(IFERROR(IF(ISNUMBER(CG25),CG25,VALUE(CG25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="CI25" s="20">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="CJ25" s="18" t="n"/>
       <c r="CK25" s="19">
-        <f>IF(CJ25="","",IF(CJ25="NE","",IF(CJ25="0",0,IF(CJ25="1",0.5,IF(CJ25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(CJ25="","",IF(CJ25="NE","",(IFERROR(IF(ISNUMBER(CJ25),CJ25,VALUE(CJ25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="CL25" s="20">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="CM25" s="18" t="n"/>
       <c r="CN25" s="19">
-        <f>IF(CM25="","",IF(CM25="NE","",IF(CM25="0",0,IF(CM25="1",0.5,IF(CM25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(CM25="","",IF(CM25="NE","",(IFERROR(IF(ISNUMBER(CM25),CM25,VALUE(CM25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="CO25" s="20">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="CP25" s="18" t="n"/>
       <c r="CQ25" s="19">
-        <f>IF(CP25="","",IF(CP25="NE","",IF(CP25="0",0,IF(CP25="1",0.5,IF(CP25="2",1,0)))*$F25*$F$21*20))</f>
+        <f>IF(CP25="","",IF(CP25="NE","",(IFERROR(IF(ISNUMBER(CP25),CP25,VALUE(CP25)),0)/2)*$F25*$F$21*20))</f>
         <v/>
       </c>
       <c r="CR25" s="20">
@@ -8397,7 +8397,7 @@
       </c>
       <c r="G27" s="18" t="n"/>
       <c r="H27" s="19">
-        <f>IF(G27="","",IF(G27="NE","",IF(G27="0",0,IF(G27="1",0.5,IF(G27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(G27="","",IF(G27="NE","",(IFERROR(IF(ISNUMBER(G27),G27,VALUE(G27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="I27" s="20">
@@ -8406,7 +8406,7 @@
       </c>
       <c r="J27" s="18" t="n"/>
       <c r="K27" s="19">
-        <f>IF(J27="","",IF(J27="NE","",IF(J27="0",0,IF(J27="1",0.5,IF(J27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(J27="","",IF(J27="NE","",(IFERROR(IF(ISNUMBER(J27),J27,VALUE(J27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="L27" s="20">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="M27" s="18" t="n"/>
       <c r="N27" s="19">
-        <f>IF(M27="","",IF(M27="NE","",IF(M27="0",0,IF(M27="1",0.5,IF(M27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(M27="","",IF(M27="NE","",(IFERROR(IF(ISNUMBER(M27),M27,VALUE(M27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="O27" s="20">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="P27" s="18" t="n"/>
       <c r="Q27" s="19">
-        <f>IF(P27="","",IF(P27="NE","",IF(P27="0",0,IF(P27="1",0.5,IF(P27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(P27="","",IF(P27="NE","",(IFERROR(IF(ISNUMBER(P27),P27,VALUE(P27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="R27" s="20">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="S27" s="18" t="n"/>
       <c r="T27" s="19">
-        <f>IF(S27="","",IF(S27="NE","",IF(S27="0",0,IF(S27="1",0.5,IF(S27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(S27="","",IF(S27="NE","",(IFERROR(IF(ISNUMBER(S27),S27,VALUE(S27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="U27" s="20">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="V27" s="18" t="n"/>
       <c r="W27" s="19">
-        <f>IF(V27="","",IF(V27="NE","",IF(V27="0",0,IF(V27="1",0.5,IF(V27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(V27="","",IF(V27="NE","",(IFERROR(IF(ISNUMBER(V27),V27,VALUE(V27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="X27" s="20">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="Y27" s="18" t="n"/>
       <c r="Z27" s="19">
-        <f>IF(Y27="","",IF(Y27="NE","",IF(Y27="0",0,IF(Y27="1",0.5,IF(Y27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(Y27="","",IF(Y27="NE","",(IFERROR(IF(ISNUMBER(Y27),Y27,VALUE(Y27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AA27" s="20">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="AB27" s="18" t="n"/>
       <c r="AC27" s="19">
-        <f>IF(AB27="","",IF(AB27="NE","",IF(AB27="0",0,IF(AB27="1",0.5,IF(AB27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AB27="","",IF(AB27="NE","",(IFERROR(IF(ISNUMBER(AB27),AB27,VALUE(AB27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AD27" s="20">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="AE27" s="18" t="n"/>
       <c r="AF27" s="19">
-        <f>IF(AE27="","",IF(AE27="NE","",IF(AE27="0",0,IF(AE27="1",0.5,IF(AE27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AE27="","",IF(AE27="NE","",(IFERROR(IF(ISNUMBER(AE27),AE27,VALUE(AE27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AG27" s="20">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AH27" s="18" t="n"/>
       <c r="AI27" s="19">
-        <f>IF(AH27="","",IF(AH27="NE","",IF(AH27="0",0,IF(AH27="1",0.5,IF(AH27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AH27="","",IF(AH27="NE","",(IFERROR(IF(ISNUMBER(AH27),AH27,VALUE(AH27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AJ27" s="20">
@@ -8487,7 +8487,7 @@
       </c>
       <c r="AK27" s="18" t="n"/>
       <c r="AL27" s="19">
-        <f>IF(AK27="","",IF(AK27="NE","",IF(AK27="0",0,IF(AK27="1",0.5,IF(AK27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AK27="","",IF(AK27="NE","",(IFERROR(IF(ISNUMBER(AK27),AK27,VALUE(AK27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AM27" s="20">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="AN27" s="18" t="n"/>
       <c r="AO27" s="19">
-        <f>IF(AN27="","",IF(AN27="NE","",IF(AN27="0",0,IF(AN27="1",0.5,IF(AN27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AN27="","",IF(AN27="NE","",(IFERROR(IF(ISNUMBER(AN27),AN27,VALUE(AN27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AP27" s="20">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="AQ27" s="18" t="n"/>
       <c r="AR27" s="19">
-        <f>IF(AQ27="","",IF(AQ27="NE","",IF(AQ27="0",0,IF(AQ27="1",0.5,IF(AQ27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AQ27="","",IF(AQ27="NE","",(IFERROR(IF(ISNUMBER(AQ27),AQ27,VALUE(AQ27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AS27" s="20">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="AT27" s="18" t="n"/>
       <c r="AU27" s="19">
-        <f>IF(AT27="","",IF(AT27="NE","",IF(AT27="0",0,IF(AT27="1",0.5,IF(AT27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AT27="","",IF(AT27="NE","",(IFERROR(IF(ISNUMBER(AT27),AT27,VALUE(AT27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AV27" s="20">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="AW27" s="18" t="n"/>
       <c r="AX27" s="19">
-        <f>IF(AW27="","",IF(AW27="NE","",IF(AW27="0",0,IF(AW27="1",0.5,IF(AW27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AW27="","",IF(AW27="NE","",(IFERROR(IF(ISNUMBER(AW27),AW27,VALUE(AW27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="AY27" s="20">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="AZ27" s="18" t="n"/>
       <c r="BA27" s="19">
-        <f>IF(AZ27="","",IF(AZ27="NE","",IF(AZ27="0",0,IF(AZ27="1",0.5,IF(AZ27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(AZ27="","",IF(AZ27="NE","",(IFERROR(IF(ISNUMBER(AZ27),AZ27,VALUE(AZ27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BB27" s="20">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="BC27" s="18" t="n"/>
       <c r="BD27" s="19">
-        <f>IF(BC27="","",IF(BC27="NE","",IF(BC27="0",0,IF(BC27="1",0.5,IF(BC27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BC27="","",IF(BC27="NE","",(IFERROR(IF(ISNUMBER(BC27),BC27,VALUE(BC27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BE27" s="20">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="BF27" s="18" t="n"/>
       <c r="BG27" s="19">
-        <f>IF(BF27="","",IF(BF27="NE","",IF(BF27="0",0,IF(BF27="1",0.5,IF(BF27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BF27="","",IF(BF27="NE","",(IFERROR(IF(ISNUMBER(BF27),BF27,VALUE(BF27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BH27" s="20">
@@ -8559,7 +8559,7 @@
       </c>
       <c r="BI27" s="18" t="n"/>
       <c r="BJ27" s="19">
-        <f>IF(BI27="","",IF(BI27="NE","",IF(BI27="0",0,IF(BI27="1",0.5,IF(BI27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BI27="","",IF(BI27="NE","",(IFERROR(IF(ISNUMBER(BI27),BI27,VALUE(BI27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BK27" s="20">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="BL27" s="18" t="n"/>
       <c r="BM27" s="19">
-        <f>IF(BL27="","",IF(BL27="NE","",IF(BL27="0",0,IF(BL27="1",0.5,IF(BL27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BL27="","",IF(BL27="NE","",(IFERROR(IF(ISNUMBER(BL27),BL27,VALUE(BL27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BN27" s="20">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="BO27" s="18" t="n"/>
       <c r="BP27" s="19">
-        <f>IF(BO27="","",IF(BO27="NE","",IF(BO27="0",0,IF(BO27="1",0.5,IF(BO27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BO27="","",IF(BO27="NE","",(IFERROR(IF(ISNUMBER(BO27),BO27,VALUE(BO27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BQ27" s="20">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="BR27" s="18" t="n"/>
       <c r="BS27" s="19">
-        <f>IF(BR27="","",IF(BR27="NE","",IF(BR27="0",0,IF(BR27="1",0.5,IF(BR27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BR27="","",IF(BR27="NE","",(IFERROR(IF(ISNUMBER(BR27),BR27,VALUE(BR27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BT27" s="20">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="BU27" s="18" t="n"/>
       <c r="BV27" s="19">
-        <f>IF(BU27="","",IF(BU27="NE","",IF(BU27="0",0,IF(BU27="1",0.5,IF(BU27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BU27="","",IF(BU27="NE","",(IFERROR(IF(ISNUMBER(BU27),BU27,VALUE(BU27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BW27" s="20">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="BX27" s="18" t="n"/>
       <c r="BY27" s="19">
-        <f>IF(BX27="","",IF(BX27="NE","",IF(BX27="0",0,IF(BX27="1",0.5,IF(BX27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(BX27="","",IF(BX27="NE","",(IFERROR(IF(ISNUMBER(BX27),BX27,VALUE(BX27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="BZ27" s="20">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="CA27" s="18" t="n"/>
       <c r="CB27" s="19">
-        <f>IF(CA27="","",IF(CA27="NE","",IF(CA27="0",0,IF(CA27="1",0.5,IF(CA27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(CA27="","",IF(CA27="NE","",(IFERROR(IF(ISNUMBER(CA27),CA27,VALUE(CA27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="CC27" s="20">
@@ -8622,7 +8622,7 @@
       </c>
       <c r="CD27" s="18" t="n"/>
       <c r="CE27" s="19">
-        <f>IF(CD27="","",IF(CD27="NE","",IF(CD27="0",0,IF(CD27="1",0.5,IF(CD27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(CD27="","",IF(CD27="NE","",(IFERROR(IF(ISNUMBER(CD27),CD27,VALUE(CD27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="CF27" s="20">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="CG27" s="18" t="n"/>
       <c r="CH27" s="19">
-        <f>IF(CG27="","",IF(CG27="NE","",IF(CG27="0",0,IF(CG27="1",0.5,IF(CG27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(CG27="","",IF(CG27="NE","",(IFERROR(IF(ISNUMBER(CG27),CG27,VALUE(CG27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="CI27" s="20">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="CJ27" s="18" t="n"/>
       <c r="CK27" s="19">
-        <f>IF(CJ27="","",IF(CJ27="NE","",IF(CJ27="0",0,IF(CJ27="1",0.5,IF(CJ27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(CJ27="","",IF(CJ27="NE","",(IFERROR(IF(ISNUMBER(CJ27),CJ27,VALUE(CJ27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="CL27" s="20">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="CM27" s="18" t="n"/>
       <c r="CN27" s="19">
-        <f>IF(CM27="","",IF(CM27="NE","",IF(CM27="0",0,IF(CM27="1",0.5,IF(CM27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(CM27="","",IF(CM27="NE","",(IFERROR(IF(ISNUMBER(CM27),CM27,VALUE(CM27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="CO27" s="20">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="CP27" s="18" t="n"/>
       <c r="CQ27" s="19">
-        <f>IF(CP27="","",IF(CP27="NE","",IF(CP27="0",0,IF(CP27="1",0.5,IF(CP27="2",1,0)))*$F27*$F$26*20))</f>
+        <f>IF(CP27="","",IF(CP27="NE","",(IFERROR(IF(ISNUMBER(CP27),CP27,VALUE(CP27)),0)/2)*$F27*$F$26*20))</f>
         <v/>
       </c>
       <c r="CR27" s="20">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="G28" s="18" t="n"/>
       <c r="H28" s="19">
-        <f>IF(G28="","",IF(G28="NE","",IF(G28="0",0,IF(G28="1",0.5,IF(G28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(G28="","",IF(G28="NE","",(IFERROR(IF(ISNUMBER(G28),G28,VALUE(G28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="I28" s="20">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="J28" s="18" t="n"/>
       <c r="K28" s="19">
-        <f>IF(J28="","",IF(J28="NE","",IF(J28="0",0,IF(J28="1",0.5,IF(J28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(J28="","",IF(J28="NE","",(IFERROR(IF(ISNUMBER(J28),J28,VALUE(J28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="L28" s="20">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="M28" s="18" t="n"/>
       <c r="N28" s="19">
-        <f>IF(M28="","",IF(M28="NE","",IF(M28="0",0,IF(M28="1",0.5,IF(M28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(M28="","",IF(M28="NE","",(IFERROR(IF(ISNUMBER(M28),M28,VALUE(M28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="O28" s="20">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="P28" s="18" t="n"/>
       <c r="Q28" s="19">
-        <f>IF(P28="","",IF(P28="NE","",IF(P28="0",0,IF(P28="1",0.5,IF(P28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(P28="","",IF(P28="NE","",(IFERROR(IF(ISNUMBER(P28),P28,VALUE(P28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="R28" s="20">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="S28" s="18" t="n"/>
       <c r="T28" s="19">
-        <f>IF(S28="","",IF(S28="NE","",IF(S28="0",0,IF(S28="1",0.5,IF(S28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(S28="","",IF(S28="NE","",(IFERROR(IF(ISNUMBER(S28),S28,VALUE(S28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="U28" s="20">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="V28" s="18" t="n"/>
       <c r="W28" s="19">
-        <f>IF(V28="","",IF(V28="NE","",IF(V28="0",0,IF(V28="1",0.5,IF(V28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(V28="","",IF(V28="NE","",(IFERROR(IF(ISNUMBER(V28),V28,VALUE(V28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="X28" s="20">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="Y28" s="18" t="n"/>
       <c r="Z28" s="19">
-        <f>IF(Y28="","",IF(Y28="NE","",IF(Y28="0",0,IF(Y28="1",0.5,IF(Y28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(Y28="","",IF(Y28="NE","",(IFERROR(IF(ISNUMBER(Y28),Y28,VALUE(Y28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AA28" s="20">
@@ -8758,7 +8758,7 @@
       </c>
       <c r="AB28" s="18" t="n"/>
       <c r="AC28" s="19">
-        <f>IF(AB28="","",IF(AB28="NE","",IF(AB28="0",0,IF(AB28="1",0.5,IF(AB28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AB28="","",IF(AB28="NE","",(IFERROR(IF(ISNUMBER(AB28),AB28,VALUE(AB28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AD28" s="20">
@@ -8767,7 +8767,7 @@
       </c>
       <c r="AE28" s="18" t="n"/>
       <c r="AF28" s="19">
-        <f>IF(AE28="","",IF(AE28="NE","",IF(AE28="0",0,IF(AE28="1",0.5,IF(AE28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AE28="","",IF(AE28="NE","",(IFERROR(IF(ISNUMBER(AE28),AE28,VALUE(AE28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AG28" s="20">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="AH28" s="18" t="n"/>
       <c r="AI28" s="19">
-        <f>IF(AH28="","",IF(AH28="NE","",IF(AH28="0",0,IF(AH28="1",0.5,IF(AH28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AH28="","",IF(AH28="NE","",(IFERROR(IF(ISNUMBER(AH28),AH28,VALUE(AH28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AJ28" s="20">
@@ -8785,7 +8785,7 @@
       </c>
       <c r="AK28" s="18" t="n"/>
       <c r="AL28" s="19">
-        <f>IF(AK28="","",IF(AK28="NE","",IF(AK28="0",0,IF(AK28="1",0.5,IF(AK28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AK28="","",IF(AK28="NE","",(IFERROR(IF(ISNUMBER(AK28),AK28,VALUE(AK28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AM28" s="20">
@@ -8794,7 +8794,7 @@
       </c>
       <c r="AN28" s="18" t="n"/>
       <c r="AO28" s="19">
-        <f>IF(AN28="","",IF(AN28="NE","",IF(AN28="0",0,IF(AN28="1",0.5,IF(AN28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AN28="","",IF(AN28="NE","",(IFERROR(IF(ISNUMBER(AN28),AN28,VALUE(AN28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AP28" s="20">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AQ28" s="18" t="n"/>
       <c r="AR28" s="19">
-        <f>IF(AQ28="","",IF(AQ28="NE","",IF(AQ28="0",0,IF(AQ28="1",0.5,IF(AQ28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AQ28="","",IF(AQ28="NE","",(IFERROR(IF(ISNUMBER(AQ28),AQ28,VALUE(AQ28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AS28" s="20">
@@ -8812,7 +8812,7 @@
       </c>
       <c r="AT28" s="18" t="n"/>
       <c r="AU28" s="19">
-        <f>IF(AT28="","",IF(AT28="NE","",IF(AT28="0",0,IF(AT28="1",0.5,IF(AT28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AT28="","",IF(AT28="NE","",(IFERROR(IF(ISNUMBER(AT28),AT28,VALUE(AT28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AV28" s="20">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="AW28" s="18" t="n"/>
       <c r="AX28" s="19">
-        <f>IF(AW28="","",IF(AW28="NE","",IF(AW28="0",0,IF(AW28="1",0.5,IF(AW28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AW28="","",IF(AW28="NE","",(IFERROR(IF(ISNUMBER(AW28),AW28,VALUE(AW28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="AY28" s="20">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AZ28" s="18" t="n"/>
       <c r="BA28" s="19">
-        <f>IF(AZ28="","",IF(AZ28="NE","",IF(AZ28="0",0,IF(AZ28="1",0.5,IF(AZ28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(AZ28="","",IF(AZ28="NE","",(IFERROR(IF(ISNUMBER(AZ28),AZ28,VALUE(AZ28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BB28" s="20">
@@ -8839,7 +8839,7 @@
       </c>
       <c r="BC28" s="18" t="n"/>
       <c r="BD28" s="19">
-        <f>IF(BC28="","",IF(BC28="NE","",IF(BC28="0",0,IF(BC28="1",0.5,IF(BC28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BC28="","",IF(BC28="NE","",(IFERROR(IF(ISNUMBER(BC28),BC28,VALUE(BC28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BE28" s="20">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="BF28" s="18" t="n"/>
       <c r="BG28" s="19">
-        <f>IF(BF28="","",IF(BF28="NE","",IF(BF28="0",0,IF(BF28="1",0.5,IF(BF28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BF28="","",IF(BF28="NE","",(IFERROR(IF(ISNUMBER(BF28),BF28,VALUE(BF28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BH28" s="20">
@@ -8857,7 +8857,7 @@
       </c>
       <c r="BI28" s="18" t="n"/>
       <c r="BJ28" s="19">
-        <f>IF(BI28="","",IF(BI28="NE","",IF(BI28="0",0,IF(BI28="1",0.5,IF(BI28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BI28="","",IF(BI28="NE","",(IFERROR(IF(ISNUMBER(BI28),BI28,VALUE(BI28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BK28" s="20">
@@ -8866,7 +8866,7 @@
       </c>
       <c r="BL28" s="18" t="n"/>
       <c r="BM28" s="19">
-        <f>IF(BL28="","",IF(BL28="NE","",IF(BL28="0",0,IF(BL28="1",0.5,IF(BL28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BL28="","",IF(BL28="NE","",(IFERROR(IF(ISNUMBER(BL28),BL28,VALUE(BL28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BN28" s="20">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="BO28" s="18" t="n"/>
       <c r="BP28" s="19">
-        <f>IF(BO28="","",IF(BO28="NE","",IF(BO28="0",0,IF(BO28="1",0.5,IF(BO28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BO28="","",IF(BO28="NE","",(IFERROR(IF(ISNUMBER(BO28),BO28,VALUE(BO28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BQ28" s="20">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="BR28" s="18" t="n"/>
       <c r="BS28" s="19">
-        <f>IF(BR28="","",IF(BR28="NE","",IF(BR28="0",0,IF(BR28="1",0.5,IF(BR28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BR28="","",IF(BR28="NE","",(IFERROR(IF(ISNUMBER(BR28),BR28,VALUE(BR28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BT28" s="20">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="BU28" s="18" t="n"/>
       <c r="BV28" s="19">
-        <f>IF(BU28="","",IF(BU28="NE","",IF(BU28="0",0,IF(BU28="1",0.5,IF(BU28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BU28="","",IF(BU28="NE","",(IFERROR(IF(ISNUMBER(BU28),BU28,VALUE(BU28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BW28" s="20">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="BX28" s="18" t="n"/>
       <c r="BY28" s="19">
-        <f>IF(BX28="","",IF(BX28="NE","",IF(BX28="0",0,IF(BX28="1",0.5,IF(BX28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(BX28="","",IF(BX28="NE","",(IFERROR(IF(ISNUMBER(BX28),BX28,VALUE(BX28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="BZ28" s="20">
@@ -8911,7 +8911,7 @@
       </c>
       <c r="CA28" s="18" t="n"/>
       <c r="CB28" s="19">
-        <f>IF(CA28="","",IF(CA28="NE","",IF(CA28="0",0,IF(CA28="1",0.5,IF(CA28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(CA28="","",IF(CA28="NE","",(IFERROR(IF(ISNUMBER(CA28),CA28,VALUE(CA28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="CC28" s="20">
@@ -8920,7 +8920,7 @@
       </c>
       <c r="CD28" s="18" t="n"/>
       <c r="CE28" s="19">
-        <f>IF(CD28="","",IF(CD28="NE","",IF(CD28="0",0,IF(CD28="1",0.5,IF(CD28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(CD28="","",IF(CD28="NE","",(IFERROR(IF(ISNUMBER(CD28),CD28,VALUE(CD28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="CF28" s="20">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="CG28" s="18" t="n"/>
       <c r="CH28" s="19">
-        <f>IF(CG28="","",IF(CG28="NE","",IF(CG28="0",0,IF(CG28="1",0.5,IF(CG28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(CG28="","",IF(CG28="NE","",(IFERROR(IF(ISNUMBER(CG28),CG28,VALUE(CG28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="CI28" s="20">
@@ -8938,7 +8938,7 @@
       </c>
       <c r="CJ28" s="18" t="n"/>
       <c r="CK28" s="19">
-        <f>IF(CJ28="","",IF(CJ28="NE","",IF(CJ28="0",0,IF(CJ28="1",0.5,IF(CJ28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(CJ28="","",IF(CJ28="NE","",(IFERROR(IF(ISNUMBER(CJ28),CJ28,VALUE(CJ28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="CL28" s="20">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="CM28" s="18" t="n"/>
       <c r="CN28" s="19">
-        <f>IF(CM28="","",IF(CM28="NE","",IF(CM28="0",0,IF(CM28="1",0.5,IF(CM28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(CM28="","",IF(CM28="NE","",(IFERROR(IF(ISNUMBER(CM28),CM28,VALUE(CM28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="CO28" s="20">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="CP28" s="18" t="n"/>
       <c r="CQ28" s="19">
-        <f>IF(CP28="","",IF(CP28="NE","",IF(CP28="0",0,IF(CP28="1",0.5,IF(CP28="2",1,0)))*$F28*$F$26*20))</f>
+        <f>IF(CP28="","",IF(CP28="NE","",(IFERROR(IF(ISNUMBER(CP28),CP28,VALUE(CP28)),0)/2)*$F28*$F$26*20))</f>
         <v/>
       </c>
       <c r="CR28" s="20">
@@ -8993,7 +8993,7 @@
       </c>
       <c r="G29" s="18" t="n"/>
       <c r="H29" s="19">
-        <f>IF(G29="","",IF(G29="NE","",IF(G29="0",0,IF(G29="1",0.5,IF(G29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(G29="","",IF(G29="NE","",(IFERROR(IF(ISNUMBER(G29),G29,VALUE(G29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="I29" s="20">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="J29" s="18" t="n"/>
       <c r="K29" s="19">
-        <f>IF(J29="","",IF(J29="NE","",IF(J29="0",0,IF(J29="1",0.5,IF(J29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(J29="","",IF(J29="NE","",(IFERROR(IF(ISNUMBER(J29),J29,VALUE(J29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="L29" s="20">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="M29" s="18" t="n"/>
       <c r="N29" s="19">
-        <f>IF(M29="","",IF(M29="NE","",IF(M29="0",0,IF(M29="1",0.5,IF(M29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(M29="","",IF(M29="NE","",(IFERROR(IF(ISNUMBER(M29),M29,VALUE(M29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="O29" s="20">
@@ -9020,7 +9020,7 @@
       </c>
       <c r="P29" s="18" t="n"/>
       <c r="Q29" s="19">
-        <f>IF(P29="","",IF(P29="NE","",IF(P29="0",0,IF(P29="1",0.5,IF(P29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(P29="","",IF(P29="NE","",(IFERROR(IF(ISNUMBER(P29),P29,VALUE(P29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="R29" s="20">
@@ -9029,7 +9029,7 @@
       </c>
       <c r="S29" s="18" t="n"/>
       <c r="T29" s="19">
-        <f>IF(S29="","",IF(S29="NE","",IF(S29="0",0,IF(S29="1",0.5,IF(S29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(S29="","",IF(S29="NE","",(IFERROR(IF(ISNUMBER(S29),S29,VALUE(S29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="U29" s="20">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="V29" s="18" t="n"/>
       <c r="W29" s="19">
-        <f>IF(V29="","",IF(V29="NE","",IF(V29="0",0,IF(V29="1",0.5,IF(V29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(V29="","",IF(V29="NE","",(IFERROR(IF(ISNUMBER(V29),V29,VALUE(V29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="X29" s="20">
@@ -9047,7 +9047,7 @@
       </c>
       <c r="Y29" s="18" t="n"/>
       <c r="Z29" s="19">
-        <f>IF(Y29="","",IF(Y29="NE","",IF(Y29="0",0,IF(Y29="1",0.5,IF(Y29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(Y29="","",IF(Y29="NE","",(IFERROR(IF(ISNUMBER(Y29),Y29,VALUE(Y29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AA29" s="20">
@@ -9056,7 +9056,7 @@
       </c>
       <c r="AB29" s="18" t="n"/>
       <c r="AC29" s="19">
-        <f>IF(AB29="","",IF(AB29="NE","",IF(AB29="0",0,IF(AB29="1",0.5,IF(AB29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AB29="","",IF(AB29="NE","",(IFERROR(IF(ISNUMBER(AB29),AB29,VALUE(AB29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AD29" s="20">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="AE29" s="18" t="n"/>
       <c r="AF29" s="19">
-        <f>IF(AE29="","",IF(AE29="NE","",IF(AE29="0",0,IF(AE29="1",0.5,IF(AE29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AE29="","",IF(AE29="NE","",(IFERROR(IF(ISNUMBER(AE29),AE29,VALUE(AE29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AG29" s="20">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="AH29" s="18" t="n"/>
       <c r="AI29" s="19">
-        <f>IF(AH29="","",IF(AH29="NE","",IF(AH29="0",0,IF(AH29="1",0.5,IF(AH29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AH29="","",IF(AH29="NE","",(IFERROR(IF(ISNUMBER(AH29),AH29,VALUE(AH29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AJ29" s="20">
@@ -9083,7 +9083,7 @@
       </c>
       <c r="AK29" s="18" t="n"/>
       <c r="AL29" s="19">
-        <f>IF(AK29="","",IF(AK29="NE","",IF(AK29="0",0,IF(AK29="1",0.5,IF(AK29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AK29="","",IF(AK29="NE","",(IFERROR(IF(ISNUMBER(AK29),AK29,VALUE(AK29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AM29" s="20">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="AN29" s="18" t="n"/>
       <c r="AO29" s="19">
-        <f>IF(AN29="","",IF(AN29="NE","",IF(AN29="0",0,IF(AN29="1",0.5,IF(AN29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AN29="","",IF(AN29="NE","",(IFERROR(IF(ISNUMBER(AN29),AN29,VALUE(AN29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AP29" s="20">
@@ -9101,7 +9101,7 @@
       </c>
       <c r="AQ29" s="18" t="n"/>
       <c r="AR29" s="19">
-        <f>IF(AQ29="","",IF(AQ29="NE","",IF(AQ29="0",0,IF(AQ29="1",0.5,IF(AQ29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AQ29="","",IF(AQ29="NE","",(IFERROR(IF(ISNUMBER(AQ29),AQ29,VALUE(AQ29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AS29" s="20">
@@ -9110,7 +9110,7 @@
       </c>
       <c r="AT29" s="18" t="n"/>
       <c r="AU29" s="19">
-        <f>IF(AT29="","",IF(AT29="NE","",IF(AT29="0",0,IF(AT29="1",0.5,IF(AT29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AT29="","",IF(AT29="NE","",(IFERROR(IF(ISNUMBER(AT29),AT29,VALUE(AT29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AV29" s="20">
@@ -9119,7 +9119,7 @@
       </c>
       <c r="AW29" s="18" t="n"/>
       <c r="AX29" s="19">
-        <f>IF(AW29="","",IF(AW29="NE","",IF(AW29="0",0,IF(AW29="1",0.5,IF(AW29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AW29="","",IF(AW29="NE","",(IFERROR(IF(ISNUMBER(AW29),AW29,VALUE(AW29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="AY29" s="20">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AZ29" s="18" t="n"/>
       <c r="BA29" s="19">
-        <f>IF(AZ29="","",IF(AZ29="NE","",IF(AZ29="0",0,IF(AZ29="1",0.5,IF(AZ29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(AZ29="","",IF(AZ29="NE","",(IFERROR(IF(ISNUMBER(AZ29),AZ29,VALUE(AZ29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BB29" s="20">
@@ -9137,7 +9137,7 @@
       </c>
       <c r="BC29" s="18" t="n"/>
       <c r="BD29" s="19">
-        <f>IF(BC29="","",IF(BC29="NE","",IF(BC29="0",0,IF(BC29="1",0.5,IF(BC29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BC29="","",IF(BC29="NE","",(IFERROR(IF(ISNUMBER(BC29),BC29,VALUE(BC29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BE29" s="20">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="BF29" s="18" t="n"/>
       <c r="BG29" s="19">
-        <f>IF(BF29="","",IF(BF29="NE","",IF(BF29="0",0,IF(BF29="1",0.5,IF(BF29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BF29="","",IF(BF29="NE","",(IFERROR(IF(ISNUMBER(BF29),BF29,VALUE(BF29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BH29" s="20">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="BI29" s="18" t="n"/>
       <c r="BJ29" s="19">
-        <f>IF(BI29="","",IF(BI29="NE","",IF(BI29="0",0,IF(BI29="1",0.5,IF(BI29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BI29="","",IF(BI29="NE","",(IFERROR(IF(ISNUMBER(BI29),BI29,VALUE(BI29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BK29" s="20">
@@ -9164,7 +9164,7 @@
       </c>
       <c r="BL29" s="18" t="n"/>
       <c r="BM29" s="19">
-        <f>IF(BL29="","",IF(BL29="NE","",IF(BL29="0",0,IF(BL29="1",0.5,IF(BL29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BL29="","",IF(BL29="NE","",(IFERROR(IF(ISNUMBER(BL29),BL29,VALUE(BL29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BN29" s="20">
@@ -9173,7 +9173,7 @@
       </c>
       <c r="BO29" s="18" t="n"/>
       <c r="BP29" s="19">
-        <f>IF(BO29="","",IF(BO29="NE","",IF(BO29="0",0,IF(BO29="1",0.5,IF(BO29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BO29="","",IF(BO29="NE","",(IFERROR(IF(ISNUMBER(BO29),BO29,VALUE(BO29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BQ29" s="20">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="BR29" s="18" t="n"/>
       <c r="BS29" s="19">
-        <f>IF(BR29="","",IF(BR29="NE","",IF(BR29="0",0,IF(BR29="1",0.5,IF(BR29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BR29="","",IF(BR29="NE","",(IFERROR(IF(ISNUMBER(BR29),BR29,VALUE(BR29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BT29" s="20">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="BU29" s="18" t="n"/>
       <c r="BV29" s="19">
-        <f>IF(BU29="","",IF(BU29="NE","",IF(BU29="0",0,IF(BU29="1",0.5,IF(BU29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BU29="","",IF(BU29="NE","",(IFERROR(IF(ISNUMBER(BU29),BU29,VALUE(BU29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BW29" s="20">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="BX29" s="18" t="n"/>
       <c r="BY29" s="19">
-        <f>IF(BX29="","",IF(BX29="NE","",IF(BX29="0",0,IF(BX29="1",0.5,IF(BX29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(BX29="","",IF(BX29="NE","",(IFERROR(IF(ISNUMBER(BX29),BX29,VALUE(BX29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="BZ29" s="20">
@@ -9209,7 +9209,7 @@
       </c>
       <c r="CA29" s="18" t="n"/>
       <c r="CB29" s="19">
-        <f>IF(CA29="","",IF(CA29="NE","",IF(CA29="0",0,IF(CA29="1",0.5,IF(CA29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(CA29="","",IF(CA29="NE","",(IFERROR(IF(ISNUMBER(CA29),CA29,VALUE(CA29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="CC29" s="20">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="CD29" s="18" t="n"/>
       <c r="CE29" s="19">
-        <f>IF(CD29="","",IF(CD29="NE","",IF(CD29="0",0,IF(CD29="1",0.5,IF(CD29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(CD29="","",IF(CD29="NE","",(IFERROR(IF(ISNUMBER(CD29),CD29,VALUE(CD29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="CF29" s="20">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="CG29" s="18" t="n"/>
       <c r="CH29" s="19">
-        <f>IF(CG29="","",IF(CG29="NE","",IF(CG29="0",0,IF(CG29="1",0.5,IF(CG29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(CG29="","",IF(CG29="NE","",(IFERROR(IF(ISNUMBER(CG29),CG29,VALUE(CG29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="CI29" s="20">
@@ -9236,7 +9236,7 @@
       </c>
       <c r="CJ29" s="18" t="n"/>
       <c r="CK29" s="19">
-        <f>IF(CJ29="","",IF(CJ29="NE","",IF(CJ29="0",0,IF(CJ29="1",0.5,IF(CJ29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(CJ29="","",IF(CJ29="NE","",(IFERROR(IF(ISNUMBER(CJ29),CJ29,VALUE(CJ29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="CL29" s="20">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="CM29" s="18" t="n"/>
       <c r="CN29" s="19">
-        <f>IF(CM29="","",IF(CM29="NE","",IF(CM29="0",0,IF(CM29="1",0.5,IF(CM29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(CM29="","",IF(CM29="NE","",(IFERROR(IF(ISNUMBER(CM29),CM29,VALUE(CM29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="CO29" s="20">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="CP29" s="18" t="n"/>
       <c r="CQ29" s="19">
-        <f>IF(CP29="","",IF(CP29="NE","",IF(CP29="0",0,IF(CP29="1",0.5,IF(CP29="2",1,0)))*$F29*$F$26*20))</f>
+        <f>IF(CP29="","",IF(CP29="NE","",(IFERROR(IF(ISNUMBER(CP29),CP29,VALUE(CP29)),0)/2)*$F29*$F$26*20))</f>
         <v/>
       </c>
       <c r="CR29" s="20">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="G30" s="18" t="n"/>
       <c r="H30" s="19">
-        <f>IF(G30="","",IF(G30="NE","",IF(G30="0",0,IF(G30="1",0.5,IF(G30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(G30="","",IF(G30="NE","",(IFERROR(IF(ISNUMBER(G30),G30,VALUE(G30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="I30" s="20">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="J30" s="18" t="n"/>
       <c r="K30" s="19">
-        <f>IF(J30="","",IF(J30="NE","",IF(J30="0",0,IF(J30="1",0.5,IF(J30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(J30="","",IF(J30="NE","",(IFERROR(IF(ISNUMBER(J30),J30,VALUE(J30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="L30" s="20">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="M30" s="18" t="n"/>
       <c r="N30" s="19">
-        <f>IF(M30="","",IF(M30="NE","",IF(M30="0",0,IF(M30="1",0.5,IF(M30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(M30="","",IF(M30="NE","",(IFERROR(IF(ISNUMBER(M30),M30,VALUE(M30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="O30" s="20">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="P30" s="18" t="n"/>
       <c r="Q30" s="19">
-        <f>IF(P30="","",IF(P30="NE","",IF(P30="0",0,IF(P30="1",0.5,IF(P30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(P30="","",IF(P30="NE","",(IFERROR(IF(ISNUMBER(P30),P30,VALUE(P30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="R30" s="20">
@@ -9327,7 +9327,7 @@
       </c>
       <c r="S30" s="18" t="n"/>
       <c r="T30" s="19">
-        <f>IF(S30="","",IF(S30="NE","",IF(S30="0",0,IF(S30="1",0.5,IF(S30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(S30="","",IF(S30="NE","",(IFERROR(IF(ISNUMBER(S30),S30,VALUE(S30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="U30" s="20">
@@ -9336,7 +9336,7 @@
       </c>
       <c r="V30" s="18" t="n"/>
       <c r="W30" s="19">
-        <f>IF(V30="","",IF(V30="NE","",IF(V30="0",0,IF(V30="1",0.5,IF(V30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(V30="","",IF(V30="NE","",(IFERROR(IF(ISNUMBER(V30),V30,VALUE(V30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="X30" s="20">
@@ -9345,7 +9345,7 @@
       </c>
       <c r="Y30" s="18" t="n"/>
       <c r="Z30" s="19">
-        <f>IF(Y30="","",IF(Y30="NE","",IF(Y30="0",0,IF(Y30="1",0.5,IF(Y30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(Y30="","",IF(Y30="NE","",(IFERROR(IF(ISNUMBER(Y30),Y30,VALUE(Y30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AA30" s="20">
@@ -9354,7 +9354,7 @@
       </c>
       <c r="AB30" s="18" t="n"/>
       <c r="AC30" s="19">
-        <f>IF(AB30="","",IF(AB30="NE","",IF(AB30="0",0,IF(AB30="1",0.5,IF(AB30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AB30="","",IF(AB30="NE","",(IFERROR(IF(ISNUMBER(AB30),AB30,VALUE(AB30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AD30" s="20">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="AE30" s="18" t="n"/>
       <c r="AF30" s="19">
-        <f>IF(AE30="","",IF(AE30="NE","",IF(AE30="0",0,IF(AE30="1",0.5,IF(AE30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AE30="","",IF(AE30="NE","",(IFERROR(IF(ISNUMBER(AE30),AE30,VALUE(AE30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AG30" s="20">
@@ -9372,7 +9372,7 @@
       </c>
       <c r="AH30" s="18" t="n"/>
       <c r="AI30" s="19">
-        <f>IF(AH30="","",IF(AH30="NE","",IF(AH30="0",0,IF(AH30="1",0.5,IF(AH30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AH30="","",IF(AH30="NE","",(IFERROR(IF(ISNUMBER(AH30),AH30,VALUE(AH30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AJ30" s="20">
@@ -9381,7 +9381,7 @@
       </c>
       <c r="AK30" s="18" t="n"/>
       <c r="AL30" s="19">
-        <f>IF(AK30="","",IF(AK30="NE","",IF(AK30="0",0,IF(AK30="1",0.5,IF(AK30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AK30="","",IF(AK30="NE","",(IFERROR(IF(ISNUMBER(AK30),AK30,VALUE(AK30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AM30" s="20">
@@ -9390,7 +9390,7 @@
       </c>
       <c r="AN30" s="18" t="n"/>
       <c r="AO30" s="19">
-        <f>IF(AN30="","",IF(AN30="NE","",IF(AN30="0",0,IF(AN30="1",0.5,IF(AN30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AN30="","",IF(AN30="NE","",(IFERROR(IF(ISNUMBER(AN30),AN30,VALUE(AN30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AP30" s="20">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="AQ30" s="18" t="n"/>
       <c r="AR30" s="19">
-        <f>IF(AQ30="","",IF(AQ30="NE","",IF(AQ30="0",0,IF(AQ30="1",0.5,IF(AQ30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AQ30="","",IF(AQ30="NE","",(IFERROR(IF(ISNUMBER(AQ30),AQ30,VALUE(AQ30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AS30" s="20">
@@ -9408,7 +9408,7 @@
       </c>
       <c r="AT30" s="18" t="n"/>
       <c r="AU30" s="19">
-        <f>IF(AT30="","",IF(AT30="NE","",IF(AT30="0",0,IF(AT30="1",0.5,IF(AT30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AT30="","",IF(AT30="NE","",(IFERROR(IF(ISNUMBER(AT30),AT30,VALUE(AT30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AV30" s="20">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AW30" s="18" t="n"/>
       <c r="AX30" s="19">
-        <f>IF(AW30="","",IF(AW30="NE","",IF(AW30="0",0,IF(AW30="1",0.5,IF(AW30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AW30="","",IF(AW30="NE","",(IFERROR(IF(ISNUMBER(AW30),AW30,VALUE(AW30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="AY30" s="20">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="AZ30" s="18" t="n"/>
       <c r="BA30" s="19">
-        <f>IF(AZ30="","",IF(AZ30="NE","",IF(AZ30="0",0,IF(AZ30="1",0.5,IF(AZ30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(AZ30="","",IF(AZ30="NE","",(IFERROR(IF(ISNUMBER(AZ30),AZ30,VALUE(AZ30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BB30" s="20">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="BC30" s="18" t="n"/>
       <c r="BD30" s="19">
-        <f>IF(BC30="","",IF(BC30="NE","",IF(BC30="0",0,IF(BC30="1",0.5,IF(BC30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BC30="","",IF(BC30="NE","",(IFERROR(IF(ISNUMBER(BC30),BC30,VALUE(BC30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BE30" s="20">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="BF30" s="18" t="n"/>
       <c r="BG30" s="19">
-        <f>IF(BF30="","",IF(BF30="NE","",IF(BF30="0",0,IF(BF30="1",0.5,IF(BF30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BF30="","",IF(BF30="NE","",(IFERROR(IF(ISNUMBER(BF30),BF30,VALUE(BF30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BH30" s="20">
@@ -9453,7 +9453,7 @@
       </c>
       <c r="BI30" s="18" t="n"/>
       <c r="BJ30" s="19">
-        <f>IF(BI30="","",IF(BI30="NE","",IF(BI30="0",0,IF(BI30="1",0.5,IF(BI30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BI30="","",IF(BI30="NE","",(IFERROR(IF(ISNUMBER(BI30),BI30,VALUE(BI30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BK30" s="20">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="BL30" s="18" t="n"/>
       <c r="BM30" s="19">
-        <f>IF(BL30="","",IF(BL30="NE","",IF(BL30="0",0,IF(BL30="1",0.5,IF(BL30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BL30="","",IF(BL30="NE","",(IFERROR(IF(ISNUMBER(BL30),BL30,VALUE(BL30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BN30" s="20">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BO30" s="18" t="n"/>
       <c r="BP30" s="19">
-        <f>IF(BO30="","",IF(BO30="NE","",IF(BO30="0",0,IF(BO30="1",0.5,IF(BO30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BO30="","",IF(BO30="NE","",(IFERROR(IF(ISNUMBER(BO30),BO30,VALUE(BO30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BQ30" s="20">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="BR30" s="18" t="n"/>
       <c r="BS30" s="19">
-        <f>IF(BR30="","",IF(BR30="NE","",IF(BR30="0",0,IF(BR30="1",0.5,IF(BR30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BR30="","",IF(BR30="NE","",(IFERROR(IF(ISNUMBER(BR30),BR30,VALUE(BR30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BT30" s="20">
@@ -9489,7 +9489,7 @@
       </c>
       <c r="BU30" s="18" t="n"/>
       <c r="BV30" s="19">
-        <f>IF(BU30="","",IF(BU30="NE","",IF(BU30="0",0,IF(BU30="1",0.5,IF(BU30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BU30="","",IF(BU30="NE","",(IFERROR(IF(ISNUMBER(BU30),BU30,VALUE(BU30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BW30" s="20">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="BX30" s="18" t="n"/>
       <c r="BY30" s="19">
-        <f>IF(BX30="","",IF(BX30="NE","",IF(BX30="0",0,IF(BX30="1",0.5,IF(BX30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(BX30="","",IF(BX30="NE","",(IFERROR(IF(ISNUMBER(BX30),BX30,VALUE(BX30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="BZ30" s="20">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="CA30" s="18" t="n"/>
       <c r="CB30" s="19">
-        <f>IF(CA30="","",IF(CA30="NE","",IF(CA30="0",0,IF(CA30="1",0.5,IF(CA30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(CA30="","",IF(CA30="NE","",(IFERROR(IF(ISNUMBER(CA30),CA30,VALUE(CA30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="CC30" s="20">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="CD30" s="18" t="n"/>
       <c r="CE30" s="19">
-        <f>IF(CD30="","",IF(CD30="NE","",IF(CD30="0",0,IF(CD30="1",0.5,IF(CD30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(CD30="","",IF(CD30="NE","",(IFERROR(IF(ISNUMBER(CD30),CD30,VALUE(CD30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="CF30" s="20">
@@ -9525,7 +9525,7 @@
       </c>
       <c r="CG30" s="18" t="n"/>
       <c r="CH30" s="19">
-        <f>IF(CG30="","",IF(CG30="NE","",IF(CG30="0",0,IF(CG30="1",0.5,IF(CG30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(CG30="","",IF(CG30="NE","",(IFERROR(IF(ISNUMBER(CG30),CG30,VALUE(CG30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="CI30" s="20">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="CJ30" s="18" t="n"/>
       <c r="CK30" s="19">
-        <f>IF(CJ30="","",IF(CJ30="NE","",IF(CJ30="0",0,IF(CJ30="1",0.5,IF(CJ30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(CJ30="","",IF(CJ30="NE","",(IFERROR(IF(ISNUMBER(CJ30),CJ30,VALUE(CJ30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="CL30" s="20">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="CM30" s="18" t="n"/>
       <c r="CN30" s="19">
-        <f>IF(CM30="","",IF(CM30="NE","",IF(CM30="0",0,IF(CM30="1",0.5,IF(CM30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(CM30="","",IF(CM30="NE","",(IFERROR(IF(ISNUMBER(CM30),CM30,VALUE(CM30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="CO30" s="20">
@@ -9552,7 +9552,7 @@
       </c>
       <c r="CP30" s="18" t="n"/>
       <c r="CQ30" s="19">
-        <f>IF(CP30="","",IF(CP30="NE","",IF(CP30="0",0,IF(CP30="1",0.5,IF(CP30="2",1,0)))*$F30*$F$26*20))</f>
+        <f>IF(CP30="","",IF(CP30="NE","",(IFERROR(IF(ISNUMBER(CP30),CP30,VALUE(CP30)),0)/2)*$F30*$F$26*20))</f>
         <v/>
       </c>
       <c r="CR30" s="20">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="G31" s="18" t="n"/>
       <c r="H31" s="19">
-        <f>IF(G31="","",IF(G31="NE","",IF(G31="0",0,IF(G31="1",0.5,IF(G31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(G31="","",IF(G31="NE","",(IFERROR(IF(ISNUMBER(G31),G31,VALUE(G31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="I31" s="20">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="J31" s="18" t="n"/>
       <c r="K31" s="19">
-        <f>IF(J31="","",IF(J31="NE","",IF(J31="0",0,IF(J31="1",0.5,IF(J31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(J31="","",IF(J31="NE","",(IFERROR(IF(ISNUMBER(J31),J31,VALUE(J31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="L31" s="20">
@@ -9607,7 +9607,7 @@
       </c>
       <c r="M31" s="18" t="n"/>
       <c r="N31" s="19">
-        <f>IF(M31="","",IF(M31="NE","",IF(M31="0",0,IF(M31="1",0.5,IF(M31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(M31="","",IF(M31="NE","",(IFERROR(IF(ISNUMBER(M31),M31,VALUE(M31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="O31" s="20">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="P31" s="18" t="n"/>
       <c r="Q31" s="19">
-        <f>IF(P31="","",IF(P31="NE","",IF(P31="0",0,IF(P31="1",0.5,IF(P31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(P31="","",IF(P31="NE","",(IFERROR(IF(ISNUMBER(P31),P31,VALUE(P31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="R31" s="20">
@@ -9625,7 +9625,7 @@
       </c>
       <c r="S31" s="18" t="n"/>
       <c r="T31" s="19">
-        <f>IF(S31="","",IF(S31="NE","",IF(S31="0",0,IF(S31="1",0.5,IF(S31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(S31="","",IF(S31="NE","",(IFERROR(IF(ISNUMBER(S31),S31,VALUE(S31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="U31" s="20">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V31" s="18" t="n"/>
       <c r="W31" s="19">
-        <f>IF(V31="","",IF(V31="NE","",IF(V31="0",0,IF(V31="1",0.5,IF(V31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(V31="","",IF(V31="NE","",(IFERROR(IF(ISNUMBER(V31),V31,VALUE(V31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="X31" s="20">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="Y31" s="18" t="n"/>
       <c r="Z31" s="19">
-        <f>IF(Y31="","",IF(Y31="NE","",IF(Y31="0",0,IF(Y31="1",0.5,IF(Y31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(Y31="","",IF(Y31="NE","",(IFERROR(IF(ISNUMBER(Y31),Y31,VALUE(Y31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AA31" s="20">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="AB31" s="18" t="n"/>
       <c r="AC31" s="19">
-        <f>IF(AB31="","",IF(AB31="NE","",IF(AB31="0",0,IF(AB31="1",0.5,IF(AB31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AB31="","",IF(AB31="NE","",(IFERROR(IF(ISNUMBER(AB31),AB31,VALUE(AB31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AD31" s="20">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="AE31" s="18" t="n"/>
       <c r="AF31" s="19">
-        <f>IF(AE31="","",IF(AE31="NE","",IF(AE31="0",0,IF(AE31="1",0.5,IF(AE31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AE31="","",IF(AE31="NE","",(IFERROR(IF(ISNUMBER(AE31),AE31,VALUE(AE31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AG31" s="20">
@@ -9670,7 +9670,7 @@
       </c>
       <c r="AH31" s="18" t="n"/>
       <c r="AI31" s="19">
-        <f>IF(AH31="","",IF(AH31="NE","",IF(AH31="0",0,IF(AH31="1",0.5,IF(AH31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AH31="","",IF(AH31="NE","",(IFERROR(IF(ISNUMBER(AH31),AH31,VALUE(AH31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AJ31" s="20">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="AK31" s="18" t="n"/>
       <c r="AL31" s="19">
-        <f>IF(AK31="","",IF(AK31="NE","",IF(AK31="0",0,IF(AK31="1",0.5,IF(AK31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AK31="","",IF(AK31="NE","",(IFERROR(IF(ISNUMBER(AK31),AK31,VALUE(AK31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AM31" s="20">
@@ -9688,7 +9688,7 @@
       </c>
       <c r="AN31" s="18" t="n"/>
       <c r="AO31" s="19">
-        <f>IF(AN31="","",IF(AN31="NE","",IF(AN31="0",0,IF(AN31="1",0.5,IF(AN31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AN31="","",IF(AN31="NE","",(IFERROR(IF(ISNUMBER(AN31),AN31,VALUE(AN31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AP31" s="20">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="AQ31" s="18" t="n"/>
       <c r="AR31" s="19">
-        <f>IF(AQ31="","",IF(AQ31="NE","",IF(AQ31="0",0,IF(AQ31="1",0.5,IF(AQ31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AQ31="","",IF(AQ31="NE","",(IFERROR(IF(ISNUMBER(AQ31),AQ31,VALUE(AQ31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AS31" s="20">
@@ -9706,7 +9706,7 @@
       </c>
       <c r="AT31" s="18" t="n"/>
       <c r="AU31" s="19">
-        <f>IF(AT31="","",IF(AT31="NE","",IF(AT31="0",0,IF(AT31="1",0.5,IF(AT31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AT31="","",IF(AT31="NE","",(IFERROR(IF(ISNUMBER(AT31),AT31,VALUE(AT31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AV31" s="20">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="AW31" s="18" t="n"/>
       <c r="AX31" s="19">
-        <f>IF(AW31="","",IF(AW31="NE","",IF(AW31="0",0,IF(AW31="1",0.5,IF(AW31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AW31="","",IF(AW31="NE","",(IFERROR(IF(ISNUMBER(AW31),AW31,VALUE(AW31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="AY31" s="20">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="AZ31" s="18" t="n"/>
       <c r="BA31" s="19">
-        <f>IF(AZ31="","",IF(AZ31="NE","",IF(AZ31="0",0,IF(AZ31="1",0.5,IF(AZ31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(AZ31="","",IF(AZ31="NE","",(IFERROR(IF(ISNUMBER(AZ31),AZ31,VALUE(AZ31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BB31" s="20">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="BC31" s="18" t="n"/>
       <c r="BD31" s="19">
-        <f>IF(BC31="","",IF(BC31="NE","",IF(BC31="0",0,IF(BC31="1",0.5,IF(BC31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BC31="","",IF(BC31="NE","",(IFERROR(IF(ISNUMBER(BC31),BC31,VALUE(BC31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BE31" s="20">
@@ -9742,7 +9742,7 @@
       </c>
       <c r="BF31" s="18" t="n"/>
       <c r="BG31" s="19">
-        <f>IF(BF31="","",IF(BF31="NE","",IF(BF31="0",0,IF(BF31="1",0.5,IF(BF31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BF31="","",IF(BF31="NE","",(IFERROR(IF(ISNUMBER(BF31),BF31,VALUE(BF31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BH31" s="20">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="BI31" s="18" t="n"/>
       <c r="BJ31" s="19">
-        <f>IF(BI31="","",IF(BI31="NE","",IF(BI31="0",0,IF(BI31="1",0.5,IF(BI31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BI31="","",IF(BI31="NE","",(IFERROR(IF(ISNUMBER(BI31),BI31,VALUE(BI31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BK31" s="20">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="BL31" s="18" t="n"/>
       <c r="BM31" s="19">
-        <f>IF(BL31="","",IF(BL31="NE","",IF(BL31="0",0,IF(BL31="1",0.5,IF(BL31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BL31="","",IF(BL31="NE","",(IFERROR(IF(ISNUMBER(BL31),BL31,VALUE(BL31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BN31" s="20">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="BO31" s="18" t="n"/>
       <c r="BP31" s="19">
-        <f>IF(BO31="","",IF(BO31="NE","",IF(BO31="0",0,IF(BO31="1",0.5,IF(BO31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BO31="","",IF(BO31="NE","",(IFERROR(IF(ISNUMBER(BO31),BO31,VALUE(BO31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BQ31" s="20">
@@ -9778,7 +9778,7 @@
       </c>
       <c r="BR31" s="18" t="n"/>
       <c r="BS31" s="19">
-        <f>IF(BR31="","",IF(BR31="NE","",IF(BR31="0",0,IF(BR31="1",0.5,IF(BR31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BR31="","",IF(BR31="NE","",(IFERROR(IF(ISNUMBER(BR31),BR31,VALUE(BR31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BT31" s="20">
@@ -9787,7 +9787,7 @@
       </c>
       <c r="BU31" s="18" t="n"/>
       <c r="BV31" s="19">
-        <f>IF(BU31="","",IF(BU31="NE","",IF(BU31="0",0,IF(BU31="1",0.5,IF(BU31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BU31="","",IF(BU31="NE","",(IFERROR(IF(ISNUMBER(BU31),BU31,VALUE(BU31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BW31" s="20">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="BX31" s="18" t="n"/>
       <c r="BY31" s="19">
-        <f>IF(BX31="","",IF(BX31="NE","",IF(BX31="0",0,IF(BX31="1",0.5,IF(BX31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(BX31="","",IF(BX31="NE","",(IFERROR(IF(ISNUMBER(BX31),BX31,VALUE(BX31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="BZ31" s="20">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="CA31" s="18" t="n"/>
       <c r="CB31" s="19">
-        <f>IF(CA31="","",IF(CA31="NE","",IF(CA31="0",0,IF(CA31="1",0.5,IF(CA31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(CA31="","",IF(CA31="NE","",(IFERROR(IF(ISNUMBER(CA31),CA31,VALUE(CA31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="CC31" s="20">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="CD31" s="18" t="n"/>
       <c r="CE31" s="19">
-        <f>IF(CD31="","",IF(CD31="NE","",IF(CD31="0",0,IF(CD31="1",0.5,IF(CD31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(CD31="","",IF(CD31="NE","",(IFERROR(IF(ISNUMBER(CD31),CD31,VALUE(CD31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="CF31" s="20">
@@ -9823,7 +9823,7 @@
       </c>
       <c r="CG31" s="18" t="n"/>
       <c r="CH31" s="19">
-        <f>IF(CG31="","",IF(CG31="NE","",IF(CG31="0",0,IF(CG31="1",0.5,IF(CG31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(CG31="","",IF(CG31="NE","",(IFERROR(IF(ISNUMBER(CG31),CG31,VALUE(CG31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="CI31" s="20">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="CJ31" s="18" t="n"/>
       <c r="CK31" s="19">
-        <f>IF(CJ31="","",IF(CJ31="NE","",IF(CJ31="0",0,IF(CJ31="1",0.5,IF(CJ31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(CJ31="","",IF(CJ31="NE","",(IFERROR(IF(ISNUMBER(CJ31),CJ31,VALUE(CJ31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="CL31" s="20">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="CM31" s="18" t="n"/>
       <c r="CN31" s="19">
-        <f>IF(CM31="","",IF(CM31="NE","",IF(CM31="0",0,IF(CM31="1",0.5,IF(CM31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(CM31="","",IF(CM31="NE","",(IFERROR(IF(ISNUMBER(CM31),CM31,VALUE(CM31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="CO31" s="20">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="CP31" s="18" t="n"/>
       <c r="CQ31" s="19">
-        <f>IF(CP31="","",IF(CP31="NE","",IF(CP31="0",0,IF(CP31="1",0.5,IF(CP31="2",1,0)))*$F31*$F$26*20))</f>
+        <f>IF(CP31="","",IF(CP31="NE","",(IFERROR(IF(ISNUMBER(CP31),CP31,VALUE(CP31)),0)/2)*$F31*$F$26*20))</f>
         <v/>
       </c>
       <c r="CR31" s="20">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="G32" s="18" t="n"/>
       <c r="H32" s="19">
-        <f>IF(G32="","",IF(G32="NE","",IF(G32="0",0,IF(G32="1",0.5,IF(G32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(G32="","",IF(G32="NE","",(IFERROR(IF(ISNUMBER(G32),G32,VALUE(G32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="I32" s="20">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="J32" s="18" t="n"/>
       <c r="K32" s="19">
-        <f>IF(J32="","",IF(J32="NE","",IF(J32="0",0,IF(J32="1",0.5,IF(J32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(J32="","",IF(J32="NE","",(IFERROR(IF(ISNUMBER(J32),J32,VALUE(J32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="L32" s="20">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="M32" s="18" t="n"/>
       <c r="N32" s="19">
-        <f>IF(M32="","",IF(M32="NE","",IF(M32="0",0,IF(M32="1",0.5,IF(M32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(M32="","",IF(M32="NE","",(IFERROR(IF(ISNUMBER(M32),M32,VALUE(M32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="O32" s="20">
@@ -9914,7 +9914,7 @@
       </c>
       <c r="P32" s="18" t="n"/>
       <c r="Q32" s="19">
-        <f>IF(P32="","",IF(P32="NE","",IF(P32="0",0,IF(P32="1",0.5,IF(P32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(P32="","",IF(P32="NE","",(IFERROR(IF(ISNUMBER(P32),P32,VALUE(P32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="R32" s="20">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="S32" s="18" t="n"/>
       <c r="T32" s="19">
-        <f>IF(S32="","",IF(S32="NE","",IF(S32="0",0,IF(S32="1",0.5,IF(S32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(S32="","",IF(S32="NE","",(IFERROR(IF(ISNUMBER(S32),S32,VALUE(S32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="U32" s="20">
@@ -9932,7 +9932,7 @@
       </c>
       <c r="V32" s="18" t="n"/>
       <c r="W32" s="19">
-        <f>IF(V32="","",IF(V32="NE","",IF(V32="0",0,IF(V32="1",0.5,IF(V32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(V32="","",IF(V32="NE","",(IFERROR(IF(ISNUMBER(V32),V32,VALUE(V32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="X32" s="20">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="Y32" s="18" t="n"/>
       <c r="Z32" s="19">
-        <f>IF(Y32="","",IF(Y32="NE","",IF(Y32="0",0,IF(Y32="1",0.5,IF(Y32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(Y32="","",IF(Y32="NE","",(IFERROR(IF(ISNUMBER(Y32),Y32,VALUE(Y32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AA32" s="20">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="AB32" s="18" t="n"/>
       <c r="AC32" s="19">
-        <f>IF(AB32="","",IF(AB32="NE","",IF(AB32="0",0,IF(AB32="1",0.5,IF(AB32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AB32="","",IF(AB32="NE","",(IFERROR(IF(ISNUMBER(AB32),AB32,VALUE(AB32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AD32" s="20">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="AE32" s="18" t="n"/>
       <c r="AF32" s="19">
-        <f>IF(AE32="","",IF(AE32="NE","",IF(AE32="0",0,IF(AE32="1",0.5,IF(AE32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AE32="","",IF(AE32="NE","",(IFERROR(IF(ISNUMBER(AE32),AE32,VALUE(AE32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AG32" s="20">
@@ -9968,7 +9968,7 @@
       </c>
       <c r="AH32" s="18" t="n"/>
       <c r="AI32" s="19">
-        <f>IF(AH32="","",IF(AH32="NE","",IF(AH32="0",0,IF(AH32="1",0.5,IF(AH32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AH32="","",IF(AH32="NE","",(IFERROR(IF(ISNUMBER(AH32),AH32,VALUE(AH32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AJ32" s="20">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="AK32" s="18" t="n"/>
       <c r="AL32" s="19">
-        <f>IF(AK32="","",IF(AK32="NE","",IF(AK32="0",0,IF(AK32="1",0.5,IF(AK32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AK32="","",IF(AK32="NE","",(IFERROR(IF(ISNUMBER(AK32),AK32,VALUE(AK32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AM32" s="20">
@@ -9986,7 +9986,7 @@
       </c>
       <c r="AN32" s="18" t="n"/>
       <c r="AO32" s="19">
-        <f>IF(AN32="","",IF(AN32="NE","",IF(AN32="0",0,IF(AN32="1",0.5,IF(AN32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AN32="","",IF(AN32="NE","",(IFERROR(IF(ISNUMBER(AN32),AN32,VALUE(AN32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AP32" s="20">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="AQ32" s="18" t="n"/>
       <c r="AR32" s="19">
-        <f>IF(AQ32="","",IF(AQ32="NE","",IF(AQ32="0",0,IF(AQ32="1",0.5,IF(AQ32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AQ32="","",IF(AQ32="NE","",(IFERROR(IF(ISNUMBER(AQ32),AQ32,VALUE(AQ32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AS32" s="20">
@@ -10004,7 +10004,7 @@
       </c>
       <c r="AT32" s="18" t="n"/>
       <c r="AU32" s="19">
-        <f>IF(AT32="","",IF(AT32="NE","",IF(AT32="0",0,IF(AT32="1",0.5,IF(AT32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AT32="","",IF(AT32="NE","",(IFERROR(IF(ISNUMBER(AT32),AT32,VALUE(AT32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AV32" s="20">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="AW32" s="18" t="n"/>
       <c r="AX32" s="19">
-        <f>IF(AW32="","",IF(AW32="NE","",IF(AW32="0",0,IF(AW32="1",0.5,IF(AW32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AW32="","",IF(AW32="NE","",(IFERROR(IF(ISNUMBER(AW32),AW32,VALUE(AW32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="AY32" s="20">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="AZ32" s="18" t="n"/>
       <c r="BA32" s="19">
-        <f>IF(AZ32="","",IF(AZ32="NE","",IF(AZ32="0",0,IF(AZ32="1",0.5,IF(AZ32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(AZ32="","",IF(AZ32="NE","",(IFERROR(IF(ISNUMBER(AZ32),AZ32,VALUE(AZ32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BB32" s="20">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="BC32" s="18" t="n"/>
       <c r="BD32" s="19">
-        <f>IF(BC32="","",IF(BC32="NE","",IF(BC32="0",0,IF(BC32="1",0.5,IF(BC32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BC32="","",IF(BC32="NE","",(IFERROR(IF(ISNUMBER(BC32),BC32,VALUE(BC32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BE32" s="20">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="BF32" s="18" t="n"/>
       <c r="BG32" s="19">
-        <f>IF(BF32="","",IF(BF32="NE","",IF(BF32="0",0,IF(BF32="1",0.5,IF(BF32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BF32="","",IF(BF32="NE","",(IFERROR(IF(ISNUMBER(BF32),BF32,VALUE(BF32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BH32" s="20">
@@ -10049,7 +10049,7 @@
       </c>
       <c r="BI32" s="18" t="n"/>
       <c r="BJ32" s="19">
-        <f>IF(BI32="","",IF(BI32="NE","",IF(BI32="0",0,IF(BI32="1",0.5,IF(BI32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BI32="","",IF(BI32="NE","",(IFERROR(IF(ISNUMBER(BI32),BI32,VALUE(BI32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BK32" s="20">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="BL32" s="18" t="n"/>
       <c r="BM32" s="19">
-        <f>IF(BL32="","",IF(BL32="NE","",IF(BL32="0",0,IF(BL32="1",0.5,IF(BL32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BL32="","",IF(BL32="NE","",(IFERROR(IF(ISNUMBER(BL32),BL32,VALUE(BL32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BN32" s="20">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="BO32" s="18" t="n"/>
       <c r="BP32" s="19">
-        <f>IF(BO32="","",IF(BO32="NE","",IF(BO32="0",0,IF(BO32="1",0.5,IF(BO32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BO32="","",IF(BO32="NE","",(IFERROR(IF(ISNUMBER(BO32),BO32,VALUE(BO32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BQ32" s="20">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="BR32" s="18" t="n"/>
       <c r="BS32" s="19">
-        <f>IF(BR32="","",IF(BR32="NE","",IF(BR32="0",0,IF(BR32="1",0.5,IF(BR32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BR32="","",IF(BR32="NE","",(IFERROR(IF(ISNUMBER(BR32),BR32,VALUE(BR32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BT32" s="20">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="BU32" s="18" t="n"/>
       <c r="BV32" s="19">
-        <f>IF(BU32="","",IF(BU32="NE","",IF(BU32="0",0,IF(BU32="1",0.5,IF(BU32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BU32="","",IF(BU32="NE","",(IFERROR(IF(ISNUMBER(BU32),BU32,VALUE(BU32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BW32" s="20">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="BX32" s="18" t="n"/>
       <c r="BY32" s="19">
-        <f>IF(BX32="","",IF(BX32="NE","",IF(BX32="0",0,IF(BX32="1",0.5,IF(BX32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(BX32="","",IF(BX32="NE","",(IFERROR(IF(ISNUMBER(BX32),BX32,VALUE(BX32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="BZ32" s="20">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="CA32" s="18" t="n"/>
       <c r="CB32" s="19">
-        <f>IF(CA32="","",IF(CA32="NE","",IF(CA32="0",0,IF(CA32="1",0.5,IF(CA32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(CA32="","",IF(CA32="NE","",(IFERROR(IF(ISNUMBER(CA32),CA32,VALUE(CA32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="CC32" s="20">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="CD32" s="18" t="n"/>
       <c r="CE32" s="19">
-        <f>IF(CD32="","",IF(CD32="NE","",IF(CD32="0",0,IF(CD32="1",0.5,IF(CD32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(CD32="","",IF(CD32="NE","",(IFERROR(IF(ISNUMBER(CD32),CD32,VALUE(CD32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="CF32" s="20">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="CG32" s="18" t="n"/>
       <c r="CH32" s="19">
-        <f>IF(CG32="","",IF(CG32="NE","",IF(CG32="0",0,IF(CG32="1",0.5,IF(CG32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(CG32="","",IF(CG32="NE","",(IFERROR(IF(ISNUMBER(CG32),CG32,VALUE(CG32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="CI32" s="20">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="CJ32" s="18" t="n"/>
       <c r="CK32" s="19">
-        <f>IF(CJ32="","",IF(CJ32="NE","",IF(CJ32="0",0,IF(CJ32="1",0.5,IF(CJ32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(CJ32="","",IF(CJ32="NE","",(IFERROR(IF(ISNUMBER(CJ32),CJ32,VALUE(CJ32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="CL32" s="20">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="CM32" s="18" t="n"/>
       <c r="CN32" s="19">
-        <f>IF(CM32="","",IF(CM32="NE","",IF(CM32="0",0,IF(CM32="1",0.5,IF(CM32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(CM32="","",IF(CM32="NE","",(IFERROR(IF(ISNUMBER(CM32),CM32,VALUE(CM32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="CO32" s="20">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="CP32" s="18" t="n"/>
       <c r="CQ32" s="19">
-        <f>IF(CP32="","",IF(CP32="NE","",IF(CP32="0",0,IF(CP32="1",0.5,IF(CP32="2",1,0)))*$F32*$F$26*20))</f>
+        <f>IF(CP32="","",IF(CP32="NE","",(IFERROR(IF(ISNUMBER(CP32),CP32,VALUE(CP32)),0)/2)*$F32*$F$26*20))</f>
         <v/>
       </c>
       <c r="CR32" s="20">
@@ -10185,7 +10185,7 @@
       </c>
       <c r="G33" s="18" t="n"/>
       <c r="H33" s="19">
-        <f>IF(G33="","",IF(G33="NE","",IF(G33="0",0,IF(G33="1",0.5,IF(G33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(G33="","",IF(G33="NE","",(IFERROR(IF(ISNUMBER(G33),G33,VALUE(G33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="I33" s="20">
@@ -10194,7 +10194,7 @@
       </c>
       <c r="J33" s="18" t="n"/>
       <c r="K33" s="19">
-        <f>IF(J33="","",IF(J33="NE","",IF(J33="0",0,IF(J33="1",0.5,IF(J33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(J33="","",IF(J33="NE","",(IFERROR(IF(ISNUMBER(J33),J33,VALUE(J33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="L33" s="20">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="M33" s="18" t="n"/>
       <c r="N33" s="19">
-        <f>IF(M33="","",IF(M33="NE","",IF(M33="0",0,IF(M33="1",0.5,IF(M33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(M33="","",IF(M33="NE","",(IFERROR(IF(ISNUMBER(M33),M33,VALUE(M33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="O33" s="20">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="P33" s="18" t="n"/>
       <c r="Q33" s="19">
-        <f>IF(P33="","",IF(P33="NE","",IF(P33="0",0,IF(P33="1",0.5,IF(P33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(P33="","",IF(P33="NE","",(IFERROR(IF(ISNUMBER(P33),P33,VALUE(P33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="R33" s="20">
@@ -10221,7 +10221,7 @@
       </c>
       <c r="S33" s="18" t="n"/>
       <c r="T33" s="19">
-        <f>IF(S33="","",IF(S33="NE","",IF(S33="0",0,IF(S33="1",0.5,IF(S33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(S33="","",IF(S33="NE","",(IFERROR(IF(ISNUMBER(S33),S33,VALUE(S33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="U33" s="20">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="V33" s="18" t="n"/>
       <c r="W33" s="19">
-        <f>IF(V33="","",IF(V33="NE","",IF(V33="0",0,IF(V33="1",0.5,IF(V33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(V33="","",IF(V33="NE","",(IFERROR(IF(ISNUMBER(V33),V33,VALUE(V33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="X33" s="20">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="Y33" s="18" t="n"/>
       <c r="Z33" s="19">
-        <f>IF(Y33="","",IF(Y33="NE","",IF(Y33="0",0,IF(Y33="1",0.5,IF(Y33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(Y33="","",IF(Y33="NE","",(IFERROR(IF(ISNUMBER(Y33),Y33,VALUE(Y33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AA33" s="20">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="AB33" s="18" t="n"/>
       <c r="AC33" s="19">
-        <f>IF(AB33="","",IF(AB33="NE","",IF(AB33="0",0,IF(AB33="1",0.5,IF(AB33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AB33="","",IF(AB33="NE","",(IFERROR(IF(ISNUMBER(AB33),AB33,VALUE(AB33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AD33" s="20">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="AE33" s="18" t="n"/>
       <c r="AF33" s="19">
-        <f>IF(AE33="","",IF(AE33="NE","",IF(AE33="0",0,IF(AE33="1",0.5,IF(AE33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AE33="","",IF(AE33="NE","",(IFERROR(IF(ISNUMBER(AE33),AE33,VALUE(AE33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AG33" s="20">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="AH33" s="18" t="n"/>
       <c r="AI33" s="19">
-        <f>IF(AH33="","",IF(AH33="NE","",IF(AH33="0",0,IF(AH33="1",0.5,IF(AH33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AH33="","",IF(AH33="NE","",(IFERROR(IF(ISNUMBER(AH33),AH33,VALUE(AH33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AJ33" s="20">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="AK33" s="18" t="n"/>
       <c r="AL33" s="19">
-        <f>IF(AK33="","",IF(AK33="NE","",IF(AK33="0",0,IF(AK33="1",0.5,IF(AK33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AK33="","",IF(AK33="NE","",(IFERROR(IF(ISNUMBER(AK33),AK33,VALUE(AK33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AM33" s="20">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="AN33" s="18" t="n"/>
       <c r="AO33" s="19">
-        <f>IF(AN33="","",IF(AN33="NE","",IF(AN33="0",0,IF(AN33="1",0.5,IF(AN33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AN33="","",IF(AN33="NE","",(IFERROR(IF(ISNUMBER(AN33),AN33,VALUE(AN33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AP33" s="20">
@@ -10293,7 +10293,7 @@
       </c>
       <c r="AQ33" s="18" t="n"/>
       <c r="AR33" s="19">
-        <f>IF(AQ33="","",IF(AQ33="NE","",IF(AQ33="0",0,IF(AQ33="1",0.5,IF(AQ33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AQ33="","",IF(AQ33="NE","",(IFERROR(IF(ISNUMBER(AQ33),AQ33,VALUE(AQ33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AS33" s="20">
@@ -10302,7 +10302,7 @@
       </c>
       <c r="AT33" s="18" t="n"/>
       <c r="AU33" s="19">
-        <f>IF(AT33="","",IF(AT33="NE","",IF(AT33="0",0,IF(AT33="1",0.5,IF(AT33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AT33="","",IF(AT33="NE","",(IFERROR(IF(ISNUMBER(AT33),AT33,VALUE(AT33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AV33" s="20">
@@ -10311,7 +10311,7 @@
       </c>
       <c r="AW33" s="18" t="n"/>
       <c r="AX33" s="19">
-        <f>IF(AW33="","",IF(AW33="NE","",IF(AW33="0",0,IF(AW33="1",0.5,IF(AW33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AW33="","",IF(AW33="NE","",(IFERROR(IF(ISNUMBER(AW33),AW33,VALUE(AW33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="AY33" s="20">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="AZ33" s="18" t="n"/>
       <c r="BA33" s="19">
-        <f>IF(AZ33="","",IF(AZ33="NE","",IF(AZ33="0",0,IF(AZ33="1",0.5,IF(AZ33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(AZ33="","",IF(AZ33="NE","",(IFERROR(IF(ISNUMBER(AZ33),AZ33,VALUE(AZ33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BB33" s="20">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="BC33" s="18" t="n"/>
       <c r="BD33" s="19">
-        <f>IF(BC33="","",IF(BC33="NE","",IF(BC33="0",0,IF(BC33="1",0.5,IF(BC33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BC33="","",IF(BC33="NE","",(IFERROR(IF(ISNUMBER(BC33),BC33,VALUE(BC33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BE33" s="20">
@@ -10338,7 +10338,7 @@
       </c>
       <c r="BF33" s="18" t="n"/>
       <c r="BG33" s="19">
-        <f>IF(BF33="","",IF(BF33="NE","",IF(BF33="0",0,IF(BF33="1",0.5,IF(BF33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BF33="","",IF(BF33="NE","",(IFERROR(IF(ISNUMBER(BF33),BF33,VALUE(BF33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BH33" s="20">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="BI33" s="18" t="n"/>
       <c r="BJ33" s="19">
-        <f>IF(BI33="","",IF(BI33="NE","",IF(BI33="0",0,IF(BI33="1",0.5,IF(BI33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BI33="","",IF(BI33="NE","",(IFERROR(IF(ISNUMBER(BI33),BI33,VALUE(BI33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BK33" s="20">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="BL33" s="18" t="n"/>
       <c r="BM33" s="19">
-        <f>IF(BL33="","",IF(BL33="NE","",IF(BL33="0",0,IF(BL33="1",0.5,IF(BL33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BL33="","",IF(BL33="NE","",(IFERROR(IF(ISNUMBER(BL33),BL33,VALUE(BL33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BN33" s="20">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="BO33" s="18" t="n"/>
       <c r="BP33" s="19">
-        <f>IF(BO33="","",IF(BO33="NE","",IF(BO33="0",0,IF(BO33="1",0.5,IF(BO33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BO33="","",IF(BO33="NE","",(IFERROR(IF(ISNUMBER(BO33),BO33,VALUE(BO33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BQ33" s="20">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="BR33" s="18" t="n"/>
       <c r="BS33" s="19">
-        <f>IF(BR33="","",IF(BR33="NE","",IF(BR33="0",0,IF(BR33="1",0.5,IF(BR33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BR33="","",IF(BR33="NE","",(IFERROR(IF(ISNUMBER(BR33),BR33,VALUE(BR33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BT33" s="20">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="BU33" s="18" t="n"/>
       <c r="BV33" s="19">
-        <f>IF(BU33="","",IF(BU33="NE","",IF(BU33="0",0,IF(BU33="1",0.5,IF(BU33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BU33="","",IF(BU33="NE","",(IFERROR(IF(ISNUMBER(BU33),BU33,VALUE(BU33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BW33" s="20">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="BX33" s="18" t="n"/>
       <c r="BY33" s="19">
-        <f>IF(BX33="","",IF(BX33="NE","",IF(BX33="0",0,IF(BX33="1",0.5,IF(BX33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(BX33="","",IF(BX33="NE","",(IFERROR(IF(ISNUMBER(BX33),BX33,VALUE(BX33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="BZ33" s="20">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="CA33" s="18" t="n"/>
       <c r="CB33" s="19">
-        <f>IF(CA33="","",IF(CA33="NE","",IF(CA33="0",0,IF(CA33="1",0.5,IF(CA33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(CA33="","",IF(CA33="NE","",(IFERROR(IF(ISNUMBER(CA33),CA33,VALUE(CA33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="CC33" s="20">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="CD33" s="18" t="n"/>
       <c r="CE33" s="19">
-        <f>IF(CD33="","",IF(CD33="NE","",IF(CD33="0",0,IF(CD33="1",0.5,IF(CD33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(CD33="","",IF(CD33="NE","",(IFERROR(IF(ISNUMBER(CD33),CD33,VALUE(CD33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="CF33" s="20">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="CG33" s="18" t="n"/>
       <c r="CH33" s="19">
-        <f>IF(CG33="","",IF(CG33="NE","",IF(CG33="0",0,IF(CG33="1",0.5,IF(CG33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(CG33="","",IF(CG33="NE","",(IFERROR(IF(ISNUMBER(CG33),CG33,VALUE(CG33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="CI33" s="20">
@@ -10428,7 +10428,7 @@
       </c>
       <c r="CJ33" s="18" t="n"/>
       <c r="CK33" s="19">
-        <f>IF(CJ33="","",IF(CJ33="NE","",IF(CJ33="0",0,IF(CJ33="1",0.5,IF(CJ33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(CJ33="","",IF(CJ33="NE","",(IFERROR(IF(ISNUMBER(CJ33),CJ33,VALUE(CJ33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="CL33" s="20">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="CM33" s="18" t="n"/>
       <c r="CN33" s="19">
-        <f>IF(CM33="","",IF(CM33="NE","",IF(CM33="0",0,IF(CM33="1",0.5,IF(CM33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(CM33="","",IF(CM33="NE","",(IFERROR(IF(ISNUMBER(CM33),CM33,VALUE(CM33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="CO33" s="20">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="CP33" s="18" t="n"/>
       <c r="CQ33" s="19">
-        <f>IF(CP33="","",IF(CP33="NE","",IF(CP33="0",0,IF(CP33="1",0.5,IF(CP33="2",1,0)))*$F33*$F$26*20))</f>
+        <f>IF(CP33="","",IF(CP33="NE","",(IFERROR(IF(ISNUMBER(CP33),CP33,VALUE(CP33)),0)/2)*$F33*$F$26*20))</f>
         <v/>
       </c>
       <c r="CR33" s="20">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="G35" s="18" t="n"/>
       <c r="H35" s="19">
-        <f>IF(G35="","",IF(G35="NE","",IF(G35="0",0,IF(G35="1",0.5,IF(G35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(G35="","",IF(G35="NE","",(IFERROR(IF(ISNUMBER(G35),G35,VALUE(G35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="I35" s="20">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="J35" s="18" t="n"/>
       <c r="K35" s="19">
-        <f>IF(J35="","",IF(J35="NE","",IF(J35="0",0,IF(J35="1",0.5,IF(J35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(J35="","",IF(J35="NE","",(IFERROR(IF(ISNUMBER(J35),J35,VALUE(J35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="L35" s="20">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="M35" s="18" t="n"/>
       <c r="N35" s="19">
-        <f>IF(M35="","",IF(M35="NE","",IF(M35="0",0,IF(M35="1",0.5,IF(M35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(M35="","",IF(M35="NE","",(IFERROR(IF(ISNUMBER(M35),M35,VALUE(M35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="O35" s="20">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="P35" s="18" t="n"/>
       <c r="Q35" s="19">
-        <f>IF(P35="","",IF(P35="NE","",IF(P35="0",0,IF(P35="1",0.5,IF(P35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(P35="","",IF(P35="NE","",(IFERROR(IF(ISNUMBER(P35),P35,VALUE(P35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="R35" s="20">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="S35" s="18" t="n"/>
       <c r="T35" s="19">
-        <f>IF(S35="","",IF(S35="NE","",IF(S35="0",0,IF(S35="1",0.5,IF(S35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(S35="","",IF(S35="NE","",(IFERROR(IF(ISNUMBER(S35),S35,VALUE(S35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="U35" s="20">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="V35" s="18" t="n"/>
       <c r="W35" s="19">
-        <f>IF(V35="","",IF(V35="NE","",IF(V35="0",0,IF(V35="1",0.5,IF(V35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(V35="","",IF(V35="NE","",(IFERROR(IF(ISNUMBER(V35),V35,VALUE(V35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="X35" s="20">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="Y35" s="18" t="n"/>
       <c r="Z35" s="19">
-        <f>IF(Y35="","",IF(Y35="NE","",IF(Y35="0",0,IF(Y35="1",0.5,IF(Y35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(Y35="","",IF(Y35="NE","",(IFERROR(IF(ISNUMBER(Y35),Y35,VALUE(Y35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA35" s="20">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AB35" s="18" t="n"/>
       <c r="AC35" s="19">
-        <f>IF(AB35="","",IF(AB35="NE","",IF(AB35="0",0,IF(AB35="1",0.5,IF(AB35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AB35="","",IF(AB35="NE","",(IFERROR(IF(ISNUMBER(AB35),AB35,VALUE(AB35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD35" s="20">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="AE35" s="18" t="n"/>
       <c r="AF35" s="19">
-        <f>IF(AE35="","",IF(AE35="NE","",IF(AE35="0",0,IF(AE35="1",0.5,IF(AE35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AE35="","",IF(AE35="NE","",(IFERROR(IF(ISNUMBER(AE35),AE35,VALUE(AE35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG35" s="20">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="AH35" s="18" t="n"/>
       <c r="AI35" s="19">
-        <f>IF(AH35="","",IF(AH35="NE","",IF(AH35="0",0,IF(AH35="1",0.5,IF(AH35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AH35="","",IF(AH35="NE","",(IFERROR(IF(ISNUMBER(AH35),AH35,VALUE(AH35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ35" s="20">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="AK35" s="18" t="n"/>
       <c r="AL35" s="19">
-        <f>IF(AK35="","",IF(AK35="NE","",IF(AK35="0",0,IF(AK35="1",0.5,IF(AK35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AK35="","",IF(AK35="NE","",(IFERROR(IF(ISNUMBER(AK35),AK35,VALUE(AK35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM35" s="20">
@@ -10694,7 +10694,7 @@
       </c>
       <c r="AN35" s="18" t="n"/>
       <c r="AO35" s="19">
-        <f>IF(AN35="","",IF(AN35="NE","",IF(AN35="0",0,IF(AN35="1",0.5,IF(AN35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AN35="","",IF(AN35="NE","",(IFERROR(IF(ISNUMBER(AN35),AN35,VALUE(AN35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP35" s="20">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="AQ35" s="18" t="n"/>
       <c r="AR35" s="19">
-        <f>IF(AQ35="","",IF(AQ35="NE","",IF(AQ35="0",0,IF(AQ35="1",0.5,IF(AQ35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AQ35="","",IF(AQ35="NE","",(IFERROR(IF(ISNUMBER(AQ35),AQ35,VALUE(AQ35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS35" s="20">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="AT35" s="18" t="n"/>
       <c r="AU35" s="19">
-        <f>IF(AT35="","",IF(AT35="NE","",IF(AT35="0",0,IF(AT35="1",0.5,IF(AT35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AT35="","",IF(AT35="NE","",(IFERROR(IF(ISNUMBER(AT35),AT35,VALUE(AT35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV35" s="20">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="AW35" s="18" t="n"/>
       <c r="AX35" s="19">
-        <f>IF(AW35="","",IF(AW35="NE","",IF(AW35="0",0,IF(AW35="1",0.5,IF(AW35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AW35="","",IF(AW35="NE","",(IFERROR(IF(ISNUMBER(AW35),AW35,VALUE(AW35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY35" s="20">
@@ -10730,7 +10730,7 @@
       </c>
       <c r="AZ35" s="18" t="n"/>
       <c r="BA35" s="19">
-        <f>IF(AZ35="","",IF(AZ35="NE","",IF(AZ35="0",0,IF(AZ35="1",0.5,IF(AZ35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(AZ35="","",IF(AZ35="NE","",(IFERROR(IF(ISNUMBER(AZ35),AZ35,VALUE(AZ35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB35" s="20">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="BC35" s="18" t="n"/>
       <c r="BD35" s="19">
-        <f>IF(BC35="","",IF(BC35="NE","",IF(BC35="0",0,IF(BC35="1",0.5,IF(BC35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BC35="","",IF(BC35="NE","",(IFERROR(IF(ISNUMBER(BC35),BC35,VALUE(BC35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE35" s="20">
@@ -10748,7 +10748,7 @@
       </c>
       <c r="BF35" s="18" t="n"/>
       <c r="BG35" s="19">
-        <f>IF(BF35="","",IF(BF35="NE","",IF(BF35="0",0,IF(BF35="1",0.5,IF(BF35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BF35="","",IF(BF35="NE","",(IFERROR(IF(ISNUMBER(BF35),BF35,VALUE(BF35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH35" s="20">
@@ -10757,7 +10757,7 @@
       </c>
       <c r="BI35" s="18" t="n"/>
       <c r="BJ35" s="19">
-        <f>IF(BI35="","",IF(BI35="NE","",IF(BI35="0",0,IF(BI35="1",0.5,IF(BI35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BI35="","",IF(BI35="NE","",(IFERROR(IF(ISNUMBER(BI35),BI35,VALUE(BI35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK35" s="20">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="BL35" s="18" t="n"/>
       <c r="BM35" s="19">
-        <f>IF(BL35="","",IF(BL35="NE","",IF(BL35="0",0,IF(BL35="1",0.5,IF(BL35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BL35="","",IF(BL35="NE","",(IFERROR(IF(ISNUMBER(BL35),BL35,VALUE(BL35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN35" s="20">
@@ -10775,7 +10775,7 @@
       </c>
       <c r="BO35" s="18" t="n"/>
       <c r="BP35" s="19">
-        <f>IF(BO35="","",IF(BO35="NE","",IF(BO35="0",0,IF(BO35="1",0.5,IF(BO35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BO35="","",IF(BO35="NE","",(IFERROR(IF(ISNUMBER(BO35),BO35,VALUE(BO35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ35" s="20">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="BR35" s="18" t="n"/>
       <c r="BS35" s="19">
-        <f>IF(BR35="","",IF(BR35="NE","",IF(BR35="0",0,IF(BR35="1",0.5,IF(BR35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BR35="","",IF(BR35="NE","",(IFERROR(IF(ISNUMBER(BR35),BR35,VALUE(BR35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT35" s="20">
@@ -10793,7 +10793,7 @@
       </c>
       <c r="BU35" s="18" t="n"/>
       <c r="BV35" s="19">
-        <f>IF(BU35="","",IF(BU35="NE","",IF(BU35="0",0,IF(BU35="1",0.5,IF(BU35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BU35="","",IF(BU35="NE","",(IFERROR(IF(ISNUMBER(BU35),BU35,VALUE(BU35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW35" s="20">
@@ -10802,7 +10802,7 @@
       </c>
       <c r="BX35" s="18" t="n"/>
       <c r="BY35" s="19">
-        <f>IF(BX35="","",IF(BX35="NE","",IF(BX35="0",0,IF(BX35="1",0.5,IF(BX35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(BX35="","",IF(BX35="NE","",(IFERROR(IF(ISNUMBER(BX35),BX35,VALUE(BX35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ35" s="20">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="CA35" s="18" t="n"/>
       <c r="CB35" s="19">
-        <f>IF(CA35="","",IF(CA35="NE","",IF(CA35="0",0,IF(CA35="1",0.5,IF(CA35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(CA35="","",IF(CA35="NE","",(IFERROR(IF(ISNUMBER(CA35),CA35,VALUE(CA35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC35" s="20">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="CD35" s="18" t="n"/>
       <c r="CE35" s="19">
-        <f>IF(CD35="","",IF(CD35="NE","",IF(CD35="0",0,IF(CD35="1",0.5,IF(CD35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(CD35="","",IF(CD35="NE","",(IFERROR(IF(ISNUMBER(CD35),CD35,VALUE(CD35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF35" s="20">
@@ -10829,7 +10829,7 @@
       </c>
       <c r="CG35" s="18" t="n"/>
       <c r="CH35" s="19">
-        <f>IF(CG35="","",IF(CG35="NE","",IF(CG35="0",0,IF(CG35="1",0.5,IF(CG35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(CG35="","",IF(CG35="NE","",(IFERROR(IF(ISNUMBER(CG35),CG35,VALUE(CG35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI35" s="20">
@@ -10838,7 +10838,7 @@
       </c>
       <c r="CJ35" s="18" t="n"/>
       <c r="CK35" s="19">
-        <f>IF(CJ35="","",IF(CJ35="NE","",IF(CJ35="0",0,IF(CJ35="1",0.5,IF(CJ35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(CJ35="","",IF(CJ35="NE","",(IFERROR(IF(ISNUMBER(CJ35),CJ35,VALUE(CJ35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL35" s="20">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="CM35" s="18" t="n"/>
       <c r="CN35" s="19">
-        <f>IF(CM35="","",IF(CM35="NE","",IF(CM35="0",0,IF(CM35="1",0.5,IF(CM35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(CM35="","",IF(CM35="NE","",(IFERROR(IF(ISNUMBER(CM35),CM35,VALUE(CM35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO35" s="20">
@@ -10856,7 +10856,7 @@
       </c>
       <c r="CP35" s="18" t="n"/>
       <c r="CQ35" s="19">
-        <f>IF(CP35="","",IF(CP35="NE","",IF(CP35="0",0,IF(CP35="1",0.5,IF(CP35="2",1,0)))*$F35*$F$34*20))</f>
+        <f>IF(CP35="","",IF(CP35="NE","",(IFERROR(IF(ISNUMBER(CP35),CP35,VALUE(CP35)),0)/2)*$F35*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR35" s="20">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="G36" s="18" t="n"/>
       <c r="H36" s="19">
-        <f>IF(G36="","",IF(G36="NE","",IF(G36="0",0,IF(G36="1",0.5,IF(G36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(G36="","",IF(G36="NE","",(IFERROR(IF(ISNUMBER(G36),G36,VALUE(G36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="I36" s="20">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="J36" s="18" t="n"/>
       <c r="K36" s="19">
-        <f>IF(J36="","",IF(J36="NE","",IF(J36="0",0,IF(J36="1",0.5,IF(J36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(J36="","",IF(J36="NE","",(IFERROR(IF(ISNUMBER(J36),J36,VALUE(J36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="L36" s="20">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="M36" s="18" t="n"/>
       <c r="N36" s="19">
-        <f>IF(M36="","",IF(M36="NE","",IF(M36="0",0,IF(M36="1",0.5,IF(M36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(M36="","",IF(M36="NE","",(IFERROR(IF(ISNUMBER(M36),M36,VALUE(M36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="O36" s="20">
@@ -10920,7 +10920,7 @@
       </c>
       <c r="P36" s="18" t="n"/>
       <c r="Q36" s="19">
-        <f>IF(P36="","",IF(P36="NE","",IF(P36="0",0,IF(P36="1",0.5,IF(P36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(P36="","",IF(P36="NE","",(IFERROR(IF(ISNUMBER(P36),P36,VALUE(P36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="R36" s="20">
@@ -10929,7 +10929,7 @@
       </c>
       <c r="S36" s="18" t="n"/>
       <c r="T36" s="19">
-        <f>IF(S36="","",IF(S36="NE","",IF(S36="0",0,IF(S36="1",0.5,IF(S36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(S36="","",IF(S36="NE","",(IFERROR(IF(ISNUMBER(S36),S36,VALUE(S36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="U36" s="20">
@@ -10938,7 +10938,7 @@
       </c>
       <c r="V36" s="18" t="n"/>
       <c r="W36" s="19">
-        <f>IF(V36="","",IF(V36="NE","",IF(V36="0",0,IF(V36="1",0.5,IF(V36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(V36="","",IF(V36="NE","",(IFERROR(IF(ISNUMBER(V36),V36,VALUE(V36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="X36" s="20">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="Y36" s="18" t="n"/>
       <c r="Z36" s="19">
-        <f>IF(Y36="","",IF(Y36="NE","",IF(Y36="0",0,IF(Y36="1",0.5,IF(Y36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(Y36="","",IF(Y36="NE","",(IFERROR(IF(ISNUMBER(Y36),Y36,VALUE(Y36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA36" s="20">
@@ -10956,7 +10956,7 @@
       </c>
       <c r="AB36" s="18" t="n"/>
       <c r="AC36" s="19">
-        <f>IF(AB36="","",IF(AB36="NE","",IF(AB36="0",0,IF(AB36="1",0.5,IF(AB36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AB36="","",IF(AB36="NE","",(IFERROR(IF(ISNUMBER(AB36),AB36,VALUE(AB36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD36" s="20">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="AE36" s="18" t="n"/>
       <c r="AF36" s="19">
-        <f>IF(AE36="","",IF(AE36="NE","",IF(AE36="0",0,IF(AE36="1",0.5,IF(AE36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AE36="","",IF(AE36="NE","",(IFERROR(IF(ISNUMBER(AE36),AE36,VALUE(AE36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG36" s="20">
@@ -10974,7 +10974,7 @@
       </c>
       <c r="AH36" s="18" t="n"/>
       <c r="AI36" s="19">
-        <f>IF(AH36="","",IF(AH36="NE","",IF(AH36="0",0,IF(AH36="1",0.5,IF(AH36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AH36="","",IF(AH36="NE","",(IFERROR(IF(ISNUMBER(AH36),AH36,VALUE(AH36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ36" s="20">
@@ -10983,7 +10983,7 @@
       </c>
       <c r="AK36" s="18" t="n"/>
       <c r="AL36" s="19">
-        <f>IF(AK36="","",IF(AK36="NE","",IF(AK36="0",0,IF(AK36="1",0.5,IF(AK36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AK36="","",IF(AK36="NE","",(IFERROR(IF(ISNUMBER(AK36),AK36,VALUE(AK36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM36" s="20">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="AN36" s="18" t="n"/>
       <c r="AO36" s="19">
-        <f>IF(AN36="","",IF(AN36="NE","",IF(AN36="0",0,IF(AN36="1",0.5,IF(AN36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AN36="","",IF(AN36="NE","",(IFERROR(IF(ISNUMBER(AN36),AN36,VALUE(AN36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP36" s="20">
@@ -11001,7 +11001,7 @@
       </c>
       <c r="AQ36" s="18" t="n"/>
       <c r="AR36" s="19">
-        <f>IF(AQ36="","",IF(AQ36="NE","",IF(AQ36="0",0,IF(AQ36="1",0.5,IF(AQ36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AQ36="","",IF(AQ36="NE","",(IFERROR(IF(ISNUMBER(AQ36),AQ36,VALUE(AQ36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS36" s="20">
@@ -11010,7 +11010,7 @@
       </c>
       <c r="AT36" s="18" t="n"/>
       <c r="AU36" s="19">
-        <f>IF(AT36="","",IF(AT36="NE","",IF(AT36="0",0,IF(AT36="1",0.5,IF(AT36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AT36="","",IF(AT36="NE","",(IFERROR(IF(ISNUMBER(AT36),AT36,VALUE(AT36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV36" s="20">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AW36" s="18" t="n"/>
       <c r="AX36" s="19">
-        <f>IF(AW36="","",IF(AW36="NE","",IF(AW36="0",0,IF(AW36="1",0.5,IF(AW36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AW36="","",IF(AW36="NE","",(IFERROR(IF(ISNUMBER(AW36),AW36,VALUE(AW36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY36" s="20">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="AZ36" s="18" t="n"/>
       <c r="BA36" s="19">
-        <f>IF(AZ36="","",IF(AZ36="NE","",IF(AZ36="0",0,IF(AZ36="1",0.5,IF(AZ36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(AZ36="","",IF(AZ36="NE","",(IFERROR(IF(ISNUMBER(AZ36),AZ36,VALUE(AZ36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB36" s="20">
@@ -11037,7 +11037,7 @@
       </c>
       <c r="BC36" s="18" t="n"/>
       <c r="BD36" s="19">
-        <f>IF(BC36="","",IF(BC36="NE","",IF(BC36="0",0,IF(BC36="1",0.5,IF(BC36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BC36="","",IF(BC36="NE","",(IFERROR(IF(ISNUMBER(BC36),BC36,VALUE(BC36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE36" s="20">
@@ -11046,7 +11046,7 @@
       </c>
       <c r="BF36" s="18" t="n"/>
       <c r="BG36" s="19">
-        <f>IF(BF36="","",IF(BF36="NE","",IF(BF36="0",0,IF(BF36="1",0.5,IF(BF36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BF36="","",IF(BF36="NE","",(IFERROR(IF(ISNUMBER(BF36),BF36,VALUE(BF36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH36" s="20">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="BI36" s="18" t="n"/>
       <c r="BJ36" s="19">
-        <f>IF(BI36="","",IF(BI36="NE","",IF(BI36="0",0,IF(BI36="1",0.5,IF(BI36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BI36="","",IF(BI36="NE","",(IFERROR(IF(ISNUMBER(BI36),BI36,VALUE(BI36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK36" s="20">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="BL36" s="18" t="n"/>
       <c r="BM36" s="19">
-        <f>IF(BL36="","",IF(BL36="NE","",IF(BL36="0",0,IF(BL36="1",0.5,IF(BL36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BL36="","",IF(BL36="NE","",(IFERROR(IF(ISNUMBER(BL36),BL36,VALUE(BL36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN36" s="20">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="BO36" s="18" t="n"/>
       <c r="BP36" s="19">
-        <f>IF(BO36="","",IF(BO36="NE","",IF(BO36="0",0,IF(BO36="1",0.5,IF(BO36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BO36="","",IF(BO36="NE","",(IFERROR(IF(ISNUMBER(BO36),BO36,VALUE(BO36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ36" s="20">
@@ -11082,7 +11082,7 @@
       </c>
       <c r="BR36" s="18" t="n"/>
       <c r="BS36" s="19">
-        <f>IF(BR36="","",IF(BR36="NE","",IF(BR36="0",0,IF(BR36="1",0.5,IF(BR36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BR36="","",IF(BR36="NE","",(IFERROR(IF(ISNUMBER(BR36),BR36,VALUE(BR36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT36" s="20">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="BU36" s="18" t="n"/>
       <c r="BV36" s="19">
-        <f>IF(BU36="","",IF(BU36="NE","",IF(BU36="0",0,IF(BU36="1",0.5,IF(BU36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BU36="","",IF(BU36="NE","",(IFERROR(IF(ISNUMBER(BU36),BU36,VALUE(BU36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW36" s="20">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="BX36" s="18" t="n"/>
       <c r="BY36" s="19">
-        <f>IF(BX36="","",IF(BX36="NE","",IF(BX36="0",0,IF(BX36="1",0.5,IF(BX36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(BX36="","",IF(BX36="NE","",(IFERROR(IF(ISNUMBER(BX36),BX36,VALUE(BX36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ36" s="20">
@@ -11109,7 +11109,7 @@
       </c>
       <c r="CA36" s="18" t="n"/>
       <c r="CB36" s="19">
-        <f>IF(CA36="","",IF(CA36="NE","",IF(CA36="0",0,IF(CA36="1",0.5,IF(CA36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(CA36="","",IF(CA36="NE","",(IFERROR(IF(ISNUMBER(CA36),CA36,VALUE(CA36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC36" s="20">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="CD36" s="18" t="n"/>
       <c r="CE36" s="19">
-        <f>IF(CD36="","",IF(CD36="NE","",IF(CD36="0",0,IF(CD36="1",0.5,IF(CD36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(CD36="","",IF(CD36="NE","",(IFERROR(IF(ISNUMBER(CD36),CD36,VALUE(CD36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF36" s="20">
@@ -11127,7 +11127,7 @@
       </c>
       <c r="CG36" s="18" t="n"/>
       <c r="CH36" s="19">
-        <f>IF(CG36="","",IF(CG36="NE","",IF(CG36="0",0,IF(CG36="1",0.5,IF(CG36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(CG36="","",IF(CG36="NE","",(IFERROR(IF(ISNUMBER(CG36),CG36,VALUE(CG36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI36" s="20">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="CJ36" s="18" t="n"/>
       <c r="CK36" s="19">
-        <f>IF(CJ36="","",IF(CJ36="NE","",IF(CJ36="0",0,IF(CJ36="1",0.5,IF(CJ36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(CJ36="","",IF(CJ36="NE","",(IFERROR(IF(ISNUMBER(CJ36),CJ36,VALUE(CJ36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL36" s="20">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="CM36" s="18" t="n"/>
       <c r="CN36" s="19">
-        <f>IF(CM36="","",IF(CM36="NE","",IF(CM36="0",0,IF(CM36="1",0.5,IF(CM36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(CM36="","",IF(CM36="NE","",(IFERROR(IF(ISNUMBER(CM36),CM36,VALUE(CM36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO36" s="20">
@@ -11154,7 +11154,7 @@
       </c>
       <c r="CP36" s="18" t="n"/>
       <c r="CQ36" s="19">
-        <f>IF(CP36="","",IF(CP36="NE","",IF(CP36="0",0,IF(CP36="1",0.5,IF(CP36="2",1,0)))*$F36*$F$34*20))</f>
+        <f>IF(CP36="","",IF(CP36="NE","",(IFERROR(IF(ISNUMBER(CP36),CP36,VALUE(CP36)),0)/2)*$F36*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR36" s="20">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="G37" s="18" t="n"/>
       <c r="H37" s="19">
-        <f>IF(G37="","",IF(G37="NE","",IF(G37="0",0,IF(G37="1",0.5,IF(G37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(G37="","",IF(G37="NE","",(IFERROR(IF(ISNUMBER(G37),G37,VALUE(G37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="I37" s="20">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="J37" s="18" t="n"/>
       <c r="K37" s="19">
-        <f>IF(J37="","",IF(J37="NE","",IF(J37="0",0,IF(J37="1",0.5,IF(J37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(J37="","",IF(J37="NE","",(IFERROR(IF(ISNUMBER(J37),J37,VALUE(J37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="L37" s="20">
@@ -11209,7 +11209,7 @@
       </c>
       <c r="M37" s="18" t="n"/>
       <c r="N37" s="19">
-        <f>IF(M37="","",IF(M37="NE","",IF(M37="0",0,IF(M37="1",0.5,IF(M37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(M37="","",IF(M37="NE","",(IFERROR(IF(ISNUMBER(M37),M37,VALUE(M37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="O37" s="20">
@@ -11218,7 +11218,7 @@
       </c>
       <c r="P37" s="18" t="n"/>
       <c r="Q37" s="19">
-        <f>IF(P37="","",IF(P37="NE","",IF(P37="0",0,IF(P37="1",0.5,IF(P37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(P37="","",IF(P37="NE","",(IFERROR(IF(ISNUMBER(P37),P37,VALUE(P37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="R37" s="20">
@@ -11227,7 +11227,7 @@
       </c>
       <c r="S37" s="18" t="n"/>
       <c r="T37" s="19">
-        <f>IF(S37="","",IF(S37="NE","",IF(S37="0",0,IF(S37="1",0.5,IF(S37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(S37="","",IF(S37="NE","",(IFERROR(IF(ISNUMBER(S37),S37,VALUE(S37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="U37" s="20">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="V37" s="18" t="n"/>
       <c r="W37" s="19">
-        <f>IF(V37="","",IF(V37="NE","",IF(V37="0",0,IF(V37="1",0.5,IF(V37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(V37="","",IF(V37="NE","",(IFERROR(IF(ISNUMBER(V37),V37,VALUE(V37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="X37" s="20">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="Y37" s="18" t="n"/>
       <c r="Z37" s="19">
-        <f>IF(Y37="","",IF(Y37="NE","",IF(Y37="0",0,IF(Y37="1",0.5,IF(Y37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(Y37="","",IF(Y37="NE","",(IFERROR(IF(ISNUMBER(Y37),Y37,VALUE(Y37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA37" s="20">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB37" s="18" t="n"/>
       <c r="AC37" s="19">
-        <f>IF(AB37="","",IF(AB37="NE","",IF(AB37="0",0,IF(AB37="1",0.5,IF(AB37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AB37="","",IF(AB37="NE","",(IFERROR(IF(ISNUMBER(AB37),AB37,VALUE(AB37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD37" s="20">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="AE37" s="18" t="n"/>
       <c r="AF37" s="19">
-        <f>IF(AE37="","",IF(AE37="NE","",IF(AE37="0",0,IF(AE37="1",0.5,IF(AE37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AE37="","",IF(AE37="NE","",(IFERROR(IF(ISNUMBER(AE37),AE37,VALUE(AE37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG37" s="20">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="AH37" s="18" t="n"/>
       <c r="AI37" s="19">
-        <f>IF(AH37="","",IF(AH37="NE","",IF(AH37="0",0,IF(AH37="1",0.5,IF(AH37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AH37="","",IF(AH37="NE","",(IFERROR(IF(ISNUMBER(AH37),AH37,VALUE(AH37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ37" s="20">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="AK37" s="18" t="n"/>
       <c r="AL37" s="19">
-        <f>IF(AK37="","",IF(AK37="NE","",IF(AK37="0",0,IF(AK37="1",0.5,IF(AK37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AK37="","",IF(AK37="NE","",(IFERROR(IF(ISNUMBER(AK37),AK37,VALUE(AK37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM37" s="20">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="AN37" s="18" t="n"/>
       <c r="AO37" s="19">
-        <f>IF(AN37="","",IF(AN37="NE","",IF(AN37="0",0,IF(AN37="1",0.5,IF(AN37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AN37="","",IF(AN37="NE","",(IFERROR(IF(ISNUMBER(AN37),AN37,VALUE(AN37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP37" s="20">
@@ -11299,7 +11299,7 @@
       </c>
       <c r="AQ37" s="18" t="n"/>
       <c r="AR37" s="19">
-        <f>IF(AQ37="","",IF(AQ37="NE","",IF(AQ37="0",0,IF(AQ37="1",0.5,IF(AQ37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AQ37="","",IF(AQ37="NE","",(IFERROR(IF(ISNUMBER(AQ37),AQ37,VALUE(AQ37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS37" s="20">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="AT37" s="18" t="n"/>
       <c r="AU37" s="19">
-        <f>IF(AT37="","",IF(AT37="NE","",IF(AT37="0",0,IF(AT37="1",0.5,IF(AT37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AT37="","",IF(AT37="NE","",(IFERROR(IF(ISNUMBER(AT37),AT37,VALUE(AT37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV37" s="20">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="AW37" s="18" t="n"/>
       <c r="AX37" s="19">
-        <f>IF(AW37="","",IF(AW37="NE","",IF(AW37="0",0,IF(AW37="1",0.5,IF(AW37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AW37="","",IF(AW37="NE","",(IFERROR(IF(ISNUMBER(AW37),AW37,VALUE(AW37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY37" s="20">
@@ -11326,7 +11326,7 @@
       </c>
       <c r="AZ37" s="18" t="n"/>
       <c r="BA37" s="19">
-        <f>IF(AZ37="","",IF(AZ37="NE","",IF(AZ37="0",0,IF(AZ37="1",0.5,IF(AZ37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(AZ37="","",IF(AZ37="NE","",(IFERROR(IF(ISNUMBER(AZ37),AZ37,VALUE(AZ37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB37" s="20">
@@ -11335,7 +11335,7 @@
       </c>
       <c r="BC37" s="18" t="n"/>
       <c r="BD37" s="19">
-        <f>IF(BC37="","",IF(BC37="NE","",IF(BC37="0",0,IF(BC37="1",0.5,IF(BC37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BC37="","",IF(BC37="NE","",(IFERROR(IF(ISNUMBER(BC37),BC37,VALUE(BC37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE37" s="20">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="BF37" s="18" t="n"/>
       <c r="BG37" s="19">
-        <f>IF(BF37="","",IF(BF37="NE","",IF(BF37="0",0,IF(BF37="1",0.5,IF(BF37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BF37="","",IF(BF37="NE","",(IFERROR(IF(ISNUMBER(BF37),BF37,VALUE(BF37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH37" s="20">
@@ -11353,7 +11353,7 @@
       </c>
       <c r="BI37" s="18" t="n"/>
       <c r="BJ37" s="19">
-        <f>IF(BI37="","",IF(BI37="NE","",IF(BI37="0",0,IF(BI37="1",0.5,IF(BI37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BI37="","",IF(BI37="NE","",(IFERROR(IF(ISNUMBER(BI37),BI37,VALUE(BI37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK37" s="20">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="BL37" s="18" t="n"/>
       <c r="BM37" s="19">
-        <f>IF(BL37="","",IF(BL37="NE","",IF(BL37="0",0,IF(BL37="1",0.5,IF(BL37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BL37="","",IF(BL37="NE","",(IFERROR(IF(ISNUMBER(BL37),BL37,VALUE(BL37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN37" s="20">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="BO37" s="18" t="n"/>
       <c r="BP37" s="19">
-        <f>IF(BO37="","",IF(BO37="NE","",IF(BO37="0",0,IF(BO37="1",0.5,IF(BO37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BO37="","",IF(BO37="NE","",(IFERROR(IF(ISNUMBER(BO37),BO37,VALUE(BO37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ37" s="20">
@@ -11380,7 +11380,7 @@
       </c>
       <c r="BR37" s="18" t="n"/>
       <c r="BS37" s="19">
-        <f>IF(BR37="","",IF(BR37="NE","",IF(BR37="0",0,IF(BR37="1",0.5,IF(BR37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BR37="","",IF(BR37="NE","",(IFERROR(IF(ISNUMBER(BR37),BR37,VALUE(BR37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT37" s="20">
@@ -11389,7 +11389,7 @@
       </c>
       <c r="BU37" s="18" t="n"/>
       <c r="BV37" s="19">
-        <f>IF(BU37="","",IF(BU37="NE","",IF(BU37="0",0,IF(BU37="1",0.5,IF(BU37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BU37="","",IF(BU37="NE","",(IFERROR(IF(ISNUMBER(BU37),BU37,VALUE(BU37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW37" s="20">
@@ -11398,7 +11398,7 @@
       </c>
       <c r="BX37" s="18" t="n"/>
       <c r="BY37" s="19">
-        <f>IF(BX37="","",IF(BX37="NE","",IF(BX37="0",0,IF(BX37="1",0.5,IF(BX37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(BX37="","",IF(BX37="NE","",(IFERROR(IF(ISNUMBER(BX37),BX37,VALUE(BX37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ37" s="20">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="CA37" s="18" t="n"/>
       <c r="CB37" s="19">
-        <f>IF(CA37="","",IF(CA37="NE","",IF(CA37="0",0,IF(CA37="1",0.5,IF(CA37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(CA37="","",IF(CA37="NE","",(IFERROR(IF(ISNUMBER(CA37),CA37,VALUE(CA37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC37" s="20">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="CD37" s="18" t="n"/>
       <c r="CE37" s="19">
-        <f>IF(CD37="","",IF(CD37="NE","",IF(CD37="0",0,IF(CD37="1",0.5,IF(CD37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(CD37="","",IF(CD37="NE","",(IFERROR(IF(ISNUMBER(CD37),CD37,VALUE(CD37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF37" s="20">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="CG37" s="18" t="n"/>
       <c r="CH37" s="19">
-        <f>IF(CG37="","",IF(CG37="NE","",IF(CG37="0",0,IF(CG37="1",0.5,IF(CG37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(CG37="","",IF(CG37="NE","",(IFERROR(IF(ISNUMBER(CG37),CG37,VALUE(CG37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI37" s="20">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="CJ37" s="18" t="n"/>
       <c r="CK37" s="19">
-        <f>IF(CJ37="","",IF(CJ37="NE","",IF(CJ37="0",0,IF(CJ37="1",0.5,IF(CJ37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(CJ37="","",IF(CJ37="NE","",(IFERROR(IF(ISNUMBER(CJ37),CJ37,VALUE(CJ37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL37" s="20">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="CM37" s="18" t="n"/>
       <c r="CN37" s="19">
-        <f>IF(CM37="","",IF(CM37="NE","",IF(CM37="0",0,IF(CM37="1",0.5,IF(CM37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(CM37="","",IF(CM37="NE","",(IFERROR(IF(ISNUMBER(CM37),CM37,VALUE(CM37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO37" s="20">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="CP37" s="18" t="n"/>
       <c r="CQ37" s="19">
-        <f>IF(CP37="","",IF(CP37="NE","",IF(CP37="0",0,IF(CP37="1",0.5,IF(CP37="2",1,0)))*$F37*$F$34*20))</f>
+        <f>IF(CP37="","",IF(CP37="NE","",(IFERROR(IF(ISNUMBER(CP37),CP37,VALUE(CP37)),0)/2)*$F37*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR37" s="20">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="G38" s="18" t="n"/>
       <c r="H38" s="19">
-        <f>IF(G38="","",IF(G38="NE","",IF(G38="0",0,IF(G38="1",0.5,IF(G38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(G38="","",IF(G38="NE","",(IFERROR(IF(ISNUMBER(G38),G38,VALUE(G38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="I38" s="20">
@@ -11498,7 +11498,7 @@
       </c>
       <c r="J38" s="18" t="n"/>
       <c r="K38" s="19">
-        <f>IF(J38="","",IF(J38="NE","",IF(J38="0",0,IF(J38="1",0.5,IF(J38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(J38="","",IF(J38="NE","",(IFERROR(IF(ISNUMBER(J38),J38,VALUE(J38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="L38" s="20">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="M38" s="18" t="n"/>
       <c r="N38" s="19">
-        <f>IF(M38="","",IF(M38="NE","",IF(M38="0",0,IF(M38="1",0.5,IF(M38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(M38="","",IF(M38="NE","",(IFERROR(IF(ISNUMBER(M38),M38,VALUE(M38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="O38" s="20">
@@ -11516,7 +11516,7 @@
       </c>
       <c r="P38" s="18" t="n"/>
       <c r="Q38" s="19">
-        <f>IF(P38="","",IF(P38="NE","",IF(P38="0",0,IF(P38="1",0.5,IF(P38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(P38="","",IF(P38="NE","",(IFERROR(IF(ISNUMBER(P38),P38,VALUE(P38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="R38" s="20">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="S38" s="18" t="n"/>
       <c r="T38" s="19">
-        <f>IF(S38="","",IF(S38="NE","",IF(S38="0",0,IF(S38="1",0.5,IF(S38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(S38="","",IF(S38="NE","",(IFERROR(IF(ISNUMBER(S38),S38,VALUE(S38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="U38" s="20">
@@ -11534,7 +11534,7 @@
       </c>
       <c r="V38" s="18" t="n"/>
       <c r="W38" s="19">
-        <f>IF(V38="","",IF(V38="NE","",IF(V38="0",0,IF(V38="1",0.5,IF(V38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(V38="","",IF(V38="NE","",(IFERROR(IF(ISNUMBER(V38),V38,VALUE(V38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="X38" s="20">
@@ -11543,7 +11543,7 @@
       </c>
       <c r="Y38" s="18" t="n"/>
       <c r="Z38" s="19">
-        <f>IF(Y38="","",IF(Y38="NE","",IF(Y38="0",0,IF(Y38="1",0.5,IF(Y38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(Y38="","",IF(Y38="NE","",(IFERROR(IF(ISNUMBER(Y38),Y38,VALUE(Y38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA38" s="20">
@@ -11552,7 +11552,7 @@
       </c>
       <c r="AB38" s="18" t="n"/>
       <c r="AC38" s="19">
-        <f>IF(AB38="","",IF(AB38="NE","",IF(AB38="0",0,IF(AB38="1",0.5,IF(AB38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AB38="","",IF(AB38="NE","",(IFERROR(IF(ISNUMBER(AB38),AB38,VALUE(AB38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD38" s="20">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="AE38" s="18" t="n"/>
       <c r="AF38" s="19">
-        <f>IF(AE38="","",IF(AE38="NE","",IF(AE38="0",0,IF(AE38="1",0.5,IF(AE38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AE38="","",IF(AE38="NE","",(IFERROR(IF(ISNUMBER(AE38),AE38,VALUE(AE38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG38" s="20">
@@ -11570,7 +11570,7 @@
       </c>
       <c r="AH38" s="18" t="n"/>
       <c r="AI38" s="19">
-        <f>IF(AH38="","",IF(AH38="NE","",IF(AH38="0",0,IF(AH38="1",0.5,IF(AH38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AH38="","",IF(AH38="NE","",(IFERROR(IF(ISNUMBER(AH38),AH38,VALUE(AH38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ38" s="20">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="AK38" s="18" t="n"/>
       <c r="AL38" s="19">
-        <f>IF(AK38="","",IF(AK38="NE","",IF(AK38="0",0,IF(AK38="1",0.5,IF(AK38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AK38="","",IF(AK38="NE","",(IFERROR(IF(ISNUMBER(AK38),AK38,VALUE(AK38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM38" s="20">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="AN38" s="18" t="n"/>
       <c r="AO38" s="19">
-        <f>IF(AN38="","",IF(AN38="NE","",IF(AN38="0",0,IF(AN38="1",0.5,IF(AN38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AN38="","",IF(AN38="NE","",(IFERROR(IF(ISNUMBER(AN38),AN38,VALUE(AN38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP38" s="20">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="AQ38" s="18" t="n"/>
       <c r="AR38" s="19">
-        <f>IF(AQ38="","",IF(AQ38="NE","",IF(AQ38="0",0,IF(AQ38="1",0.5,IF(AQ38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AQ38="","",IF(AQ38="NE","",(IFERROR(IF(ISNUMBER(AQ38),AQ38,VALUE(AQ38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS38" s="20">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="AT38" s="18" t="n"/>
       <c r="AU38" s="19">
-        <f>IF(AT38="","",IF(AT38="NE","",IF(AT38="0",0,IF(AT38="1",0.5,IF(AT38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AT38="","",IF(AT38="NE","",(IFERROR(IF(ISNUMBER(AT38),AT38,VALUE(AT38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV38" s="20">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="AW38" s="18" t="n"/>
       <c r="AX38" s="19">
-        <f>IF(AW38="","",IF(AW38="NE","",IF(AW38="0",0,IF(AW38="1",0.5,IF(AW38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AW38="","",IF(AW38="NE","",(IFERROR(IF(ISNUMBER(AW38),AW38,VALUE(AW38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY38" s="20">
@@ -11624,7 +11624,7 @@
       </c>
       <c r="AZ38" s="18" t="n"/>
       <c r="BA38" s="19">
-        <f>IF(AZ38="","",IF(AZ38="NE","",IF(AZ38="0",0,IF(AZ38="1",0.5,IF(AZ38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(AZ38="","",IF(AZ38="NE","",(IFERROR(IF(ISNUMBER(AZ38),AZ38,VALUE(AZ38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB38" s="20">
@@ -11633,7 +11633,7 @@
       </c>
       <c r="BC38" s="18" t="n"/>
       <c r="BD38" s="19">
-        <f>IF(BC38="","",IF(BC38="NE","",IF(BC38="0",0,IF(BC38="1",0.5,IF(BC38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BC38="","",IF(BC38="NE","",(IFERROR(IF(ISNUMBER(BC38),BC38,VALUE(BC38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE38" s="20">
@@ -11642,7 +11642,7 @@
       </c>
       <c r="BF38" s="18" t="n"/>
       <c r="BG38" s="19">
-        <f>IF(BF38="","",IF(BF38="NE","",IF(BF38="0",0,IF(BF38="1",0.5,IF(BF38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BF38="","",IF(BF38="NE","",(IFERROR(IF(ISNUMBER(BF38),BF38,VALUE(BF38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH38" s="20">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="BI38" s="18" t="n"/>
       <c r="BJ38" s="19">
-        <f>IF(BI38="","",IF(BI38="NE","",IF(BI38="0",0,IF(BI38="1",0.5,IF(BI38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BI38="","",IF(BI38="NE","",(IFERROR(IF(ISNUMBER(BI38),BI38,VALUE(BI38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK38" s="20">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="BL38" s="18" t="n"/>
       <c r="BM38" s="19">
-        <f>IF(BL38="","",IF(BL38="NE","",IF(BL38="0",0,IF(BL38="1",0.5,IF(BL38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BL38="","",IF(BL38="NE","",(IFERROR(IF(ISNUMBER(BL38),BL38,VALUE(BL38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN38" s="20">
@@ -11669,7 +11669,7 @@
       </c>
       <c r="BO38" s="18" t="n"/>
       <c r="BP38" s="19">
-        <f>IF(BO38="","",IF(BO38="NE","",IF(BO38="0",0,IF(BO38="1",0.5,IF(BO38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BO38="","",IF(BO38="NE","",(IFERROR(IF(ISNUMBER(BO38),BO38,VALUE(BO38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ38" s="20">
@@ -11678,7 +11678,7 @@
       </c>
       <c r="BR38" s="18" t="n"/>
       <c r="BS38" s="19">
-        <f>IF(BR38="","",IF(BR38="NE","",IF(BR38="0",0,IF(BR38="1",0.5,IF(BR38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BR38="","",IF(BR38="NE","",(IFERROR(IF(ISNUMBER(BR38),BR38,VALUE(BR38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT38" s="20">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="BU38" s="18" t="n"/>
       <c r="BV38" s="19">
-        <f>IF(BU38="","",IF(BU38="NE","",IF(BU38="0",0,IF(BU38="1",0.5,IF(BU38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BU38="","",IF(BU38="NE","",(IFERROR(IF(ISNUMBER(BU38),BU38,VALUE(BU38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW38" s="20">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="BX38" s="18" t="n"/>
       <c r="BY38" s="19">
-        <f>IF(BX38="","",IF(BX38="NE","",IF(BX38="0",0,IF(BX38="1",0.5,IF(BX38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(BX38="","",IF(BX38="NE","",(IFERROR(IF(ISNUMBER(BX38),BX38,VALUE(BX38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ38" s="20">
@@ -11705,7 +11705,7 @@
       </c>
       <c r="CA38" s="18" t="n"/>
       <c r="CB38" s="19">
-        <f>IF(CA38="","",IF(CA38="NE","",IF(CA38="0",0,IF(CA38="1",0.5,IF(CA38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(CA38="","",IF(CA38="NE","",(IFERROR(IF(ISNUMBER(CA38),CA38,VALUE(CA38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC38" s="20">
@@ -11714,7 +11714,7 @@
       </c>
       <c r="CD38" s="18" t="n"/>
       <c r="CE38" s="19">
-        <f>IF(CD38="","",IF(CD38="NE","",IF(CD38="0",0,IF(CD38="1",0.5,IF(CD38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(CD38="","",IF(CD38="NE","",(IFERROR(IF(ISNUMBER(CD38),CD38,VALUE(CD38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF38" s="20">
@@ -11723,7 +11723,7 @@
       </c>
       <c r="CG38" s="18" t="n"/>
       <c r="CH38" s="19">
-        <f>IF(CG38="","",IF(CG38="NE","",IF(CG38="0",0,IF(CG38="1",0.5,IF(CG38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(CG38="","",IF(CG38="NE","",(IFERROR(IF(ISNUMBER(CG38),CG38,VALUE(CG38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI38" s="20">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="CJ38" s="18" t="n"/>
       <c r="CK38" s="19">
-        <f>IF(CJ38="","",IF(CJ38="NE","",IF(CJ38="0",0,IF(CJ38="1",0.5,IF(CJ38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(CJ38="","",IF(CJ38="NE","",(IFERROR(IF(ISNUMBER(CJ38),CJ38,VALUE(CJ38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL38" s="20">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="CM38" s="18" t="n"/>
       <c r="CN38" s="19">
-        <f>IF(CM38="","",IF(CM38="NE","",IF(CM38="0",0,IF(CM38="1",0.5,IF(CM38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(CM38="","",IF(CM38="NE","",(IFERROR(IF(ISNUMBER(CM38),CM38,VALUE(CM38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO38" s="20">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="CP38" s="18" t="n"/>
       <c r="CQ38" s="19">
-        <f>IF(CP38="","",IF(CP38="NE","",IF(CP38="0",0,IF(CP38="1",0.5,IF(CP38="2",1,0)))*$F38*$F$34*20))</f>
+        <f>IF(CP38="","",IF(CP38="NE","",(IFERROR(IF(ISNUMBER(CP38),CP38,VALUE(CP38)),0)/2)*$F38*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR38" s="20">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="G39" s="18" t="n"/>
       <c r="H39" s="19">
-        <f>IF(G39="","",IF(G39="NE","",IF(G39="0",0,IF(G39="1",0.5,IF(G39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(G39="","",IF(G39="NE","",(IFERROR(IF(ISNUMBER(G39),G39,VALUE(G39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="I39" s="20">
@@ -11796,7 +11796,7 @@
       </c>
       <c r="J39" s="18" t="n"/>
       <c r="K39" s="19">
-        <f>IF(J39="","",IF(J39="NE","",IF(J39="0",0,IF(J39="1",0.5,IF(J39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(J39="","",IF(J39="NE","",(IFERROR(IF(ISNUMBER(J39),J39,VALUE(J39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="L39" s="20">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="M39" s="18" t="n"/>
       <c r="N39" s="19">
-        <f>IF(M39="","",IF(M39="NE","",IF(M39="0",0,IF(M39="1",0.5,IF(M39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(M39="","",IF(M39="NE","",(IFERROR(IF(ISNUMBER(M39),M39,VALUE(M39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="O39" s="20">
@@ -11814,7 +11814,7 @@
       </c>
       <c r="P39" s="18" t="n"/>
       <c r="Q39" s="19">
-        <f>IF(P39="","",IF(P39="NE","",IF(P39="0",0,IF(P39="1",0.5,IF(P39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(P39="","",IF(P39="NE","",(IFERROR(IF(ISNUMBER(P39),P39,VALUE(P39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="R39" s="20">
@@ -11823,7 +11823,7 @@
       </c>
       <c r="S39" s="18" t="n"/>
       <c r="T39" s="19">
-        <f>IF(S39="","",IF(S39="NE","",IF(S39="0",0,IF(S39="1",0.5,IF(S39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(S39="","",IF(S39="NE","",(IFERROR(IF(ISNUMBER(S39),S39,VALUE(S39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="U39" s="20">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="V39" s="18" t="n"/>
       <c r="W39" s="19">
-        <f>IF(V39="","",IF(V39="NE","",IF(V39="0",0,IF(V39="1",0.5,IF(V39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(V39="","",IF(V39="NE","",(IFERROR(IF(ISNUMBER(V39),V39,VALUE(V39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="X39" s="20">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="Y39" s="18" t="n"/>
       <c r="Z39" s="19">
-        <f>IF(Y39="","",IF(Y39="NE","",IF(Y39="0",0,IF(Y39="1",0.5,IF(Y39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(Y39="","",IF(Y39="NE","",(IFERROR(IF(ISNUMBER(Y39),Y39,VALUE(Y39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA39" s="20">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="AB39" s="18" t="n"/>
       <c r="AC39" s="19">
-        <f>IF(AB39="","",IF(AB39="NE","",IF(AB39="0",0,IF(AB39="1",0.5,IF(AB39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AB39="","",IF(AB39="NE","",(IFERROR(IF(ISNUMBER(AB39),AB39,VALUE(AB39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD39" s="20">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="AE39" s="18" t="n"/>
       <c r="AF39" s="19">
-        <f>IF(AE39="","",IF(AE39="NE","",IF(AE39="0",0,IF(AE39="1",0.5,IF(AE39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AE39="","",IF(AE39="NE","",(IFERROR(IF(ISNUMBER(AE39),AE39,VALUE(AE39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG39" s="20">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="AH39" s="18" t="n"/>
       <c r="AI39" s="19">
-        <f>IF(AH39="","",IF(AH39="NE","",IF(AH39="0",0,IF(AH39="1",0.5,IF(AH39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AH39="","",IF(AH39="NE","",(IFERROR(IF(ISNUMBER(AH39),AH39,VALUE(AH39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ39" s="20">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="AK39" s="18" t="n"/>
       <c r="AL39" s="19">
-        <f>IF(AK39="","",IF(AK39="NE","",IF(AK39="0",0,IF(AK39="1",0.5,IF(AK39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AK39="","",IF(AK39="NE","",(IFERROR(IF(ISNUMBER(AK39),AK39,VALUE(AK39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM39" s="20">
@@ -11886,7 +11886,7 @@
       </c>
       <c r="AN39" s="18" t="n"/>
       <c r="AO39" s="19">
-        <f>IF(AN39="","",IF(AN39="NE","",IF(AN39="0",0,IF(AN39="1",0.5,IF(AN39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AN39="","",IF(AN39="NE","",(IFERROR(IF(ISNUMBER(AN39),AN39,VALUE(AN39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP39" s="20">
@@ -11895,7 +11895,7 @@
       </c>
       <c r="AQ39" s="18" t="n"/>
       <c r="AR39" s="19">
-        <f>IF(AQ39="","",IF(AQ39="NE","",IF(AQ39="0",0,IF(AQ39="1",0.5,IF(AQ39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AQ39="","",IF(AQ39="NE","",(IFERROR(IF(ISNUMBER(AQ39),AQ39,VALUE(AQ39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS39" s="20">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="AT39" s="18" t="n"/>
       <c r="AU39" s="19">
-        <f>IF(AT39="","",IF(AT39="NE","",IF(AT39="0",0,IF(AT39="1",0.5,IF(AT39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AT39="","",IF(AT39="NE","",(IFERROR(IF(ISNUMBER(AT39),AT39,VALUE(AT39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV39" s="20">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="AW39" s="18" t="n"/>
       <c r="AX39" s="19">
-        <f>IF(AW39="","",IF(AW39="NE","",IF(AW39="0",0,IF(AW39="1",0.5,IF(AW39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AW39="","",IF(AW39="NE","",(IFERROR(IF(ISNUMBER(AW39),AW39,VALUE(AW39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY39" s="20">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="AZ39" s="18" t="n"/>
       <c r="BA39" s="19">
-        <f>IF(AZ39="","",IF(AZ39="NE","",IF(AZ39="0",0,IF(AZ39="1",0.5,IF(AZ39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(AZ39="","",IF(AZ39="NE","",(IFERROR(IF(ISNUMBER(AZ39),AZ39,VALUE(AZ39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB39" s="20">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="BC39" s="18" t="n"/>
       <c r="BD39" s="19">
-        <f>IF(BC39="","",IF(BC39="NE","",IF(BC39="0",0,IF(BC39="1",0.5,IF(BC39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BC39="","",IF(BC39="NE","",(IFERROR(IF(ISNUMBER(BC39),BC39,VALUE(BC39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE39" s="20">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="BF39" s="18" t="n"/>
       <c r="BG39" s="19">
-        <f>IF(BF39="","",IF(BF39="NE","",IF(BF39="0",0,IF(BF39="1",0.5,IF(BF39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BF39="","",IF(BF39="NE","",(IFERROR(IF(ISNUMBER(BF39),BF39,VALUE(BF39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH39" s="20">
@@ -11949,7 +11949,7 @@
       </c>
       <c r="BI39" s="18" t="n"/>
       <c r="BJ39" s="19">
-        <f>IF(BI39="","",IF(BI39="NE","",IF(BI39="0",0,IF(BI39="1",0.5,IF(BI39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BI39="","",IF(BI39="NE","",(IFERROR(IF(ISNUMBER(BI39),BI39,VALUE(BI39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK39" s="20">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="BL39" s="18" t="n"/>
       <c r="BM39" s="19">
-        <f>IF(BL39="","",IF(BL39="NE","",IF(BL39="0",0,IF(BL39="1",0.5,IF(BL39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BL39="","",IF(BL39="NE","",(IFERROR(IF(ISNUMBER(BL39),BL39,VALUE(BL39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN39" s="20">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="BO39" s="18" t="n"/>
       <c r="BP39" s="19">
-        <f>IF(BO39="","",IF(BO39="NE","",IF(BO39="0",0,IF(BO39="1",0.5,IF(BO39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BO39="","",IF(BO39="NE","",(IFERROR(IF(ISNUMBER(BO39),BO39,VALUE(BO39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ39" s="20">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="BR39" s="18" t="n"/>
       <c r="BS39" s="19">
-        <f>IF(BR39="","",IF(BR39="NE","",IF(BR39="0",0,IF(BR39="1",0.5,IF(BR39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BR39="","",IF(BR39="NE","",(IFERROR(IF(ISNUMBER(BR39),BR39,VALUE(BR39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT39" s="20">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="BU39" s="18" t="n"/>
       <c r="BV39" s="19">
-        <f>IF(BU39="","",IF(BU39="NE","",IF(BU39="0",0,IF(BU39="1",0.5,IF(BU39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BU39="","",IF(BU39="NE","",(IFERROR(IF(ISNUMBER(BU39),BU39,VALUE(BU39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW39" s="20">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="BX39" s="18" t="n"/>
       <c r="BY39" s="19">
-        <f>IF(BX39="","",IF(BX39="NE","",IF(BX39="0",0,IF(BX39="1",0.5,IF(BX39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(BX39="","",IF(BX39="NE","",(IFERROR(IF(ISNUMBER(BX39),BX39,VALUE(BX39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ39" s="20">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="CA39" s="18" t="n"/>
       <c r="CB39" s="19">
-        <f>IF(CA39="","",IF(CA39="NE","",IF(CA39="0",0,IF(CA39="1",0.5,IF(CA39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(CA39="","",IF(CA39="NE","",(IFERROR(IF(ISNUMBER(CA39),CA39,VALUE(CA39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC39" s="20">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="CD39" s="18" t="n"/>
       <c r="CE39" s="19">
-        <f>IF(CD39="","",IF(CD39="NE","",IF(CD39="0",0,IF(CD39="1",0.5,IF(CD39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(CD39="","",IF(CD39="NE","",(IFERROR(IF(ISNUMBER(CD39),CD39,VALUE(CD39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF39" s="20">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="CG39" s="18" t="n"/>
       <c r="CH39" s="19">
-        <f>IF(CG39="","",IF(CG39="NE","",IF(CG39="0",0,IF(CG39="1",0.5,IF(CG39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(CG39="","",IF(CG39="NE","",(IFERROR(IF(ISNUMBER(CG39),CG39,VALUE(CG39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI39" s="20">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="CJ39" s="18" t="n"/>
       <c r="CK39" s="19">
-        <f>IF(CJ39="","",IF(CJ39="NE","",IF(CJ39="0",0,IF(CJ39="1",0.5,IF(CJ39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(CJ39="","",IF(CJ39="NE","",(IFERROR(IF(ISNUMBER(CJ39),CJ39,VALUE(CJ39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL39" s="20">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="CM39" s="18" t="n"/>
       <c r="CN39" s="19">
-        <f>IF(CM39="","",IF(CM39="NE","",IF(CM39="0",0,IF(CM39="1",0.5,IF(CM39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(CM39="","",IF(CM39="NE","",(IFERROR(IF(ISNUMBER(CM39),CM39,VALUE(CM39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO39" s="20">
@@ -12048,7 +12048,7 @@
       </c>
       <c r="CP39" s="18" t="n"/>
       <c r="CQ39" s="19">
-        <f>IF(CP39="","",IF(CP39="NE","",IF(CP39="0",0,IF(CP39="1",0.5,IF(CP39="2",1,0)))*$F39*$F$34*20))</f>
+        <f>IF(CP39="","",IF(CP39="NE","",(IFERROR(IF(ISNUMBER(CP39),CP39,VALUE(CP39)),0)/2)*$F39*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR39" s="20">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="G40" s="18" t="n"/>
       <c r="H40" s="19">
-        <f>IF(G40="","",IF(G40="NE","",IF(G40="0",0,IF(G40="1",0.5,IF(G40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(G40="","",IF(G40="NE","",(IFERROR(IF(ISNUMBER(G40),G40,VALUE(G40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="I40" s="20">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="J40" s="18" t="n"/>
       <c r="K40" s="19">
-        <f>IF(J40="","",IF(J40="NE","",IF(J40="0",0,IF(J40="1",0.5,IF(J40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(J40="","",IF(J40="NE","",(IFERROR(IF(ISNUMBER(J40),J40,VALUE(J40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="L40" s="20">
@@ -12103,7 +12103,7 @@
       </c>
       <c r="M40" s="18" t="n"/>
       <c r="N40" s="19">
-        <f>IF(M40="","",IF(M40="NE","",IF(M40="0",0,IF(M40="1",0.5,IF(M40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(M40="","",IF(M40="NE","",(IFERROR(IF(ISNUMBER(M40),M40,VALUE(M40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="O40" s="20">
@@ -12112,7 +12112,7 @@
       </c>
       <c r="P40" s="18" t="n"/>
       <c r="Q40" s="19">
-        <f>IF(P40="","",IF(P40="NE","",IF(P40="0",0,IF(P40="1",0.5,IF(P40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(P40="","",IF(P40="NE","",(IFERROR(IF(ISNUMBER(P40),P40,VALUE(P40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="R40" s="20">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="S40" s="18" t="n"/>
       <c r="T40" s="19">
-        <f>IF(S40="","",IF(S40="NE","",IF(S40="0",0,IF(S40="1",0.5,IF(S40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(S40="","",IF(S40="NE","",(IFERROR(IF(ISNUMBER(S40),S40,VALUE(S40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="U40" s="20">
@@ -12130,7 +12130,7 @@
       </c>
       <c r="V40" s="18" t="n"/>
       <c r="W40" s="19">
-        <f>IF(V40="","",IF(V40="NE","",IF(V40="0",0,IF(V40="1",0.5,IF(V40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(V40="","",IF(V40="NE","",(IFERROR(IF(ISNUMBER(V40),V40,VALUE(V40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="X40" s="20">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="Y40" s="18" t="n"/>
       <c r="Z40" s="19">
-        <f>IF(Y40="","",IF(Y40="NE","",IF(Y40="0",0,IF(Y40="1",0.5,IF(Y40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(Y40="","",IF(Y40="NE","",(IFERROR(IF(ISNUMBER(Y40),Y40,VALUE(Y40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA40" s="20">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="AB40" s="18" t="n"/>
       <c r="AC40" s="19">
-        <f>IF(AB40="","",IF(AB40="NE","",IF(AB40="0",0,IF(AB40="1",0.5,IF(AB40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AB40="","",IF(AB40="NE","",(IFERROR(IF(ISNUMBER(AB40),AB40,VALUE(AB40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD40" s="20">
@@ -12157,7 +12157,7 @@
       </c>
       <c r="AE40" s="18" t="n"/>
       <c r="AF40" s="19">
-        <f>IF(AE40="","",IF(AE40="NE","",IF(AE40="0",0,IF(AE40="1",0.5,IF(AE40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AE40="","",IF(AE40="NE","",(IFERROR(IF(ISNUMBER(AE40),AE40,VALUE(AE40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG40" s="20">
@@ -12166,7 +12166,7 @@
       </c>
       <c r="AH40" s="18" t="n"/>
       <c r="AI40" s="19">
-        <f>IF(AH40="","",IF(AH40="NE","",IF(AH40="0",0,IF(AH40="1",0.5,IF(AH40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AH40="","",IF(AH40="NE","",(IFERROR(IF(ISNUMBER(AH40),AH40,VALUE(AH40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ40" s="20">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="AK40" s="18" t="n"/>
       <c r="AL40" s="19">
-        <f>IF(AK40="","",IF(AK40="NE","",IF(AK40="0",0,IF(AK40="1",0.5,IF(AK40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AK40="","",IF(AK40="NE","",(IFERROR(IF(ISNUMBER(AK40),AK40,VALUE(AK40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM40" s="20">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="AN40" s="18" t="n"/>
       <c r="AO40" s="19">
-        <f>IF(AN40="","",IF(AN40="NE","",IF(AN40="0",0,IF(AN40="1",0.5,IF(AN40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AN40="","",IF(AN40="NE","",(IFERROR(IF(ISNUMBER(AN40),AN40,VALUE(AN40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP40" s="20">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="AQ40" s="18" t="n"/>
       <c r="AR40" s="19">
-        <f>IF(AQ40="","",IF(AQ40="NE","",IF(AQ40="0",0,IF(AQ40="1",0.5,IF(AQ40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AQ40="","",IF(AQ40="NE","",(IFERROR(IF(ISNUMBER(AQ40),AQ40,VALUE(AQ40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS40" s="20">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="AT40" s="18" t="n"/>
       <c r="AU40" s="19">
-        <f>IF(AT40="","",IF(AT40="NE","",IF(AT40="0",0,IF(AT40="1",0.5,IF(AT40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AT40="","",IF(AT40="NE","",(IFERROR(IF(ISNUMBER(AT40),AT40,VALUE(AT40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV40" s="20">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="AW40" s="18" t="n"/>
       <c r="AX40" s="19">
-        <f>IF(AW40="","",IF(AW40="NE","",IF(AW40="0",0,IF(AW40="1",0.5,IF(AW40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AW40="","",IF(AW40="NE","",(IFERROR(IF(ISNUMBER(AW40),AW40,VALUE(AW40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY40" s="20">
@@ -12220,7 +12220,7 @@
       </c>
       <c r="AZ40" s="18" t="n"/>
       <c r="BA40" s="19">
-        <f>IF(AZ40="","",IF(AZ40="NE","",IF(AZ40="0",0,IF(AZ40="1",0.5,IF(AZ40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(AZ40="","",IF(AZ40="NE","",(IFERROR(IF(ISNUMBER(AZ40),AZ40,VALUE(AZ40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB40" s="20">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="BC40" s="18" t="n"/>
       <c r="BD40" s="19">
-        <f>IF(BC40="","",IF(BC40="NE","",IF(BC40="0",0,IF(BC40="1",0.5,IF(BC40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BC40="","",IF(BC40="NE","",(IFERROR(IF(ISNUMBER(BC40),BC40,VALUE(BC40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE40" s="20">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="BF40" s="18" t="n"/>
       <c r="BG40" s="19">
-        <f>IF(BF40="","",IF(BF40="NE","",IF(BF40="0",0,IF(BF40="1",0.5,IF(BF40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BF40="","",IF(BF40="NE","",(IFERROR(IF(ISNUMBER(BF40),BF40,VALUE(BF40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH40" s="20">
@@ -12247,7 +12247,7 @@
       </c>
       <c r="BI40" s="18" t="n"/>
       <c r="BJ40" s="19">
-        <f>IF(BI40="","",IF(BI40="NE","",IF(BI40="0",0,IF(BI40="1",0.5,IF(BI40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BI40="","",IF(BI40="NE","",(IFERROR(IF(ISNUMBER(BI40),BI40,VALUE(BI40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK40" s="20">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="BL40" s="18" t="n"/>
       <c r="BM40" s="19">
-        <f>IF(BL40="","",IF(BL40="NE","",IF(BL40="0",0,IF(BL40="1",0.5,IF(BL40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BL40="","",IF(BL40="NE","",(IFERROR(IF(ISNUMBER(BL40),BL40,VALUE(BL40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN40" s="20">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="BO40" s="18" t="n"/>
       <c r="BP40" s="19">
-        <f>IF(BO40="","",IF(BO40="NE","",IF(BO40="0",0,IF(BO40="1",0.5,IF(BO40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BO40="","",IF(BO40="NE","",(IFERROR(IF(ISNUMBER(BO40),BO40,VALUE(BO40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ40" s="20">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="BR40" s="18" t="n"/>
       <c r="BS40" s="19">
-        <f>IF(BR40="","",IF(BR40="NE","",IF(BR40="0",0,IF(BR40="1",0.5,IF(BR40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BR40="","",IF(BR40="NE","",(IFERROR(IF(ISNUMBER(BR40),BR40,VALUE(BR40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT40" s="20">
@@ -12283,7 +12283,7 @@
       </c>
       <c r="BU40" s="18" t="n"/>
       <c r="BV40" s="19">
-        <f>IF(BU40="","",IF(BU40="NE","",IF(BU40="0",0,IF(BU40="1",0.5,IF(BU40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BU40="","",IF(BU40="NE","",(IFERROR(IF(ISNUMBER(BU40),BU40,VALUE(BU40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW40" s="20">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="BX40" s="18" t="n"/>
       <c r="BY40" s="19">
-        <f>IF(BX40="","",IF(BX40="NE","",IF(BX40="0",0,IF(BX40="1",0.5,IF(BX40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(BX40="","",IF(BX40="NE","",(IFERROR(IF(ISNUMBER(BX40),BX40,VALUE(BX40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ40" s="20">
@@ -12301,7 +12301,7 @@
       </c>
       <c r="CA40" s="18" t="n"/>
       <c r="CB40" s="19">
-        <f>IF(CA40="","",IF(CA40="NE","",IF(CA40="0",0,IF(CA40="1",0.5,IF(CA40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(CA40="","",IF(CA40="NE","",(IFERROR(IF(ISNUMBER(CA40),CA40,VALUE(CA40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC40" s="20">
@@ -12310,7 +12310,7 @@
       </c>
       <c r="CD40" s="18" t="n"/>
       <c r="CE40" s="19">
-        <f>IF(CD40="","",IF(CD40="NE","",IF(CD40="0",0,IF(CD40="1",0.5,IF(CD40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(CD40="","",IF(CD40="NE","",(IFERROR(IF(ISNUMBER(CD40),CD40,VALUE(CD40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF40" s="20">
@@ -12319,7 +12319,7 @@
       </c>
       <c r="CG40" s="18" t="n"/>
       <c r="CH40" s="19">
-        <f>IF(CG40="","",IF(CG40="NE","",IF(CG40="0",0,IF(CG40="1",0.5,IF(CG40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(CG40="","",IF(CG40="NE","",(IFERROR(IF(ISNUMBER(CG40),CG40,VALUE(CG40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI40" s="20">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="CJ40" s="18" t="n"/>
       <c r="CK40" s="19">
-        <f>IF(CJ40="","",IF(CJ40="NE","",IF(CJ40="0",0,IF(CJ40="1",0.5,IF(CJ40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(CJ40="","",IF(CJ40="NE","",(IFERROR(IF(ISNUMBER(CJ40),CJ40,VALUE(CJ40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL40" s="20">
@@ -12337,7 +12337,7 @@
       </c>
       <c r="CM40" s="18" t="n"/>
       <c r="CN40" s="19">
-        <f>IF(CM40="","",IF(CM40="NE","",IF(CM40="0",0,IF(CM40="1",0.5,IF(CM40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(CM40="","",IF(CM40="NE","",(IFERROR(IF(ISNUMBER(CM40),CM40,VALUE(CM40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO40" s="20">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="CP40" s="18" t="n"/>
       <c r="CQ40" s="19">
-        <f>IF(CP40="","",IF(CP40="NE","",IF(CP40="0",0,IF(CP40="1",0.5,IF(CP40="2",1,0)))*$F40*$F$34*20))</f>
+        <f>IF(CP40="","",IF(CP40="NE","",(IFERROR(IF(ISNUMBER(CP40),CP40,VALUE(CP40)),0)/2)*$F40*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR40" s="20">
@@ -12383,7 +12383,7 @@
       </c>
       <c r="G41" s="18" t="n"/>
       <c r="H41" s="19">
-        <f>IF(G41="","",IF(G41="NE","",IF(G41="0",0,IF(G41="1",0.5,IF(G41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(G41="","",IF(G41="NE","",(IFERROR(IF(ISNUMBER(G41),G41,VALUE(G41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="I41" s="20">
@@ -12392,7 +12392,7 @@
       </c>
       <c r="J41" s="18" t="n"/>
       <c r="K41" s="19">
-        <f>IF(J41="","",IF(J41="NE","",IF(J41="0",0,IF(J41="1",0.5,IF(J41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(J41="","",IF(J41="NE","",(IFERROR(IF(ISNUMBER(J41),J41,VALUE(J41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="L41" s="20">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="M41" s="18" t="n"/>
       <c r="N41" s="19">
-        <f>IF(M41="","",IF(M41="NE","",IF(M41="0",0,IF(M41="1",0.5,IF(M41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(M41="","",IF(M41="NE","",(IFERROR(IF(ISNUMBER(M41),M41,VALUE(M41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="O41" s="20">
@@ -12410,7 +12410,7 @@
       </c>
       <c r="P41" s="18" t="n"/>
       <c r="Q41" s="19">
-        <f>IF(P41="","",IF(P41="NE","",IF(P41="0",0,IF(P41="1",0.5,IF(P41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(P41="","",IF(P41="NE","",(IFERROR(IF(ISNUMBER(P41),P41,VALUE(P41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="R41" s="20">
@@ -12419,7 +12419,7 @@
       </c>
       <c r="S41" s="18" t="n"/>
       <c r="T41" s="19">
-        <f>IF(S41="","",IF(S41="NE","",IF(S41="0",0,IF(S41="1",0.5,IF(S41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(S41="","",IF(S41="NE","",(IFERROR(IF(ISNUMBER(S41),S41,VALUE(S41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="U41" s="20">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="V41" s="18" t="n"/>
       <c r="W41" s="19">
-        <f>IF(V41="","",IF(V41="NE","",IF(V41="0",0,IF(V41="1",0.5,IF(V41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(V41="","",IF(V41="NE","",(IFERROR(IF(ISNUMBER(V41),V41,VALUE(V41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="X41" s="20">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="Y41" s="18" t="n"/>
       <c r="Z41" s="19">
-        <f>IF(Y41="","",IF(Y41="NE","",IF(Y41="0",0,IF(Y41="1",0.5,IF(Y41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(Y41="","",IF(Y41="NE","",(IFERROR(IF(ISNUMBER(Y41),Y41,VALUE(Y41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA41" s="20">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="AB41" s="18" t="n"/>
       <c r="AC41" s="19">
-        <f>IF(AB41="","",IF(AB41="NE","",IF(AB41="0",0,IF(AB41="1",0.5,IF(AB41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AB41="","",IF(AB41="NE","",(IFERROR(IF(ISNUMBER(AB41),AB41,VALUE(AB41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD41" s="20">
@@ -12455,7 +12455,7 @@
       </c>
       <c r="AE41" s="18" t="n"/>
       <c r="AF41" s="19">
-        <f>IF(AE41="","",IF(AE41="NE","",IF(AE41="0",0,IF(AE41="1",0.5,IF(AE41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AE41="","",IF(AE41="NE","",(IFERROR(IF(ISNUMBER(AE41),AE41,VALUE(AE41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG41" s="20">
@@ -12464,7 +12464,7 @@
       </c>
       <c r="AH41" s="18" t="n"/>
       <c r="AI41" s="19">
-        <f>IF(AH41="","",IF(AH41="NE","",IF(AH41="0",0,IF(AH41="1",0.5,IF(AH41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AH41="","",IF(AH41="NE","",(IFERROR(IF(ISNUMBER(AH41),AH41,VALUE(AH41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ41" s="20">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="AK41" s="18" t="n"/>
       <c r="AL41" s="19">
-        <f>IF(AK41="","",IF(AK41="NE","",IF(AK41="0",0,IF(AK41="1",0.5,IF(AK41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AK41="","",IF(AK41="NE","",(IFERROR(IF(ISNUMBER(AK41),AK41,VALUE(AK41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM41" s="20">
@@ -12482,7 +12482,7 @@
       </c>
       <c r="AN41" s="18" t="n"/>
       <c r="AO41" s="19">
-        <f>IF(AN41="","",IF(AN41="NE","",IF(AN41="0",0,IF(AN41="1",0.5,IF(AN41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AN41="","",IF(AN41="NE","",(IFERROR(IF(ISNUMBER(AN41),AN41,VALUE(AN41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP41" s="20">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="AQ41" s="18" t="n"/>
       <c r="AR41" s="19">
-        <f>IF(AQ41="","",IF(AQ41="NE","",IF(AQ41="0",0,IF(AQ41="1",0.5,IF(AQ41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AQ41="","",IF(AQ41="NE","",(IFERROR(IF(ISNUMBER(AQ41),AQ41,VALUE(AQ41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS41" s="20">
@@ -12500,7 +12500,7 @@
       </c>
       <c r="AT41" s="18" t="n"/>
       <c r="AU41" s="19">
-        <f>IF(AT41="","",IF(AT41="NE","",IF(AT41="0",0,IF(AT41="1",0.5,IF(AT41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AT41="","",IF(AT41="NE","",(IFERROR(IF(ISNUMBER(AT41),AT41,VALUE(AT41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV41" s="20">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="AW41" s="18" t="n"/>
       <c r="AX41" s="19">
-        <f>IF(AW41="","",IF(AW41="NE","",IF(AW41="0",0,IF(AW41="1",0.5,IF(AW41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AW41="","",IF(AW41="NE","",(IFERROR(IF(ISNUMBER(AW41),AW41,VALUE(AW41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY41" s="20">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="AZ41" s="18" t="n"/>
       <c r="BA41" s="19">
-        <f>IF(AZ41="","",IF(AZ41="NE","",IF(AZ41="0",0,IF(AZ41="1",0.5,IF(AZ41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(AZ41="","",IF(AZ41="NE","",(IFERROR(IF(ISNUMBER(AZ41),AZ41,VALUE(AZ41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB41" s="20">
@@ -12527,7 +12527,7 @@
       </c>
       <c r="BC41" s="18" t="n"/>
       <c r="BD41" s="19">
-        <f>IF(BC41="","",IF(BC41="NE","",IF(BC41="0",0,IF(BC41="1",0.5,IF(BC41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BC41="","",IF(BC41="NE","",(IFERROR(IF(ISNUMBER(BC41),BC41,VALUE(BC41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE41" s="20">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="BF41" s="18" t="n"/>
       <c r="BG41" s="19">
-        <f>IF(BF41="","",IF(BF41="NE","",IF(BF41="0",0,IF(BF41="1",0.5,IF(BF41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BF41="","",IF(BF41="NE","",(IFERROR(IF(ISNUMBER(BF41),BF41,VALUE(BF41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH41" s="20">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="BI41" s="18" t="n"/>
       <c r="BJ41" s="19">
-        <f>IF(BI41="","",IF(BI41="NE","",IF(BI41="0",0,IF(BI41="1",0.5,IF(BI41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BI41="","",IF(BI41="NE","",(IFERROR(IF(ISNUMBER(BI41),BI41,VALUE(BI41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK41" s="20">
@@ -12554,7 +12554,7 @@
       </c>
       <c r="BL41" s="18" t="n"/>
       <c r="BM41" s="19">
-        <f>IF(BL41="","",IF(BL41="NE","",IF(BL41="0",0,IF(BL41="1",0.5,IF(BL41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BL41="","",IF(BL41="NE","",(IFERROR(IF(ISNUMBER(BL41),BL41,VALUE(BL41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN41" s="20">
@@ -12563,7 +12563,7 @@
       </c>
       <c r="BO41" s="18" t="n"/>
       <c r="BP41" s="19">
-        <f>IF(BO41="","",IF(BO41="NE","",IF(BO41="0",0,IF(BO41="1",0.5,IF(BO41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BO41="","",IF(BO41="NE","",(IFERROR(IF(ISNUMBER(BO41),BO41,VALUE(BO41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ41" s="20">
@@ -12572,7 +12572,7 @@
       </c>
       <c r="BR41" s="18" t="n"/>
       <c r="BS41" s="19">
-        <f>IF(BR41="","",IF(BR41="NE","",IF(BR41="0",0,IF(BR41="1",0.5,IF(BR41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BR41="","",IF(BR41="NE","",(IFERROR(IF(ISNUMBER(BR41),BR41,VALUE(BR41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT41" s="20">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="BU41" s="18" t="n"/>
       <c r="BV41" s="19">
-        <f>IF(BU41="","",IF(BU41="NE","",IF(BU41="0",0,IF(BU41="1",0.5,IF(BU41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BU41="","",IF(BU41="NE","",(IFERROR(IF(ISNUMBER(BU41),BU41,VALUE(BU41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW41" s="20">
@@ -12590,7 +12590,7 @@
       </c>
       <c r="BX41" s="18" t="n"/>
       <c r="BY41" s="19">
-        <f>IF(BX41="","",IF(BX41="NE","",IF(BX41="0",0,IF(BX41="1",0.5,IF(BX41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(BX41="","",IF(BX41="NE","",(IFERROR(IF(ISNUMBER(BX41),BX41,VALUE(BX41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ41" s="20">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="CA41" s="18" t="n"/>
       <c r="CB41" s="19">
-        <f>IF(CA41="","",IF(CA41="NE","",IF(CA41="0",0,IF(CA41="1",0.5,IF(CA41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(CA41="","",IF(CA41="NE","",(IFERROR(IF(ISNUMBER(CA41),CA41,VALUE(CA41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC41" s="20">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="CD41" s="18" t="n"/>
       <c r="CE41" s="19">
-        <f>IF(CD41="","",IF(CD41="NE","",IF(CD41="0",0,IF(CD41="1",0.5,IF(CD41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(CD41="","",IF(CD41="NE","",(IFERROR(IF(ISNUMBER(CD41),CD41,VALUE(CD41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF41" s="20">
@@ -12617,7 +12617,7 @@
       </c>
       <c r="CG41" s="18" t="n"/>
       <c r="CH41" s="19">
-        <f>IF(CG41="","",IF(CG41="NE","",IF(CG41="0",0,IF(CG41="1",0.5,IF(CG41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(CG41="","",IF(CG41="NE","",(IFERROR(IF(ISNUMBER(CG41),CG41,VALUE(CG41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI41" s="20">
@@ -12626,7 +12626,7 @@
       </c>
       <c r="CJ41" s="18" t="n"/>
       <c r="CK41" s="19">
-        <f>IF(CJ41="","",IF(CJ41="NE","",IF(CJ41="0",0,IF(CJ41="1",0.5,IF(CJ41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(CJ41="","",IF(CJ41="NE","",(IFERROR(IF(ISNUMBER(CJ41),CJ41,VALUE(CJ41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL41" s="20">
@@ -12635,7 +12635,7 @@
       </c>
       <c r="CM41" s="18" t="n"/>
       <c r="CN41" s="19">
-        <f>IF(CM41="","",IF(CM41="NE","",IF(CM41="0",0,IF(CM41="1",0.5,IF(CM41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(CM41="","",IF(CM41="NE","",(IFERROR(IF(ISNUMBER(CM41),CM41,VALUE(CM41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO41" s="20">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="CP41" s="18" t="n"/>
       <c r="CQ41" s="19">
-        <f>IF(CP41="","",IF(CP41="NE","",IF(CP41="0",0,IF(CP41="1",0.5,IF(CP41="2",1,0)))*$F41*$F$34*20))</f>
+        <f>IF(CP41="","",IF(CP41="NE","",(IFERROR(IF(ISNUMBER(CP41),CP41,VALUE(CP41)),0)/2)*$F41*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR41" s="20">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="G42" s="18" t="n"/>
       <c r="H42" s="19">
-        <f>IF(G42="","",IF(G42="NE","",IF(G42="0",0,IF(G42="1",0.5,IF(G42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(G42="","",IF(G42="NE","",(IFERROR(IF(ISNUMBER(G42),G42,VALUE(G42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="I42" s="20">
@@ -12690,7 +12690,7 @@
       </c>
       <c r="J42" s="18" t="n"/>
       <c r="K42" s="19">
-        <f>IF(J42="","",IF(J42="NE","",IF(J42="0",0,IF(J42="1",0.5,IF(J42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(J42="","",IF(J42="NE","",(IFERROR(IF(ISNUMBER(J42),J42,VALUE(J42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="L42" s="20">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="M42" s="18" t="n"/>
       <c r="N42" s="19">
-        <f>IF(M42="","",IF(M42="NE","",IF(M42="0",0,IF(M42="1",0.5,IF(M42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(M42="","",IF(M42="NE","",(IFERROR(IF(ISNUMBER(M42),M42,VALUE(M42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="O42" s="20">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="P42" s="18" t="n"/>
       <c r="Q42" s="19">
-        <f>IF(P42="","",IF(P42="NE","",IF(P42="0",0,IF(P42="1",0.5,IF(P42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(P42="","",IF(P42="NE","",(IFERROR(IF(ISNUMBER(P42),P42,VALUE(P42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="R42" s="20">
@@ -12717,7 +12717,7 @@
       </c>
       <c r="S42" s="18" t="n"/>
       <c r="T42" s="19">
-        <f>IF(S42="","",IF(S42="NE","",IF(S42="0",0,IF(S42="1",0.5,IF(S42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(S42="","",IF(S42="NE","",(IFERROR(IF(ISNUMBER(S42),S42,VALUE(S42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="U42" s="20">
@@ -12726,7 +12726,7 @@
       </c>
       <c r="V42" s="18" t="n"/>
       <c r="W42" s="19">
-        <f>IF(V42="","",IF(V42="NE","",IF(V42="0",0,IF(V42="1",0.5,IF(V42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(V42="","",IF(V42="NE","",(IFERROR(IF(ISNUMBER(V42),V42,VALUE(V42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="X42" s="20">
@@ -12735,7 +12735,7 @@
       </c>
       <c r="Y42" s="18" t="n"/>
       <c r="Z42" s="19">
-        <f>IF(Y42="","",IF(Y42="NE","",IF(Y42="0",0,IF(Y42="1",0.5,IF(Y42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(Y42="","",IF(Y42="NE","",(IFERROR(IF(ISNUMBER(Y42),Y42,VALUE(Y42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AA42" s="20">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="AB42" s="18" t="n"/>
       <c r="AC42" s="19">
-        <f>IF(AB42="","",IF(AB42="NE","",IF(AB42="0",0,IF(AB42="1",0.5,IF(AB42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AB42="","",IF(AB42="NE","",(IFERROR(IF(ISNUMBER(AB42),AB42,VALUE(AB42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AD42" s="20">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="AE42" s="18" t="n"/>
       <c r="AF42" s="19">
-        <f>IF(AE42="","",IF(AE42="NE","",IF(AE42="0",0,IF(AE42="1",0.5,IF(AE42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AE42="","",IF(AE42="NE","",(IFERROR(IF(ISNUMBER(AE42),AE42,VALUE(AE42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AG42" s="20">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="AH42" s="18" t="n"/>
       <c r="AI42" s="19">
-        <f>IF(AH42="","",IF(AH42="NE","",IF(AH42="0",0,IF(AH42="1",0.5,IF(AH42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AH42="","",IF(AH42="NE","",(IFERROR(IF(ISNUMBER(AH42),AH42,VALUE(AH42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AJ42" s="20">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="AK42" s="18" t="n"/>
       <c r="AL42" s="19">
-        <f>IF(AK42="","",IF(AK42="NE","",IF(AK42="0",0,IF(AK42="1",0.5,IF(AK42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AK42="","",IF(AK42="NE","",(IFERROR(IF(ISNUMBER(AK42),AK42,VALUE(AK42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AM42" s="20">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="AN42" s="18" t="n"/>
       <c r="AO42" s="19">
-        <f>IF(AN42="","",IF(AN42="NE","",IF(AN42="0",0,IF(AN42="1",0.5,IF(AN42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AN42="","",IF(AN42="NE","",(IFERROR(IF(ISNUMBER(AN42),AN42,VALUE(AN42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AP42" s="20">
@@ -12789,7 +12789,7 @@
       </c>
       <c r="AQ42" s="18" t="n"/>
       <c r="AR42" s="19">
-        <f>IF(AQ42="","",IF(AQ42="NE","",IF(AQ42="0",0,IF(AQ42="1",0.5,IF(AQ42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AQ42="","",IF(AQ42="NE","",(IFERROR(IF(ISNUMBER(AQ42),AQ42,VALUE(AQ42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AS42" s="20">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="AT42" s="18" t="n"/>
       <c r="AU42" s="19">
-        <f>IF(AT42="","",IF(AT42="NE","",IF(AT42="0",0,IF(AT42="1",0.5,IF(AT42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AT42="","",IF(AT42="NE","",(IFERROR(IF(ISNUMBER(AT42),AT42,VALUE(AT42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AV42" s="20">
@@ -12807,7 +12807,7 @@
       </c>
       <c r="AW42" s="18" t="n"/>
       <c r="AX42" s="19">
-        <f>IF(AW42="","",IF(AW42="NE","",IF(AW42="0",0,IF(AW42="1",0.5,IF(AW42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AW42="","",IF(AW42="NE","",(IFERROR(IF(ISNUMBER(AW42),AW42,VALUE(AW42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="AY42" s="20">
@@ -12816,7 +12816,7 @@
       </c>
       <c r="AZ42" s="18" t="n"/>
       <c r="BA42" s="19">
-        <f>IF(AZ42="","",IF(AZ42="NE","",IF(AZ42="0",0,IF(AZ42="1",0.5,IF(AZ42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(AZ42="","",IF(AZ42="NE","",(IFERROR(IF(ISNUMBER(AZ42),AZ42,VALUE(AZ42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BB42" s="20">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="BC42" s="18" t="n"/>
       <c r="BD42" s="19">
-        <f>IF(BC42="","",IF(BC42="NE","",IF(BC42="0",0,IF(BC42="1",0.5,IF(BC42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BC42="","",IF(BC42="NE","",(IFERROR(IF(ISNUMBER(BC42),BC42,VALUE(BC42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BE42" s="20">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="BF42" s="18" t="n"/>
       <c r="BG42" s="19">
-        <f>IF(BF42="","",IF(BF42="NE","",IF(BF42="0",0,IF(BF42="1",0.5,IF(BF42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BF42="","",IF(BF42="NE","",(IFERROR(IF(ISNUMBER(BF42),BF42,VALUE(BF42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BH42" s="20">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="BI42" s="18" t="n"/>
       <c r="BJ42" s="19">
-        <f>IF(BI42="","",IF(BI42="NE","",IF(BI42="0",0,IF(BI42="1",0.5,IF(BI42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BI42="","",IF(BI42="NE","",(IFERROR(IF(ISNUMBER(BI42),BI42,VALUE(BI42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BK42" s="20">
@@ -12852,7 +12852,7 @@
       </c>
       <c r="BL42" s="18" t="n"/>
       <c r="BM42" s="19">
-        <f>IF(BL42="","",IF(BL42="NE","",IF(BL42="0",0,IF(BL42="1",0.5,IF(BL42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BL42="","",IF(BL42="NE","",(IFERROR(IF(ISNUMBER(BL42),BL42,VALUE(BL42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BN42" s="20">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="BO42" s="18" t="n"/>
       <c r="BP42" s="19">
-        <f>IF(BO42="","",IF(BO42="NE","",IF(BO42="0",0,IF(BO42="1",0.5,IF(BO42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BO42="","",IF(BO42="NE","",(IFERROR(IF(ISNUMBER(BO42),BO42,VALUE(BO42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BQ42" s="20">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="BR42" s="18" t="n"/>
       <c r="BS42" s="19">
-        <f>IF(BR42="","",IF(BR42="NE","",IF(BR42="0",0,IF(BR42="1",0.5,IF(BR42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BR42="","",IF(BR42="NE","",(IFERROR(IF(ISNUMBER(BR42),BR42,VALUE(BR42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BT42" s="20">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="BU42" s="18" t="n"/>
       <c r="BV42" s="19">
-        <f>IF(BU42="","",IF(BU42="NE","",IF(BU42="0",0,IF(BU42="1",0.5,IF(BU42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BU42="","",IF(BU42="NE","",(IFERROR(IF(ISNUMBER(BU42),BU42,VALUE(BU42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BW42" s="20">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="BX42" s="18" t="n"/>
       <c r="BY42" s="19">
-        <f>IF(BX42="","",IF(BX42="NE","",IF(BX42="0",0,IF(BX42="1",0.5,IF(BX42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(BX42="","",IF(BX42="NE","",(IFERROR(IF(ISNUMBER(BX42),BX42,VALUE(BX42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="BZ42" s="20">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="CA42" s="18" t="n"/>
       <c r="CB42" s="19">
-        <f>IF(CA42="","",IF(CA42="NE","",IF(CA42="0",0,IF(CA42="1",0.5,IF(CA42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(CA42="","",IF(CA42="NE","",(IFERROR(IF(ISNUMBER(CA42),CA42,VALUE(CA42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="CC42" s="20">
@@ -12906,7 +12906,7 @@
       </c>
       <c r="CD42" s="18" t="n"/>
       <c r="CE42" s="19">
-        <f>IF(CD42="","",IF(CD42="NE","",IF(CD42="0",0,IF(CD42="1",0.5,IF(CD42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(CD42="","",IF(CD42="NE","",(IFERROR(IF(ISNUMBER(CD42),CD42,VALUE(CD42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="CF42" s="20">
@@ -12915,7 +12915,7 @@
       </c>
       <c r="CG42" s="18" t="n"/>
       <c r="CH42" s="19">
-        <f>IF(CG42="","",IF(CG42="NE","",IF(CG42="0",0,IF(CG42="1",0.5,IF(CG42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(CG42="","",IF(CG42="NE","",(IFERROR(IF(ISNUMBER(CG42),CG42,VALUE(CG42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="CI42" s="20">
@@ -12924,7 +12924,7 @@
       </c>
       <c r="CJ42" s="18" t="n"/>
       <c r="CK42" s="19">
-        <f>IF(CJ42="","",IF(CJ42="NE","",IF(CJ42="0",0,IF(CJ42="1",0.5,IF(CJ42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(CJ42="","",IF(CJ42="NE","",(IFERROR(IF(ISNUMBER(CJ42),CJ42,VALUE(CJ42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="CL42" s="20">
@@ -12933,7 +12933,7 @@
       </c>
       <c r="CM42" s="18" t="n"/>
       <c r="CN42" s="19">
-        <f>IF(CM42="","",IF(CM42="NE","",IF(CM42="0",0,IF(CM42="1",0.5,IF(CM42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(CM42="","",IF(CM42="NE","",(IFERROR(IF(ISNUMBER(CM42),CM42,VALUE(CM42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="CO42" s="20">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="CP42" s="18" t="n"/>
       <c r="CQ42" s="19">
-        <f>IF(CP42="","",IF(CP42="NE","",IF(CP42="0",0,IF(CP42="1",0.5,IF(CP42="2",1,0)))*$F42*$F$34*20))</f>
+        <f>IF(CP42="","",IF(CP42="NE","",(IFERROR(IF(ISNUMBER(CP42),CP42,VALUE(CP42)),0)/2)*$F42*$F$34*20))</f>
         <v/>
       </c>
       <c r="CR42" s="20">
